--- a/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Viewpoint Elicitation</t>
+          <t>Active Idea Listening</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Collects others' views and integrates feedback to improve ideas during collaborative discussions.</t>
+          <t>Elicits others’ views and integrates feedback to refine ideas during collaborative discussions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Best Practice Comparison</t>
+          <t>Best Practice Benchmarking</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Compares project concepts with industry best‑practice examples of similar products to identify improvement opportunities.</t>
+          <t>Compares project concepts against industry best‑practice examples of similar products to identify improvement opportunities.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="S3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Idea Generation</t>
+          <t>Concept Generation and Development</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lead focused brainstorming sessions to create diverse solutions for identified issues.</t>
+          <t>Generates diverse solutions by leading focused brainstorming sessions to address identified issues.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Concept Generation and Evaluation</t>
+          <t>Concept Development</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Solution Development</t>
+          <t>Creative Thinking</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Applies creative thinking techniques to develop innovative solutions for workplace challenges.</t>
+          <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="S6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Feedback Documentation</t>
+          <t>Document Feedback According to Requirements</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Record and format feedback according to organisational standards for consistent documentation.</t>
+          <t>Records and formats feedback in line with organisational standards to ensure consistent documentation.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="S7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Viability Evaluation</t>
+          <t>Idea Viability Evaluation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Systematically compares ideas against identified viability factors to assess them.</t>
+          <t>Assesses ideas by systematically comparing them against identified viability factors.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1281,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="V8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Works with relevant personnel to identify and select consultation issues for focused analysis.</t>
+          <t>Collaborates with relevant personnel to identify and select consultation issues for focused analysis.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="V9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Information Research</t>
+          <t>Research Information on Solutions</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Collects and assesses data to find viable solutions for the identified issue.</t>
+          <t>Gathers and evaluates relevant data to identify viable solutions to the identified issue.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="V11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Select appropriate solution formats and deliver tailored presentations to stakeholders.</t>
+          <t>Selects appropriate solution formats and delivers tailored presentations to stakeholders.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1701,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="V12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Solution Refinement</t>
+          <t>Solution Refinement and Finalisation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Iteratively refine and finalise solutions to meet specific task requirements.</t>
+          <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Viability Assessment</t>
+          <t>Solution Viability Assessment</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Evaluates alternative solutions to a business problem, identifies constraints, and determines feasible options.</t>
+          <t>Evaluates alternative solutions to a business problem, identifying constraints to determine feasible options.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Feedback Solicitation</t>
+          <t>Stakeholder Idea Feedback Solicitation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Group Facilitation</t>
+          <t>Team Solution Development</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Facilitates group discussions, encourages participation, and coordinates tasks to achieve shared outcomes.</t>
+          <t>Guides group discussions, encourages participation and coordinates tasks to achieve shared outcomes.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2125,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Security Awareness Program Development</t>
+          <t>Cyber Security Awareness Program Development</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Designs, implements and updates organisation‑wide cyber security awareness programmes in line with best practice.</t>
+          <t>Designs, implements and updates organisation‑wide cyber security awareness programs in line with best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="V17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Technical Writing</t>
+          <t>Clear, Industry‑Specific Cyber‑Security Terminology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2337,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Security Awareness Assessment</t>
+          <t>Current Awareness Assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>We assess cyber security awareness in the work area using surveys and interviews to establish a baseline level.</t>
+          <t>Assesses cyber security awareness within the work area through surveys and interviews to establish baseline levels.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="S19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0.97</v>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Security Improvement Communication</t>
+          <t>Communicate Improvement Outcomes</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Communicates review results and cyber security improvement needs following organisational policies and procedures.</t>
+          <t>Communicates review results and cyber security improvement needs in accordance with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="V20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Security Insight Presentation</t>
+          <t>Insight Presentation</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2649,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Data Breach Legislation Interpretation</t>
+          <t>Australian Privacy Legislation Awareness</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Interpret the Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
+          <t>Interprets Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="V22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Security Review Reporting</t>
+          <t>Outcome Documentation of Review and Improvements</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Prepares detailed reports on review outcomes and improvement recommendations for relevant personnel.</t>
+          <t>Prepares detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2861,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="V23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Policy Drafting</t>
+          <t>Cyber Security Policy Development</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Drafts cyber security policies and procedures and shares them with relevant staff.</t>
+          <t>Drafts cyber security policies and procedures and disseminates them to relevant staff.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="V24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Security Practice Review</t>
+          <t>Cyber Security Practice Review</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Systematically reviews cyber security practices to ensure they align with organisational policies and procedures.</t>
+          <t>Conducts systematic reviews of cyber security practices to ensure alignment with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3077,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="V25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cyber Security Record Keeping</t>
+          <t>Cyber Security Documentation Management</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Keeps cyber security protection records current by organising and documenting relevant data.</t>
+          <t>Maintains up‑to‑date cyber security protection records by organising and documenting relevant data.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3185,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="V26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Engage relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
+          <t>Engages relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="V27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Collaborative Cyber Security Awareness</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Works with interdisciplinary teams to design and implement cyber security measures.</t>
+          <t>Collaborates with interdisciplinary teams to design and implement cyber security measures.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3389,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="V28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Platform Utilisation</t>
+          <t>Technology Platform Utilization for Cybersecurity</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Threat Trend Analysis</t>
+          <t>Cyber Threat Trend Review</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3605,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Security Awareness Training Coordination</t>
+          <t>Cyber Security Awareness Training Coordination</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3713,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Evidence Provision and Skill Naming</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="S32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="b">
@@ -3784,7 +3784,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Evidence Provision and Skill Naming</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="S33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="b">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Anti-Malware Installation</t>
+          <t>Anti-Malware Deployment</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Install and configure up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
+          <t>Installs and configures up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="S34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="V34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Impact Analysis</t>
+          <t>Digital Device Security Review</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4011,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration</t>
+          <t>Device Initial Configuration and Update</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sets up new devices by updating firmware and configuring settings.</t>
+          <t>Performs initial device set‑up by updating firmware and configuring settings on new devices.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4112,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="V36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Device Encryption</t>
+          <t>Implement Device Encryption and Security Measures</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Implements device encryption following prescribed procedures to secure hardware.</t>
+          <t>Implements device encryption in accordance with prescribed procedures to secure hardware.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4213,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="V37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Register Maintenance</t>
+          <t>Device Register Management</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Create and update a register of networked devices to support inventory tracking and asset management.</t>
+          <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4326,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="V38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Strategy Effectiveness Evaluation</t>
+          <t>Security Gap Analysis</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Conduct gap analyses to assess and benchmark best‑practice implementation effectiveness.</t>
+          <t>Conducts gap analyses to assess and benchmark best‑practice implementation effectiveness.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4435,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="V39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Creation</t>
+          <t>Create Strong Passwords</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Creates strong, unique passwords for personal and work accounts that meet approved complexity criteria.</t>
+          <t>Generates robust, unique passwords for personal and work accounts in line with approved complexity criteria.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4536,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="V40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Security Planning</t>
+          <t>Physical Security Planning for Digital Devices</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Creates detailed physical security plans and shares them across the organisation to ensure coordinated protection.</t>
+          <t>Develops comprehensive physical security plans and disseminates them organisation‑wide to ensure coordinated protection.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="S41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0.95</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="V41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Risk Categorisation</t>
+          <t>Device Risk Categorisation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Evaluates device data sensitivity and assigns a risk category for security management.</t>
+          <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="V42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Briefing</t>
+          <t>Physical Security Plan Development and Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4859,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Select appropriate security protocols for each device to mitigate identified risk levels.</t>
+          <t>Selects appropriate security protocols for each device to mitigate identified risk levels.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="S44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0.97</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="V44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Strategy Evaluation</t>
+          <t>Security Strategy Selection Support</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5077,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Trend Monitoring</t>
+          <t>Digital Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5182,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Patch Application</t>
+          <t>Device Software Patch Application</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="S47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Two-Factor Authentication Enabling</t>
+          <t>Enable Two-Factor Authentication</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Enable multi‑factor authentication on supported systems to strengthen account security.</t>
+          <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5400,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="V48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Action Plan Development</t>
+          <t>Strategic Action Plan Development</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Creates detailed action plans that align with policies, prioritise tasks and schedule implementation.</t>
+          <t>Develops detailed action plans aligned with policies, prioritising tasks and scheduling implementation.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="S49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="V49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ranks proposed changes to clarify improvement opportunities and guide implementation scheduling.</t>
+          <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="V50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Technology Evaluation</t>
+          <t>Digital Technology Utilization</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="S51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Strategic Evaluation Documentation</t>
+          <t>Document Evaluation and Feedback for Strategic Planning</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5772,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Gap Analysis</t>
+          <t>ICT Gap Analysis and Improvement</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5876,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Impact Assessment</t>
+          <t>Strategic Impact Assessment</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Evaluates proposed ICT system changes in hybrid environments to ensure they align with organisational strategic objectives.</t>
+          <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="V54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Idea Evaluation</t>
+          <t>Innovative Idea Investigation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Researches and tests innovative ideas, then applies findings to refine work practices and processes.</t>
+          <t>Researches and tests innovative ideas, applying findings to refine work practices and processes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6076,7 +6076,7 @@
         <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="V55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Impact Assessment</t>
+          <t>Financial Data Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Compliance Evaluation</t>
+          <t>Policy Compliance Assessment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Assesses policy compliance by documenting standards, targets and implementation approaches in action plans.</t>
+          <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="S57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="V57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Implementation Scheduling</t>
+          <t>Project Scheduling and Action Planning</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Creates detailed action plans and prioritised schedules to implement change initiatives efficiently.</t>
+          <t>Develops detailed action plans with prioritised schedules to implement change initiatives efficiently.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6352,7 +6352,7 @@
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="V58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Change Risk Assessment</t>
+          <t>Implementation Difficulty Assessment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6444,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Proposal Reporting</t>
+          <t>Superior Reporting on Changes and Gaps</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Prepares concise reports that outline changes, gaps and improvement opportunities for senior staff.</t>
+          <t>Prepares concise reports outlining changes, gaps and improvement opportunities for senior staff.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6548,7 +6548,7 @@
         <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="V60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Plan Evaluation</t>
+          <t>Strategic Plan Evaluation</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Decision Analysis</t>
+          <t>Systematic Decision‑Making for Complex Situations</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Applies structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
+          <t>Uses structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6748,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="V62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technical Communication</t>
+          <t>Technical Communication for Diverse Audiences</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Translates technical terms into plain English to help diverse staff understand.</t>
+          <t>Translates technical terminology into plain English to support understanding across diverse staff groups.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="S63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="V63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Text Compliance Analysis</t>
+          <t>Complex Text Analysis for IP, Ethics, and Privacy</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6933,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Policy Compliance Review</t>
+          <t>Privacy Policy Compliance Review</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Code Application</t>
+          <t>Review Ethical Work Practices and Apply Code</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Reviews ethical practices and feedback, then applies the organisational code of ethics to guide decisions.</t>
+          <t>Reviews ethical practices and feedback and applies the organisational code of ethics to guide decisions.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7119,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="V66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Feedback Collection and Response</t>
+          <t>Feedback Handling for Review Procedures</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Collect feedback on review and grievance documents from designated personnel and address it promptly.</t>
+          <t>Collects and addresses feedback on review and grievance documentation from designated personnel.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7212,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="V67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Security Testing</t>
+          <t>Information Security Testing</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Conduct industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
+          <t>Conducts industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         </is>
       </c>
       <c r="V68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Information Synthesis</t>
+          <t>Policy Synthesis and Integration</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Combines diverse sources into clear written reports using specialised terminology and supporting documentation.</t>
+          <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7398,7 +7398,7 @@
         <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="V69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Intellectual Property Legislation Analysis</t>
+          <t>Identify IP &amp; Copyright Legislation, Policies and Procedures</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Policy Distribution</t>
+          <t>Distribute Revised Policies</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="S71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Policy Updating</t>
+          <t>Privacy, Ethics, and IP Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7677,7 +7677,7 @@
         <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Project Planning</t>
+          <t>Develop and Apply IP, Ethics, and Privacy Policies</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sequences and schedules complex activities, monitors progress, and coordinates communication to maintain delivery momentum.</t>
+          <t>Sequences and schedules complex activities, monitors progress and coordinates communication to maintain delivery momentum.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="V74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Change Monitoring</t>
+          <t>Regulatory Change Monitoring</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7956,7 +7956,7 @@
         <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Information Security Management</t>
+          <t>Safe Ethical Digital Handling</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8049,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Distributes updated policies to stakeholders following organisational protocols.</t>
+          <t>Distributes updated policies to stakeholders in accordance with organisational protocols.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="V77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Viewpoint Elicitation</t>
+          <t>Verbal Communication</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Talks with others, listens actively and asks questions to draw out their views.</t>
+          <t>Engages in verbal idea exchange, actively listening and questioning to draw out others’ views.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="S78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="V78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Platform Installation</t>
+          <t>Set Up Blockchain Platform</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Installs and configures blockchain platform components according to approved design specifications.</t>
+          <t>Installs and configures blockchain platform components in line with approved design specifications.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8328,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="V79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Anomaly Detection</t>
+          <t>Blockchain Problem Solving</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="S80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Requirements Definition</t>
+          <t>Blockchain Requirements Definition</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Defines blockchain objectives and requirements that align with organisational needs in hybrid environments.</t>
+          <t>Defines blockchain objectives and requirements aligned with organisational needs in hybrid environments.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8514,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="V81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mechanism Configuration</t>
+          <t>Implement Consensus Mechanism</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Configure and deploy system components to implement consensus mechanisms.</t>
+          <t>Implements consensus mechanisms by configuring and deploying required system components.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="V82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Design Documentation Preparation</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Creates detailed design documentation that meets organisational requirements and supports project delivery.</t>
+          <t>Produces detailed design documentation aligned with organisational requirements to support project delivery.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8700,7 +8700,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="V83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Documentation Submission and Feedback Management</t>
+          <t>Submit Documentation and Manage Feedback</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Submit documentation for review, seek feedback, and incorporate approved amendments.</t>
+          <t>Submits documentation for review, seeks feedback and incorporates approved amendments.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8793,7 +8793,7 @@
         <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="V84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Design integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
+          <t>Designs integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="S85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="V85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Schedule Development</t>
+          <t>Document Maintenance Schedule</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Creates and records maintenance schedules that match equipment needs and timelines.</t>
+          <t>Develops and records maintenance schedules aligned with equipment requirements and timelines.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8979,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="V86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing</t>
+          <t>Determine and Conduct Maintenance Tests</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9072,7 +9072,7 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Security Platform Selection</t>
+          <t>Blockchain Security Platform Selection</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Contract Deployment</t>
+          <t>Smart Contract Execution</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Deploys and manages smart contracts on approved blockchain platforms according to solution specifications.</t>
+          <t>Deploys and manages smart contracts on approved blockchain platforms in line with solution specifications.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="S89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="V89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Diagnoses and resolves blockchain solution issues, then optimises performance for scalable deployment.</t>
+          <t>Diagnoses and resolves blockchain solution issues and optimises performance for scalable deployment.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9348,10 +9348,10 @@
         </is>
       </c>
       <c r="S90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="V90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Performance Evaluation</t>
+          <t>Solution Performance Testing</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="S91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Requirements Communication</t>
+          <t>Stakeholder Requirements Oral Communication</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9537,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Use‑Case Identification</t>
+          <t>Identify Organisational Use Case</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9630,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Log Ingestion</t>
+          <t>Analytic Platform Data Ingestion, Analysis, and Interpretation</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ingest data logs into analytics platforms to support monitoring and analysis.</t>
+          <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9734,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="V94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Requirement Identification</t>
+          <t>Identify Compliance Requirements for Threat Data Gathering</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Identifies relevant legislation and internal policies that govern the collection, analysis and use of threat data.</t>
+          <t>Identifies relevant legislation and internal policies governing the collection, analysis and use of threat data.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9842,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="V95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Discrepancy Identification</t>
+          <t>Threat Data Discrepancy Detection</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9946,7 +9946,7 @@
         <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Data Set Creation</t>
+          <t>Threat Data Collection and Creation</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Compiles alerts, logs and event reports into structured datasets following organisational policies.</t>
+          <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -10050,7 +10050,7 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         </is>
       </c>
       <c r="V97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>False Positive and Negative Identification</t>
+          <t>False Positive Detection and Analysis</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Reviews test results to spot and fix false positives and false negatives.</t>
+          <t>Reviews test results to identify and correct false positives and false negatives.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10158,7 +10158,7 @@
         <v>1</v>
       </c>
       <c r="T98" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         </is>
       </c>
       <c r="V98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Data Report Documentation</t>
+          <t>Document Findings and Recommendations</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Produces formal investigation reports that outline findings and recommendations following organisational procedures.</t>
+          <t>Produces formal investigation reports outlining findings and recommendations in accordance with organisational procedures.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10258,7 +10258,7 @@
         <v>1</v>
       </c>
       <c r="T99" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="V99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Strategy Recommendation</t>
+          <t>Threat Mitigation Strategy Recommendation</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="S100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Likelihood Assessment</t>
+          <t>Risk Likelihood and Impact Assessment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Evaluates threats by judging likelihood and impact, then prioritises risk mitigation actions.</t>
+          <t>Assesses threats by evaluating likelihood and impact to prioritise risk mitigation actions.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10470,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="T101" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="V101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Equipment Identification</t>
+          <t>Identify Security Equipment and Data Sources</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10571,10 +10571,10 @@
         </is>
       </c>
       <c r="S102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Log Ingestion</t>
+          <t>Security Log Ingestion</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10678,7 +10678,7 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Findings Communication</t>
+          <t>Threat Data Discussion and Review</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10782,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="T104" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Data Gathering</t>
+          <t>Threat Data Collection</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collect and structure alerts, logs and event data according to organisational data policies.</t>
+          <t>Collects and structures alerts, logs and event data in accordance with organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="S105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="V105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Anomaly Detection and Resolution</t>
+          <t>Anomaly Detection, Response, and Protection Strategy</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Monitors operational data, detects contextual anomalies, and resolves deviations promptly.</t>
+          <t>Monitors operational data to detect contextual anomalies and resolves deviations in a timely manner.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10979,7 +10979,7 @@
         <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="V106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Protection Strategy and Asset Management Implementation</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11072,7 +11072,7 @@
         <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Research</t>
+          <t>Critical Infrastructure Protection Research</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Conducts research on critical infrastructure to support protection planning and documentation requirements.</t>
+          <t>Conducts critical infrastructure research to support protection planning and documentation requirements.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -11162,10 +11162,10 @@
         </is>
       </c>
       <c r="S108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         </is>
       </c>
       <c r="V108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Backup Execution</t>
+          <t>Critical Infrastructure Data Backup</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Runs scheduled data backups according to organisational policies and procedures.</t>
+          <t>Executes scheduled data backups in line with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -11255,10 +11255,10 @@
         </is>
       </c>
       <c r="S109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         </is>
       </c>
       <c r="V109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Security Implementation</t>
+          <t>Secure Devices per Protection Strategy</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Implements device security controls according to protection plans and technical specifications.</t>
+          <t>Implements device security controls in accordance with protection plans and technical specifications.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -11348,10 +11348,10 @@
         </is>
       </c>
       <c r="S110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         </is>
       </c>
       <c r="V110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Feedback Handling</t>
+          <t>Feedback Seeking and Response Management</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Submit protection plans for review and incorporate stakeholder feedback to improve outcomes.</t>
+          <t>Submits protection plans for review and incorporates stakeholder feedback to improve outcomes.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -11444,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         </is>
       </c>
       <c r="V111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Segmentation Implementation</t>
+          <t>Network Segmentation</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation to isolate security zones according to approved protection plans.</t>
+          <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="V112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Planning and Review</t>
+          <t>Critical Infrastructure Protection Strategy Development</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Creates staged operational plans and reviews priorities and performance regularly during execution.</t>
+          <t>Develops staged operational plans and regularly reviews priorities and performance during execution.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -11630,7 +11630,7 @@
         <v>1</v>
       </c>
       <c r="T113" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="V113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Evaluates current critical infrastructure protection plans, identifies gaps, and recommends improvements.</t>
+          <t>Evaluates current critical infrastructure protection plans to identify gaps and recommend improvements.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11723,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="T114" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="V114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Protection Planning</t>
+          <t>Critical Infrastructure Protection Plan</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Develops and records critical infrastructure protection plans that align with organisational policies and procedures.</t>
+          <t>Develops and records critical infrastructure protection plans aligned with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11816,7 +11816,7 @@
         <v>1</v>
       </c>
       <c r="T115" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="V115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Plan Testing</t>
+          <t>Protection Deployment Testing</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Validates protection plans by testing safeguards against organisational requirements.</t>
+          <t>Conducts protection plan testing to validate safeguards in line with organisational requirements.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11909,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="T116" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="V116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Results Analysis and Reporting</t>
+          <t>Results Analysis Reporting</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11999,10 +11999,10 @@
         </is>
       </c>
       <c r="S117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Critical Infrastructure Risk Assessment</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12095,7 +12095,7 @@
         <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Patch Installation</t>
+          <t>Apply Software Patches for Critical Infrastructure Protection</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Installs and configures software updates according to documented technical specifications.</t>
+          <t>Installs and configures software updates in line with documented technical specifications.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -12188,7 +12188,7 @@
         <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="V119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Technical Documentation Preparation</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Creates workplace documentation that follows required structure, layout and organisational language standards.</t>
+          <t>Produces workplace documentation using mandated structure, layout and organisational language standards.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="S120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="V120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data Classification Identification</t>
+          <t>Establish Data Types for Security Architecture</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="S121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T121" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Feedback Submission</t>
+          <t>Manage Feedback Responses</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Submit required documentation promptly to obtain initial stakeholder feedback.</t>
+          <t>Submits required documentation promptly to obtain initial stakeholder feedback.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -12493,7 +12493,7 @@
         <v>1</v>
       </c>
       <c r="T122" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="V122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W122" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Architecture Methodology Research</t>
+          <t>Security Architecture Design Methodology</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Anomaly Identification</t>
+          <t>Contextual Analysis for Security Architecture Design</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Uses contextual awareness to spot security anomalies and deviations from normal operating patterns.</t>
+          <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -12701,7 +12701,7 @@
         <v>1</v>
       </c>
       <c r="T124" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="V124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Architecture Documentation</t>
+          <t>Security Architecture Documentation and Confirmation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Document and validate security architecture findings with relevant personnel.</t>
+          <t>Documents and validates security architecture findings with relevant personnel.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -12802,10 +12802,10 @@
         </is>
       </c>
       <c r="S125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         </is>
       </c>
       <c r="V125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W125" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Architecture Presentation</t>
+          <t>Security Architecture Presentation Documentation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="S126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Design Validation</t>
+          <t>Validate Security Design Using Standard Methodologies</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -13010,10 +13010,10 @@
         </is>
       </c>
       <c r="S127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Level Assessment</t>
+          <t>Determine Required Security Level</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13121,7 +13121,7 @@
         <v>1</v>
       </c>
       <c r="T128" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Initiative Planning</t>
+          <t>Security Project Planning</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Creates staged operational plans for security initiatives and reviews progress during delivery.</t>
+          <t>Develops staged operational plans for security initiatives and reviews progress during delivery.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -13226,10 +13226,10 @@
         </is>
       </c>
       <c r="S129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         </is>
       </c>
       <c r="V129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W129" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Requirements Analysis</t>
+          <t>Security Requirements Analysis</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Architecture Design</t>
+          <t>Security Solution Design</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Designs and documents security solutions that align with organisational standards and requirements.</t>
+          <t>Designs and documents security solutions aligned with organisational standards and requirements.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="S131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
         <v>0.97</v>
@@ -13445,7 +13445,7 @@
         </is>
       </c>
       <c r="V131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W131" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Security Architecture Documentation Preparation</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Creates detailed technical documentation that outlines findings and proposed solutions.</t>
+          <t>Produces detailed technical documentation outlining findings and proposed solutions.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -13542,10 +13542,10 @@
         </is>
       </c>
       <c r="S132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T132" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="V132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W132" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Specification Interpretation</t>
+          <t>Documentation Interpretation</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements before work starts.</t>
+          <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements prior to work commencement.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -13649,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="T133" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="V133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Strategic Decision Making</t>
+          <t>Autonomous Incident Response Planning</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Makes independent strategic decisions that align actions with organisational objectives and improve performance.</t>
+          <t>Makes independent strategic decisions to align actions with organisational objectives and improve performance.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -13758,7 +13758,7 @@
         <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         </is>
       </c>
       <c r="V134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W134" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Evidence Collection Procedure Development</t>
+          <t>Develop Forensic Evidence Collection Procedure</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -13863,7 +13863,7 @@
         <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Incident Report Preparation</t>
+          <t>Incident Response Documentation</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Prepares detailed incident reports that document response actions and meet task requirements.</t>
+          <t>Prepares detailed incident reports documenting response actions against task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="V136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W136" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Incident Response Planning Development</t>
+          <t>Incident Response Planning</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Develop and record incident response plans that meet organisational requirements.</t>
+          <t>Develops and records incident response plans aligned with organisational requirements.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -14171,10 +14171,10 @@
         </is>
       </c>
       <c r="S138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="V138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W138" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Incident Response Team Coordination</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Document incident response team roles and services to support coordinated response.</t>
+          <t>Documents incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -14275,7 +14275,7 @@
         <v>1</v>
       </c>
       <c r="T139" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         </is>
       </c>
       <c r="V139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W139" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Incident Response Design</t>
+          <t>Incident Response Plan Development, Implementation, and Evaluation</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Designs and runs red‑team exercises and incident response simulations, including staffing and training plans.</t>
+          <t>Designs and conducts red‑team exercises and incident response simulations, including staffing and training plans.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -14380,7 +14380,7 @@
         <v>1</v>
       </c>
       <c r="T140" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         </is>
       </c>
       <c r="V140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W140" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Evaluates how well incident response communications work with internal and external stakeholders.</t>
+          <t>Evaluates the effectiveness of incident response communications across internal and external stakeholders.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -14485,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="V141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W141" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Assessment Data Interpretation</t>
+          <t>Interpret, Analyze, and Document System Data</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Interprets and records numerical and technical system data to support risk assessment.</t>
+          <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -14602,7 +14602,7 @@
         </is>
       </c>
       <c r="V142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W142" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Response Execution</t>
+          <t>Incident Response Planning and Execution</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Executes incident response actions following approved response plans.</t>
+          <t>Executes incident response actions in accordance with approved incident response plans.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -14703,7 +14703,7 @@
         <v>1</v>
       </c>
       <c r="T143" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         </is>
       </c>
       <c r="V143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W143" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Policy Development</t>
+          <t>Incident Response Plan Development</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Develops and documents incident management policies that meet organisational specifications.</t>
+          <t>Develops and documents incident management policies aligned with organisational specifications.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -14812,7 +14812,7 @@
         <v>1</v>
       </c>
       <c r="T144" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="V144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W144" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Data Analysis and Documentation</t>
+          <t>Develop, Implement, and Evaluate Incident Response Plan</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -14921,7 +14921,7 @@
         <v>1</v>
       </c>
       <c r="T145" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Continuity Assessment</t>
+          <t>Business Continuity Evaluation</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Assesses system impacts on business continuity, identifies risks and mitigation strategies.</t>
+          <t>Assesses system impacts on business continuity to identify risks and mitigation strategies.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -15023,10 +15023,10 @@
         </is>
       </c>
       <c r="S146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="V146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W146" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Compliance Planning</t>
+          <t>Disaster Recovery and Business Continuity Planning</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Designs and implements compliance strategies that align organisational processes with regulatory requirements.</t>
+          <t>Designs and implements compliance strategies to align organisational processes with regulatory requirements.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="V147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W147" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Contingency Planning</t>
+          <t>Contingency Planning and Disaster Recovery</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15240,7 +15240,7 @@
         <v>1</v>
       </c>
       <c r="T148" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Constraint Evaluation</t>
+          <t>Cost Constraint Evaluation</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15345,7 +15345,7 @@
         <v>1</v>
       </c>
       <c r="T149" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Recovery Planning</t>
+          <t>Disaster Recovery Planning</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Develop comprehensive disaster recovery plans that detail procedures, resources and recovery timeframes.</t>
+          <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -15450,7 +15450,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="V150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W150" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Standards Evaluation</t>
+          <t>Industry Standards Review and Risk Safeguard Assessment</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15555,7 +15555,7 @@
         <v>1</v>
       </c>
       <c r="T151" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Disaster Recovery Data Analysis</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -15657,10 +15657,10 @@
         </is>
       </c>
       <c r="S152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Designs and implements strategies that prevent incidents and aid recovery, strengthening system resilience.</t>
+          <t>Designs and implements prevention and recovery strategies to strengthen system resilience.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -15773,7 +15773,7 @@
         </is>
       </c>
       <c r="V153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W153" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Recovery Planning Evaluation</t>
+          <t>Disaster Recovery and Business Continuity Evaluation</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Collects and analyses data, incorporates feedback, and refines plans and processes.</t>
+          <t>Collects and analyses data, incorporates feedback and refines plans and processes.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -15874,7 +15874,7 @@
         <v>1</v>
       </c>
       <c r="T154" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         </is>
       </c>
       <c r="V154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W154" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Risk Assessment and Disaster Recovery Planning</t>
+          <t>Disaster Recovery and Risk Analysis</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conduct comprehensive risk assessments and develop disaster recovery and contingency solutions.</t>
+          <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -15979,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="T155" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         </is>
       </c>
       <c r="V155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W155" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Feedback Management</t>
+          <t>Stakeholder Communication and Feedback Management</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Engages stakeholders by submitting documents on time, collecting feedback, and responding promptly.</t>
+          <t>Engages stakeholders through timely document submission, feedback collection and response.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -16084,7 +16084,7 @@
         <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         </is>
       </c>
       <c r="V156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W156" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>1</v>
       </c>
       <c r="T157" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Team Collaboration</t>
+          <t>Effective Team Collaboration</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Works with team members using communication tools and strategies to maintain effective relationships.</t>
+          <t>Collaborates with team members using communication tools and strategies to maintain effective working relationships.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -16291,10 +16291,10 @@
         </is>
       </c>
       <c r="S158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T158" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         </is>
       </c>
       <c r="V158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W158" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Recovery Documentation Preparation</t>
+          <t>Evaluation and Strategy Documentation</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Prepares evaluation and strategy documents that outline findings and recommendations for stakeholders.</t>
+          <t>Prepares evaluation and strategy documents outlining findings and recommendations for stakeholders.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -16399,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="T159" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="V159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W159" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Threat Assessment</t>
+          <t>Threat Assessment and Evaluation</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Identifies system vulnerabilities by structuring threat identification and analysis to support mitigation planning.</t>
+          <t>Assesses system vulnerabilities through structured threat identification and analysis to support mitigation planning.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -16504,7 +16504,7 @@
         <v>1</v>
       </c>
       <c r="T160" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         </is>
       </c>
       <c r="V160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W160" t="inlineStr">
         <is>

--- a/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Active Idea Listening</t>
+          <t>Idea Elicitation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Elicits others’ views and integrates feedback to refine ideas during collaborative discussions.</t>
+          <t>Gather others’ views and combine feedback to improve ideas in group discussions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>communication, empathy, feedback, stakeholder engagement, interpersonal skills</t>
+          <t>["communication", "empathy", "feedback", "stakeholder engagement", "interpersonal skills"]</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="X2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -696,12 +696,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Compares project concepts against industry best‑practice examples of similar products to identify improvement opportunities.</t>
+          <t>Compares project concepts with industry best‑practice examples of similar products to identify improvement opportunities.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
+          <t>["benchmarking", "best practice", "performance metrics", "competitive analysis", "industry standards"]</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="X3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -788,7 +788,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Concept Generation and Development</t>
+          <t>Idea Generation and Presentation</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Generates diverse solutions by leading focused brainstorming sessions to address identified issues.</t>
+          <t>Leads focused brainstorming sessions to create diverse solutions for identified issues.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ideation, creative problem solving, mind mapping, group facilitation, innovation techniques</t>
+          <t>["ideation", "creative problem solving", "mind mapping", "group facilitation", "innovation techniques"]</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="X4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -900,7 +900,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Concept Development</t>
+          <t>Concept Generation and Refinement</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Applies systematic analytical methods to collect and assess concepts in complex, non‑routine scenarios.</t>
+          <t>Uses systematic analytical methods to collect and assess concepts in complex, non‑routine scenarios.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>analytical methodology, systematic concept evaluation, ideation processes, feasibility analysis, design thinking</t>
+          <t>["analytical methodology", "systematic concept evaluation", "ideation processes", "feasibility analysis", "design thinking"]</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="V5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
+          <t>Uses creative thinking techniques to develop innovative solutions for workplace challenges.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
+          <t>["ideation", "innovation", "brainstorming", "design thinking", "problem solving"]</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Document Feedback According to Requirements</t>
+          <t>Compiled Feedback Documentation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Records and formats feedback in line with organisational standards to ensure consistent documentation.</t>
+          <t>Records and formats feedback to meet organisational standards, ensuring consistent documentation.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>record‑keeping, compliance, audit trail, quality assurance, organisational standards</t>
+          <t>["record\u2011keeping", "compliance", "audit trail", "quality assurance", "organisational standards"]</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="X7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Idea Viability Evaluation</t>
+          <t>Idea Viability Assessment</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Assesses ideas by systematically comparing them against identified viability factors.</t>
+          <t>Systematically compare ideas with identified viability factors to assess them.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>feasibility analysis, risk assessment, criteria weighting, business case evaluation, market viability</t>
+          <t>["feasibility analysis", "risk assessment", "criteria weighting", "business case evaluation", "market viability"]</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1281,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="V8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="X8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to identify and select consultation issues for focused analysis.</t>
+          <t>Works with relevant staff to identify and choose consultation issues for focused analysis.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>stakeholder engagement, problem identification, needs assessment, consultation processes, decision‑making</t>
+          <t>["stakeholder engagement", "problem identification", "needs assessment", "consultation processes", "decision\u2011making"]</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="V9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="X9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Proposal Development</t>
+          <t>Proposal Development and Planning</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stakeholder communication, business case development, grant and RFP responses, technical documentation, persuasive writing</t>
+          <t>["stakeholder communication", "business case development", "grant and RFP responses", "technical documentation", "persuasive writing"]</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1497,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="X10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Research Information on Solutions</t>
+          <t>Solution Research Information</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Gathers and evaluates relevant data to identify viable solutions to the identified issue.</t>
+          <t>Collects and assesses data to find workable solutions for the identified problem.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
+          <t>["literature review", "data collection", "search strategies", "online databases", "evidence\u2011based analysis"]</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="V11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="X11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Selects appropriate solution formats and delivers tailored presentations to stakeholders.</t>
+          <t>Chooses suitable solution formats and delivers customised presentations to stakeholders.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
+          <t>["stakeholder communication", "visual presentation tools", "solution pitching", "format selection", "business briefings"]</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1701,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="X12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Solution Refinement and Finalisation</t>
+          <t>Solution Refinement</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>requirements analysis, design optimisation, prototype testing, continuous improvement, validation feedback</t>
+          <t>["requirements analysis", "design optimisation", "prototype testing", "continuous improvement", "validation feedback"]</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="X13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Evaluates alternative solutions to a business problem, identifying constraints to determine feasible options.</t>
+          <t>Evaluates alternative solutions to a business problem, identifies constraints, and determines feasible options.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
+          <t>["feasibility analysis", "constraint identification", "business issue evaluation", "risk assessment", "decision matrices"]</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="V14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="X14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stakeholder Idea Feedback Solicitation</t>
+          <t>Stakeholder Feedback Solicitation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback collection, surveys, interviews, communication</t>
+          <t>["stakeholder engagement", "feedback collection", "surveys", "interviews", "communication"]</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="S15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="X15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Team Solution Development</t>
+          <t>Team Solution Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Guides group discussions, encourages participation and coordinates tasks to achieve shared outcomes.</t>
+          <t>Leads group discussions, encourages participation, and coordinates tasks to achieve shared outcomes.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>group dynamics, collaboration tools, meeting facilitation, conflict resolution, consensus building</t>
+          <t>["group dynamics", "collaboration tools", "meeting facilitation", "conflict resolution", "consensus building"]</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="V16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="X16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cyber Security Awareness Program Development</t>
+          <t>Cyber Security Awareness Program</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Designs, implements and updates organisation‑wide cyber security awareness programs in line with best practice.</t>
+          <t>Designs, implements and updates organisation‑wide cyber security awareness programmes following best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>cyber security, security awareness training, risk management, phishing simulations, compliance governance</t>
+          <t>["cyber security", "security awareness training", "risk management", "phishing simulations", "compliance governance"]</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="V17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="X17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Clear, Industry‑Specific Cyber‑Security Terminology</t>
+          <t>Clear Technical Writing</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
+          <t>["cyber security terminology", "technical documentation", "information security policies", "industry standards (ISO 27001, NIST)", "risk assessment reporting"]</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="S18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="X18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Current Awareness Assessment</t>
+          <t>Cyber Security Awareness Assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Assesses cyber security awareness within the work area through surveys and interviews to establish baseline levels.</t>
+          <t>Conduct surveys and interviews to assess cyber security awareness in the work area and establish baseline levels.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>cyber security, risk awareness, security posture, threat intelligence, security metrics</t>
+          <t>["cyber security awareness", "risk awareness", "security posture", "threat intelligence", "security metrics"]</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="S19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0.97</v>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="V19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="X19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Communicate Improvement Outcomes</t>
+          <t>Improvement Communication</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Communicates review results and cyber security improvement needs in accordance with organisational policies and procedures.</t>
+          <t>Communicates review results and cyber security improvement needs following organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
+          <t>["cyber security", "policy compliance", "risk communication", "security standards", "stakeholder reporting"]</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="S20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="V20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="X20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Insight Presentation</t>
+          <t>Insight Presentation Delivery</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
+          <t>Delivers concise insight presentations from reviews and training to designated personnel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>stakeholder communication, knowledge transfer, visual storytelling, training briefings, presentation tools</t>
+          <t>["stakeholder communication", "knowledge transfer", "visual storytelling", "training briefings", "presentation tools"]</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="S21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="V21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="X21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Australian Privacy Legislation Awareness</t>
+          <t>Legislation Interpretation</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
+          <t>["Notifiable Data Breach", "Australian Privacy Act", "data protection compliance", "privacy law interpretation", "regulatory risk assessment"]</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="S22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="X22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Outcome Documentation of Review and Improvements</t>
+          <t>Outcome Documentation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Prepares detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
+          <t>Prepares detailed outcome reports that outline improvement recommendations for relevant personnel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>reporting, review outcomes, improvement recommendations, stakeholder communication, record‑keeping</t>
+          <t>["reporting", "review outcomes", "improvement recommendations", "stakeholder communication", "record\u2011keeping"]</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="S23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="V23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="X23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cyber Security Policy Development</t>
+          <t>Cybersecurity Policy Contribution</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Drafts cyber security policies and procedures and disseminates them to relevant staff.</t>
+          <t>Drafts cyber security policies and procedures and shares them with relevant staff.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>cyber security governance, policy development, risk management, compliance frameworks, stakeholder communication</t>
+          <t>["cyber security governance", "policy development", "risk management", "compliance frameworks", "stakeholder communication"]</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="V24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="X24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Conducts systematic reviews of cyber security practices to ensure alignment with organisational policies and procedures.</t>
+          <t>Systematically reviews cyber security practices to ensure they align with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>cyber security, policy compliance, risk assessment, security governance, audit controls</t>
+          <t>["cyber security", "policy compliance", "risk assessment", "security governance", "audit controls"]</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="V25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="X25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cyber Security Documentation Management</t>
+          <t>Cyber Security Record Keeping</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maintains up‑to‑date cyber security protection records by organising and documenting relevant data.</t>
+          <t>Keeps cyber security protection records current by organising and documenting relevant data.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>cyber security documentation, information security records, compliance logging, data governance, audit trail management</t>
+          <t>["cyber security documentation", "information security records", "compliance logging", "data governance", "audit trail management"]</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="V26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="X26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
+          <t>["stakeholder engagement", "consultation workshops", "decision support", "needs analysis", "facilitation"]</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="X27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Collaborative Cyber Security Awareness</t>
+          <t>Cyber Security Collaboration</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Collaborates with interdisciplinary teams to design and implement cyber security measures.</t>
+          <t>Works with interdisciplinary teams to design and implement cyber security measures.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, collaboration tools</t>
+          <t>["interdisciplinary teamwork", "cyber security coordination", "cross\u2011functional communication", "stakeholder engagement", "collaboration tools"]</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -3389,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="V28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="X28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Technology Platform Utilization for Cybersecurity</t>
+          <t>Technology Platform Utilisation</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>cyber security, security platforms, SIEM, threat monitoring, information security</t>
+          <t>["cyber security", "security platforms", "SIEM", "threat monitoring", "information security"]</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="S29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0.92</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="X29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cyber Threat Trend Review</t>
+          <t>Threat Trend Analysis</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
+          <t>["cyber security", "threat intelligence", "trend monitoring", "vulnerability assessment", "security analytics"]</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="S30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="X30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cyber Security Awareness Training Coordination</t>
+          <t>Training Coordination and Record Keeping</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coordinates training sessions and information updates by scheduling, delivering and recording activities.</t>
+          <t>Coordinates training sessions and updates information by scheduling, delivering and recording activities.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>training schedules, learning management systems, record management, information updates, training logistics</t>
+          <t>["training schedules", "learning management systems", "record management", "information updates", "training logistics"]</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -3713,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="V31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="X31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3740,14 +3740,18 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Evidence Provision and Skill Naming</t>
+          <t>Unnamed Skill</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -3784,14 +3788,18 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Evidence Provision and Skill Naming</t>
+          <t>NaN Value</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -3809,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="b">
@@ -3836,7 +3844,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Anti-Malware Deployment</t>
+          <t>Anti‑Malware Deployment</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3861,7 +3869,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>cyber security, endpoint protection, malware scanning, signature updates, security hygiene</t>
+          <t>["cyber security", "endpoint protection", "malware scanning", "signature updates", "security hygiene"]</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -3903,10 +3911,10 @@
         </is>
       </c>
       <c r="S34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3922,7 +3930,7 @@
         </is>
       </c>
       <c r="X34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3941,7 +3949,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Digital Device Security Review</t>
+          <t>Breach Impact Assessment</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3966,7 +3974,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>risk assessment, incident tracking, business impact analysis, compliance reporting, security metrics</t>
+          <t>["risk assessment", "incident tracking", "business impact analysis", "compliance reporting", "security metrics"]</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -4027,7 +4035,7 @@
         </is>
       </c>
       <c r="X35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -4046,7 +4054,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Initial Configuration and Update</t>
+          <t>Device Security Configuration</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4066,12 +4074,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Performs initial device set‑up by updating firmware and configuring settings on new devices.</t>
+          <t>Sets up new devices by updating firmware and configuring settings.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>device provisioning, firmware updates, configuration management, hardware initialisation, system onboarding</t>
+          <t>["device provisioning", "firmware updates", "configuration management", "hardware initialisation", "system onboarding"]</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -4120,7 +4128,7 @@
         </is>
       </c>
       <c r="V36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4128,7 +4136,7 @@
         </is>
       </c>
       <c r="X36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4147,7 +4155,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Implement Device Encryption and Security Measures</t>
+          <t>Device Encryption Implementation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4167,12 +4175,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Implements device encryption in accordance with prescribed procedures to secure hardware.</t>
+          <t>Implements device encryption following prescribed procedures to secure hardware.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>encryption, device security, endpoint encryption, mobile device management, cryptography</t>
+          <t>["encryption", "device security", "endpoint encryption", "mobile device management", "cryptography"]</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -4210,7 +4218,7 @@
         </is>
       </c>
       <c r="S37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0.92</v>
@@ -4221,7 +4229,7 @@
         </is>
       </c>
       <c r="V37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4229,7 +4237,7 @@
         </is>
       </c>
       <c r="X37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4248,7 +4256,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Device Register Management</t>
+          <t>Device Inventory Register</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4273,7 +4281,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IT asset tracking, hardware registers, network inventories, CMDB, asset management software</t>
+          <t>["IT asset tracking", "hardware registers", "network inventories", "CMDB", "asset management software"]</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -4326,7 +4334,7 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -4342,7 +4350,7 @@
         </is>
       </c>
       <c r="X38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4386,7 +4394,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
+          <t>["benchmarking", "performance metrics", "best\u2011practice assessment", "process improvement", "effectiveness evaluation"]</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -4435,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -4451,7 +4459,7 @@
         </is>
       </c>
       <c r="X39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4470,7 +4478,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Create Strong Passwords</t>
+          <t>Strong Password Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4490,12 +4498,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Generates robust, unique passwords for personal and work accounts in line with approved complexity criteria.</t>
+          <t>Creates strong, unique passwords for personal and work accounts that meet approved complexity rules.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>authentication, password complexity, entropy, cyber security, password managers</t>
+          <t>["authentication", "password complexity", "entropy", "cyber security", "password managers"]</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -4536,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -4544,7 +4552,7 @@
         </is>
       </c>
       <c r="V40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4552,7 +4560,7 @@
         </is>
       </c>
       <c r="X40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -4571,7 +4579,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Physical Security Planning for Digital Devices</t>
+          <t>Digital Device Security Planning</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4591,12 +4599,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Develops comprehensive physical security plans and disseminates them organisation‑wide to ensure coordinated protection.</t>
+          <t>Creates physical security plans and shares them across the organisation to ensure coordinated protection.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
+          <t>["risk assessment", "access control systems", "security policy development", "facility protection", "stakeholder communication"]</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -4653,7 +4661,7 @@
         </is>
       </c>
       <c r="V41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4661,7 +4669,7 @@
         </is>
       </c>
       <c r="X41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -4680,7 +4688,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Device Risk Categorisation</t>
+          <t>Device Risk Level Categorisation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4700,12 +4708,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
+          <t>Evaluates how sensitive device data are and assigns a risk category for security management.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>risk assessment, information sensitivity, device classification, cyber security, risk matrices</t>
+          <t>["risk assessment", "information sensitivity", "device classification", "cyber security", "risk matrices"]</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -4750,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -4758,7 +4766,7 @@
         </is>
       </c>
       <c r="V42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4766,7 +4774,7 @@
         </is>
       </c>
       <c r="X42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -4785,7 +4793,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physical Security Plan Development and Communication</t>
+          <t>Physical Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4805,12 +4813,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Delivers organisation‑wide briefings on physical security plans to support understanding and compliance.</t>
+          <t>Provides organisation‑wide briefings on physical security plans to improve understanding and compliance.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>physical security, risk assessment, security policy, stakeholder communication, access control</t>
+          <t>["physical security", "risk assessment", "security policy", "stakeholder communication", "access control"]</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -4859,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -4867,7 +4875,7 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -4875,7 +4883,7 @@
         </is>
       </c>
       <c r="X43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4914,12 +4922,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Selects appropriate security protocols for each device to mitigate identified risk levels.</t>
+          <t>Choose suitable security protocols for each device to reduce identified risk levels.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
+          <t>["risk assessment", "encryption standards", "device hardening", "cyber security governance", "protocol compliance"]</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -4968,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -4976,7 +4984,7 @@
         </is>
       </c>
       <c r="V44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4984,7 +4992,7 @@
         </is>
       </c>
       <c r="X44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -5023,12 +5031,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Advises the organisation by evaluating options and recommending optimal security strategies.</t>
+          <t>Provides advice to the organisation by evaluating options and recommending the best security strategies.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
+          <t>["cyber security governance", "risk assessment", "security frameworks", "threat modelling", "ISO 27001"]</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -5077,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -5085,7 +5093,7 @@
         </is>
       </c>
       <c r="V45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5093,7 +5101,7 @@
         </is>
       </c>
       <c r="X45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -5112,7 +5120,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Digital Security Trend Monitoring</t>
+          <t>Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5132,12 +5140,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Monitors emerging digital security developments to inform risk assessments and protective measures.</t>
+          <t>Monitors new digital security developments to inform risk assessments and protective measures.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>cyber security, threat intelligence, vulnerability tracking, security intelligence feeds, digital risk monitoring</t>
+          <t>["cyber security", "threat intelligence", "vulnerability tracking", "security intelligence feeds", "digital risk monitoring"]</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -5179,7 +5187,7 @@
         </is>
       </c>
       <c r="S46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0.92</v>
@@ -5190,7 +5198,7 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5198,7 +5206,7 @@
         </is>
       </c>
       <c r="X46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -5217,7 +5225,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Device Software Patch Application</t>
+          <t>Software Patch Application</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5242,7 +5250,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>patch management, software updates, endpoint management, mobile device management, security patches</t>
+          <t>["patch management", "software updates", "endpoint management", "mobile device management", "security patches"]</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -5288,10 +5296,10 @@
         </is>
       </c>
       <c r="S47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -5307,7 +5315,7 @@
         </is>
       </c>
       <c r="X47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -5326,7 +5334,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Enable Two-Factor Authentication</t>
+          <t>Two‑Factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5351,7 +5359,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>multi‑factor authentication, MFA, OTP, access control, cyber security</t>
+          <t>["multi\u2011factor authentication", "MFA", "OTP", "access control", "cyber security"]</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -5397,7 +5405,7 @@
         </is>
       </c>
       <c r="S48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
         <v>0.97</v>
@@ -5416,7 +5424,7 @@
         </is>
       </c>
       <c r="X48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5435,7 +5443,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Strategic Action Plan Development</t>
+          <t>Strategic Action Plan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5455,12 +5463,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Develops detailed action plans aligned with policies, prioritising tasks and scheduling implementation.</t>
+          <t>Creates detailed action plans that match policies, set priorities, and schedule implementation tasks.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>project scheduling, prioritisation, policy compliance, change management, implementation planning</t>
+          <t>["project scheduling", "prioritisation", "policy compliance", "change management", "implementation planning"]</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -5492,7 +5500,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -5500,7 +5508,7 @@
         </is>
       </c>
       <c r="V49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5508,7 +5516,7 @@
         </is>
       </c>
       <c r="X49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -5547,12 +5555,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
+          <t>Ranks proposed changes to clarify improvement opportunities and guide implementation scheduling.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
+          <t>["change management", "prioritisation", "opportunity assessment", "implementation scheduling", "project planning"]</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -5596,7 +5604,7 @@
         </is>
       </c>
       <c r="V50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5604,7 +5612,7 @@
         </is>
       </c>
       <c r="X50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -5623,7 +5631,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Digital Technology Utilization</t>
+          <t>Digital Technology Utilisation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5648,7 +5656,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data management, digital collaboration tools, emerging technologies, cloud computing, data visualisation</t>
+          <t>["data management", "digital collaboration tools", "emerging technologies", "cloud computing", "data visualisation"]</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -5696,7 +5704,7 @@
         </is>
       </c>
       <c r="X51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -5715,7 +5723,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Document Evaluation and Feedback for Strategic Planning</t>
+          <t>Evaluation Process Documentation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5740,7 +5748,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>technical writing, document review, quality assurance, reporting standards, document control</t>
+          <t>["technical writing", "document review", "quality assurance", "reporting standards", "document control"]</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -5772,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -5788,7 +5796,7 @@
         </is>
       </c>
       <c r="X52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -5807,7 +5815,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Analysis and Improvement</t>
+          <t>ICT Gap Analysis</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5827,12 +5835,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
+          <t>Compares strategic objectives with current ICT capability in hybrid environments, identifies gaps, and proposes improvements.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>gap analysis, strategic alignment, technology roadmaps, ICT governance, digital transformation</t>
+          <t>["gap analysis", "strategic alignment", "technology roadmaps", "ICT governance", "digital transformation"]</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -5884,7 +5892,7 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5892,7 +5900,7 @@
         </is>
       </c>
       <c r="X53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -5911,7 +5919,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Strategic Impact Assessment</t>
+          <t>Impact Evaluation</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5931,12 +5939,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
+          <t>Evaluates proposed ICT system changes in hybrid environments to ensure they align with organisational strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>impact assessment, ICT systems, strategic alignment, change management, performance metrics</t>
+          <t>["impact assessment", "ICT systems", "strategic alignment", "change management", "performance metrics"]</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -5981,10 +5989,10 @@
         </is>
       </c>
       <c r="S54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -5992,7 +6000,7 @@
         </is>
       </c>
       <c r="V54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6000,7 +6008,7 @@
         </is>
       </c>
       <c r="X54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -6019,7 +6027,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Innovative Idea Investigation</t>
+          <t>Innovative Idea Evaluation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6039,12 +6047,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Researches and tests innovative ideas, applying findings to refine work practices and processes.</t>
+          <t>Researches and tests new ideas, then applies findings to improve work practices and processes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>continuous improvement, process optimisation, ideation techniques, creative problem solving, innovation management</t>
+          <t>["continuous improvement", "process optimisation", "ideation techniques", "creative problem solving", "innovation management"]</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -6076,7 +6084,7 @@
         <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -6084,7 +6092,7 @@
         </is>
       </c>
       <c r="V55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6092,7 +6100,7 @@
         </is>
       </c>
       <c r="X55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -6111,7 +6119,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial Data Interpretation</t>
+          <t>Numerical Data Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6136,7 +6144,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, statistical calculations</t>
+          <t>["financial analysis", "quantitative modelling", "cost\u2011benefit assessment", "Excel", "statistical calculations"]</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -6165,7 +6173,7 @@
         </is>
       </c>
       <c r="S56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
         <v>0.97</v>
@@ -6184,7 +6192,7 @@
         </is>
       </c>
       <c r="X56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -6203,7 +6211,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Policy Compliance Assessment</t>
+          <t>Strategic Action Plan Detailing</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6228,7 +6236,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>regulatory standards, compliance frameworks, risk assessment, governance risk and compliance, policy implementation planning</t>
+          <t>["regulatory standards", "compliance frameworks", "risk assessment", "governance risk and compliance", "policy implementation planning"]</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -6257,10 +6265,10 @@
         </is>
       </c>
       <c r="S57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -6276,7 +6284,7 @@
         </is>
       </c>
       <c r="X57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -6295,7 +6303,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Project Scheduling and Action Planning</t>
+          <t>Project Action Planning</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6315,12 +6323,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Develops detailed action plans with prioritised schedules to implement change initiatives efficiently.</t>
+          <t>Creates detailed action plans with prioritised schedules to implement change initiatives efficiently.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>action planning, prioritised schedules, timeline management, resource allocation, critical path</t>
+          <t>["action planning", "prioritised schedules", "timeline management", "resource allocation", "critical path"]</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -6360,7 +6368,7 @@
         </is>
       </c>
       <c r="V58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -6368,7 +6376,7 @@
         </is>
       </c>
       <c r="X58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -6387,7 +6395,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Implementation Difficulty Assessment</t>
+          <t>Implementation Difficulty Evaluation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6412,7 +6420,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ICT systems, change management, implementation complexity, risk analysis, impact assessment</t>
+          <t>["ICT systems", "change management", "implementation complexity", "risk analysis", "impact assessment"]</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -6460,7 +6468,7 @@
         </is>
       </c>
       <c r="X59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -6479,7 +6487,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Superior Reporting on Changes and Gaps</t>
+          <t>Strategic Change Reporting</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6499,12 +6507,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Prepares concise reports outlining changes, gaps and improvement opportunities for senior staff.</t>
+          <t>Prepares concise reports that outline changes, gaps and improvement opportunities for senior staff.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
+          <t>["executive communication", "gap analysis", "change management", "improvement recommendations", "business reporting"]</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -6548,7 +6556,7 @@
         <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -6556,7 +6564,7 @@
         </is>
       </c>
       <c r="V60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6564,7 +6572,7 @@
         </is>
       </c>
       <c r="X60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -6583,7 +6591,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Strategic Plan Evaluation</t>
+          <t>Current Strategic Plan Evaluation</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6608,7 +6616,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>strategic alignment, industry benchmarking, SWOT analysis, organisational objectives, gap analysis</t>
+          <t>["strategic alignment", "industry benchmarking", "SWOT analysis", "organisational objectives", "gap analysis"]</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -6656,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -6672,7 +6680,7 @@
         </is>
       </c>
       <c r="X61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -6691,7 +6699,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Systematic Decision‑Making for Complex Situations</t>
+          <t>Strategic Decision Analysis</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6711,12 +6719,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Uses structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
+          <t>Applies structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
+          <t>["decision analysis", "analytical reasoning", "structured methodologies", "risk assessment", "scenario modelling"]</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -6756,7 +6764,7 @@
         </is>
       </c>
       <c r="V62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6764,7 +6772,7 @@
         </is>
       </c>
       <c r="X62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -6783,7 +6791,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technical Communication for Diverse Audiences</t>
+          <t>Technical Communication</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6803,12 +6811,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Translates technical terminology into plain English to support understanding across diverse staff groups.</t>
+          <t>Translates technical terms into plain English to help diverse staff understand. Uses clear language for all audiences.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
+          <t>["plain language", "jargon translation", "stakeholder communication", "technical writing", "audience adaptation"]</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -6837,10 +6845,10 @@
         </is>
       </c>
       <c r="S63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -6848,7 +6856,7 @@
         </is>
       </c>
       <c r="V63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6856,7 +6864,7 @@
         </is>
       </c>
       <c r="X63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -6875,7 +6883,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Complex Text Analysis for IP, Ethics, and Privacy</t>
+          <t>Complex Text Legislative Analysis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6900,7 +6908,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>legislative compliance, policy analysis, regulatory standards, qualitative analysis</t>
+          <t>["legislative compliance", "policy analysis", "regulatory standards", "qualitative analysis"]</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -6933,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -6949,7 +6957,7 @@
         </is>
       </c>
       <c r="X64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -6993,7 +7001,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>privacy policy, regulatory standards, risk assessment, audit, data protection</t>
+          <t>["privacy policy", "regulatory standards", "risk assessment", "audit", "data protection"]</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -7042,7 +7050,7 @@
         </is>
       </c>
       <c r="X65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -7061,7 +7069,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Review Ethical Work Practices and Apply Code</t>
+          <t>Ethics, IP, and Privacy Application</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7081,12 +7089,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Reviews ethical practices and feedback and applies the organisational code of ethics to guide decisions.</t>
+          <t>Reviews ethical practices and feedback, then applies the organisational code of ethics to guide decisions.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical frameworks</t>
+          <t>["professional ethics", "codes of conduct", "compliance", "organisational governance", "ethical frameworks"]</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -7119,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -7127,7 +7135,7 @@
         </is>
       </c>
       <c r="V66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -7135,7 +7143,7 @@
         </is>
       </c>
       <c r="X66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -7154,7 +7162,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Feedback Handling for Review Procedures</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7179,7 +7187,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>grievance procedures, review processes, stakeholder communication, document management, complaint handling</t>
+          <t>["grievance procedures", "review processes", "stakeholder communication", "document management", "complaint handling"]</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -7228,7 +7236,7 @@
         </is>
       </c>
       <c r="X67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -7272,7 +7280,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, security controls</t>
+          <t>["penetration testing", "vulnerability assessment", "ISO 27001", "CIA triad", "security controls"]</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -7321,7 +7329,7 @@
         </is>
       </c>
       <c r="X68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -7340,7 +7348,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Policy Synthesis and Integration</t>
+          <t>Information Synthesis for Policy Development</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7360,12 +7368,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
+          <t>Combines diverse sources into clear written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>literature review, source integration, technical writing, citation management, knowledge synthesis</t>
+          <t>["literature review", "source integration", "technical writing", "citation management", "knowledge synthesis"]</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -7406,7 +7414,7 @@
         </is>
       </c>
       <c r="V69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7414,7 +7422,7 @@
         </is>
       </c>
       <c r="X69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -7433,7 +7441,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Identify IP &amp; Copyright Legislation, Policies and Procedures</t>
+          <t>IP Legislation Identification</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7458,7 +7466,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
+          <t>["intellectual property law", "copyright legislation", "policy compliance", "legal research", "regulatory analysis"]</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -7507,7 +7515,7 @@
         </is>
       </c>
       <c r="X70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -7526,7 +7534,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Distribute Revised Policies</t>
+          <t>Policy Distribution to Personnel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7551,7 +7559,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
+          <t>["document dissemination", "compliance communication", "stakeholder engagement", "internal governance", "ethics training"]</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -7584,7 +7592,7 @@
         <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -7600,7 +7608,7 @@
         </is>
       </c>
       <c r="X71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -7619,7 +7627,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Privacy, Ethics, and IP Policy Documentation</t>
+          <t>Privacy Policy and Ethics Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7639,12 +7647,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Updates privacy policies, procedures and codes of ethics to reflect current legislation and compliance requirements.</t>
+          <t>Update privacy policies, procedures and codes of ethics to match current legislation and compliance requirements.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>privacy legislation, compliance governance, policy management, codes of ethics, regulatory documentation</t>
+          <t>["privacy legislation", "compliance governance", "policy management", "codes of ethics", "regulatory documentation"]</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -7677,7 +7685,7 @@
         <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -7685,7 +7693,7 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
@@ -7693,7 +7701,7 @@
         </is>
       </c>
       <c r="X72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -7712,7 +7720,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Procedure Development</t>
+          <t>Review and Grievance Procedure</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7732,12 +7740,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Develops, records and submits review and grievance procedures to designated personnel.</t>
+          <t>Creates, records and sends review and grievance procedures to the appointed staff.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
+          <t>["policy drafting", "grievance management", "standard operating procedures", "process documentation", "compliance workflows"]</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -7767,7 +7775,7 @@
         </is>
       </c>
       <c r="S73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
         <v>0.92</v>
@@ -7778,7 +7786,7 @@
         </is>
       </c>
       <c r="V73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -7786,7 +7794,7 @@
         </is>
       </c>
       <c r="X73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7805,7 +7813,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Develop and Apply IP, Ethics, and Privacy Policies</t>
+          <t>Project Planning and Communication Management</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7825,12 +7833,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sequences and schedules complex activities, monitors progress and coordinates communication to maintain delivery momentum.</t>
+          <t>Create schedules for complex activities, monitor progress, and coordinate communication to keep delivery moving forward.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
+          <t>["scheduling", "resource allocation", "stakeholder communication", "project monitoring", "Gantt charts"]</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -7863,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -7871,7 +7879,7 @@
         </is>
       </c>
       <c r="V74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -7879,7 +7887,7 @@
         </is>
       </c>
       <c r="X74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -7898,7 +7906,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Regulatory Change Monitoring</t>
+          <t>Regulatory Monitoring</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7923,7 +7931,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>compliance, legislation monitoring, regulatory analysis, policy tracking, legal research</t>
+          <t>["compliance", "legislation monitoring", "regulatory analysis", "policy tracking", "legal research"]</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -7953,10 +7961,10 @@
         </is>
       </c>
       <c r="S75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -7972,7 +7980,7 @@
         </is>
       </c>
       <c r="X75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7991,7 +7999,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Safe Ethical Digital Handling</t>
+          <t>Digital Ethics and Privacy Management</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8016,7 +8024,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>cyber security, data protection, information governance, privacy compliance, access control</t>
+          <t>["cyber security", "data protection", "information governance", "privacy compliance", "access control"]</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -8049,7 +8057,7 @@
         <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -8065,7 +8073,7 @@
         </is>
       </c>
       <c r="X76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -8084,7 +8092,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Policy Distribution</t>
+          <t>Stakeholder Policy Distribution</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8104,12 +8112,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Distributes updated policies to stakeholders in accordance with organisational protocols.</t>
+          <t>Distribute updated policies to stakeholders following organisational protocols.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>policy dissemination, stakeholder engagement, communication protocols, change management, organisational compliance</t>
+          <t>["policy dissemination", "stakeholder engagement", "communication protocols", "change management", "organisational compliance"]</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -8150,7 +8158,7 @@
         </is>
       </c>
       <c r="V77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -8158,7 +8166,7 @@
         </is>
       </c>
       <c r="X77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8177,7 +8185,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Verbal Communication</t>
+          <t>Verbal Communication Participation</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8202,7 +8210,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>active listening, questioning techniques, stakeholder engagement, dialogue facilitation, interpersonal communication</t>
+          <t>["active listening", "questioning techniques", "stakeholder engagement", "dialogue facilitation", "interpersonal communication"]</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -8232,10 +8240,10 @@
         </is>
       </c>
       <c r="S78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -8251,7 +8259,7 @@
         </is>
       </c>
       <c r="X78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8270,7 +8278,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Set Up Blockchain Platform</t>
+          <t>Blockchain Solution Development</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8290,12 +8298,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Installs and configures blockchain platform components in line with approved design specifications.</t>
+          <t>Installs and configures blockchain platform components according to approved design specifications.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
+          <t>["distributed ledger", "node deployment", "consensus configuration", "Ethereum", "Docker"]</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -8328,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -8336,7 +8344,7 @@
         </is>
       </c>
       <c r="V79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -8344,7 +8352,7 @@
         </is>
       </c>
       <c r="X79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8383,12 +8391,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Identifies and resolves blockchain anomalies through contextual analysis to detect subtle deviations.</t>
+          <t>Detects and fixes blockchain anomalies by analysing context to spot subtle deviations.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
+          <t>["anomaly detection", "blockchain analytics", "smart contract debugging", "cryptographic forensics", "pattern recognition"]</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -8421,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -8429,7 +8437,7 @@
         </is>
       </c>
       <c r="V80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -8437,7 +8445,7 @@
         </is>
       </c>
       <c r="X80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8456,7 +8464,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Blockchain Requirements Definition</t>
+          <t>Blockchain Requirements Analysis</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8476,12 +8484,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Defines blockchain objectives and requirements aligned with organisational needs in hybrid environments.</t>
+          <t>Defines blockchain objectives and requirements that match organisational needs in hybrid environments.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>distributed ledger, use‑case definition, stakeholder analysis, smart contract design, governance frameworks</t>
+          <t>["distributed ledger", "use\u2011case definition", "stakeholder analysis", "smart contract design", "governance frameworks"]</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -8511,7 +8519,7 @@
         </is>
       </c>
       <c r="S81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
         <v>0.95</v>
@@ -8522,7 +8530,7 @@
         </is>
       </c>
       <c r="V81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8530,7 +8538,7 @@
         </is>
       </c>
       <c r="X81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -8549,7 +8557,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Implement Consensus Mechanism</t>
+          <t>Consensus Mechanism Implementation</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8569,12 +8577,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Implements consensus mechanisms by configuring and deploying required system components.</t>
+          <t>Configures and deploys system components to implement consensus mechanisms.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
+          <t>["blockchain", "distributed ledger", "consensus algorithms", "peer\u2011to\u2011peer networking", "Byzantine fault tolerance"]</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -8604,10 +8612,10 @@
         </is>
       </c>
       <c r="S82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -8615,7 +8623,7 @@
         </is>
       </c>
       <c r="V82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8623,7 +8631,7 @@
         </is>
       </c>
       <c r="X82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8662,12 +8670,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Produces detailed design documentation aligned with organisational requirements to support project delivery.</t>
+          <t>Creates detailed design documents that meet organisational requirements and support project delivery.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>technical specifications, design standards, engineering documentation, organisational requirements</t>
+          <t>["technical specifications", "design standards", "engineering documentation", "organisational requirements"]</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -8700,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -8708,7 +8716,7 @@
         </is>
       </c>
       <c r="V83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8716,7 +8724,7 @@
         </is>
       </c>
       <c r="X83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -8735,7 +8743,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Submit Documentation and Manage Feedback</t>
+          <t>Documentation Submission</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8755,12 +8763,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Submits documentation for review, seeks feedback and incorporates approved amendments.</t>
+          <t>Submit documentation for review, seek feedback and incorporate approved amendments.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
+          <t>["record\u2011keeping", "feedback loops", "compliance", "workflow approvals", "electronic filing"]</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -8790,10 +8798,10 @@
         </is>
       </c>
       <c r="S84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -8801,7 +8809,7 @@
         </is>
       </c>
       <c r="V84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8809,7 +8817,7 @@
         </is>
       </c>
       <c r="X84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -8848,12 +8856,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Designs integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
+          <t>Design integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>systems integration, workflow orchestration, process automation, ETL, API middleware</t>
+          <t>["systems integration", "workflow orchestration", "process automation", "ETL", "API middleware"]</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -8886,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -8894,7 +8902,7 @@
         </is>
       </c>
       <c r="V85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8902,7 +8910,7 @@
         </is>
       </c>
       <c r="X85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -8921,7 +8929,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Document Maintenance Schedule</t>
+          <t>Maintenance Schedule Documentation</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8941,12 +8949,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Develops and records maintenance schedules aligned with equipment requirements and timelines.</t>
+          <t>Creates and records maintenance schedules that match equipment needs and timelines.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
+          <t>["preventive maintenance", "asset management", "CMMS", "work order scheduling", "reliability engineering"]</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -8979,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -8987,7 +8995,7 @@
         </is>
       </c>
       <c r="V86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8995,7 +9003,7 @@
         </is>
       </c>
       <c r="X86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -9014,7 +9022,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Determine and Conduct Maintenance Tests</t>
+          <t>Maintenance Test Execution</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9039,7 +9047,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>preventive maintenance, test procedures, equipment inspection, reliability testing, compliance standards</t>
+          <t>["preventive maintenance", "test procedures", "equipment inspection", "reliability testing", "compliance standards"]</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -9072,7 +9080,7 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -9088,7 +9096,7 @@
         </is>
       </c>
       <c r="X87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -9107,7 +9115,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Blockchain Security Platform Selection</t>
+          <t>Security Platform Selection</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9132,7 +9140,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
+          <t>["blockchain", "security architecture", "platform evaluation", "cryptography", "risk assessment"]</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -9162,7 +9170,7 @@
         </is>
       </c>
       <c r="S88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
         <v>0.97</v>
@@ -9181,7 +9189,7 @@
         </is>
       </c>
       <c r="X88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -9220,12 +9228,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Deploys and manages smart contracts on approved blockchain platforms in line with solution specifications.</t>
+          <t>Deploys and manages smart contracts on approved blockchain platforms according to solution specifications.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>blockchain, Ethereum, Solidity, decentralised applications, Web3</t>
+          <t>["blockchain", "Ethereum", "Solidity", "decentralised applications", "Web3"]</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -9258,7 +9266,7 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -9266,7 +9274,7 @@
         </is>
       </c>
       <c r="V89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -9274,7 +9282,7 @@
         </is>
       </c>
       <c r="X89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -9293,7 +9301,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Solution Debugging</t>
+          <t>Blockchain Solution Debugging</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9313,12 +9321,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Diagnoses and resolves blockchain solution issues and optimises performance for scalable deployment.</t>
+          <t>Identifies and fixes blockchain solution problems, then improves performance for scalable deployment.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
+          <t>["blockchain", "smart contracts", "Solidity", "distributed ledger", "performance scaling"]</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -9348,10 +9356,10 @@
         </is>
       </c>
       <c r="S90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -9359,7 +9367,7 @@
         </is>
       </c>
       <c r="V90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9367,7 +9375,7 @@
         </is>
       </c>
       <c r="X90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -9386,7 +9394,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Solution Performance Testing</t>
+          <t>Organisational Performance Testing</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9406,12 +9414,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
+          <t>Tests solutions against organisational requirements to confirm they are suitable.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>benchmarking, requirements compliance, load testing, service level agreements, performance metrics</t>
+          <t>["benchmarking", "requirements compliance", "load testing", "service level agreements", "performance metrics"]</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -9441,10 +9449,10 @@
         </is>
       </c>
       <c r="S91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -9452,7 +9460,7 @@
         </is>
       </c>
       <c r="V91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9460,7 +9468,7 @@
         </is>
       </c>
       <c r="X91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -9479,7 +9487,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Stakeholder Requirements Oral Communication</t>
+          <t>Stakeholder Oral Communication</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9504,7 +9512,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, active listening</t>
+          <t>["stakeholder engagement", "requirements gathering", "industry terminology", "verbal communication", "active listening"]</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -9534,10 +9542,10 @@
         </is>
       </c>
       <c r="S92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -9553,7 +9561,7 @@
         </is>
       </c>
       <c r="X92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -9572,7 +9580,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Identify Organisational Use Case</t>
+          <t>Use‑Case Identification</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9592,12 +9600,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Analyses hybrid environments to identify organisational use cases aligned with business needs.</t>
+          <t>Analyses hybrid environments to identify organisational use cases that match business needs.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, functional requirements</t>
+          <t>["requirements analysis", "business analysis", "stakeholder mapping", "use\u2011case modelling", "functional requirements"]</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -9630,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -9638,7 +9646,7 @@
         </is>
       </c>
       <c r="V93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -9646,7 +9654,7 @@
         </is>
       </c>
       <c r="X93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -9665,7 +9673,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Analytic Platform Data Ingestion, Analysis, and Interpretation</t>
+          <t>Threat Data Ingestion Platform</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9685,12 +9693,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
+          <t>The system ingests data logs into analytics platforms to support monitoring and analysis.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data ingestion, log analytics, ETL pipelines, analytics platforms, monitoring</t>
+          <t>["data ingestion", "log analytics", "ETL pipelines", "analytics platforms", "monitoring"]</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -9742,7 +9750,7 @@
         </is>
       </c>
       <c r="V94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -9750,7 +9758,7 @@
         </is>
       </c>
       <c r="X94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -9769,7 +9777,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Identify Compliance Requirements for Threat Data Gathering</t>
+          <t>Compliance Threat Data Identification</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9789,12 +9797,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Identifies relevant legislation and internal policies governing the collection, analysis and use of threat data.</t>
+          <t>Identifies legislation and internal policies that govern the collection, analysis and use of threat data.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>regulatory compliance, legislation, policy analysis, threat intelligence, risk assessment</t>
+          <t>["regulatory compliance", "legislation", "policy analysis", "threat intelligence", "risk assessment"]</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -9850,7 +9858,7 @@
         </is>
       </c>
       <c r="V95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -9858,7 +9866,7 @@
         </is>
       </c>
       <c r="X95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -9877,7 +9885,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Threat Data Discrepancy Detection</t>
+          <t>Data Discrepancy Analysis</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9897,12 +9905,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Examines datasets to identify, document and resolve data discrepancies and inconsistencies.</t>
+          <t>Examines datasets to find, record and fix data discrepancies and inconsistencies.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data validation, anomaly detection, data quality, data auditing, profiling</t>
+          <t>["data validation", "anomaly detection", "data quality", "data auditing", "profiling"]</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -9943,7 +9951,7 @@
         </is>
       </c>
       <c r="S96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
         <v>0.92</v>
@@ -9954,7 +9962,7 @@
         </is>
       </c>
       <c r="V96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -9962,7 +9970,7 @@
         </is>
       </c>
       <c r="X96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -9981,7 +9989,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Threat Data Collection and Creation</t>
+          <t>Threat Data Set Procedure</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10001,12 +10009,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
+          <t>Collect alerts, logs and event reports and organise them into structured data sets following organisational policies.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>log analysis, data ingestion, security monitoring, data governance, ETL processes</t>
+          <t>["log analysis", "data ingestion", "security monitoring", "data governance", "ETL processes"]</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -10058,7 +10066,7 @@
         </is>
       </c>
       <c r="V97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -10066,7 +10074,7 @@
         </is>
       </c>
       <c r="X97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -10085,7 +10093,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>False Positive Detection and Analysis</t>
+          <t>False Positive Detection</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10110,7 +10118,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>type I error, anomaly detection, validation testing, precision‑recall analysis, statistical significance</t>
+          <t>["type I error", "anomaly detection", "validation testing", "precision\u2011recall analysis", "statistical significance"]</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -10155,10 +10163,10 @@
         </is>
       </c>
       <c r="S98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -10174,7 +10182,7 @@
         </is>
       </c>
       <c r="X98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -10193,7 +10201,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Document Findings and Recommendations</t>
+          <t>Threat Data Report</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10213,12 +10221,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Produces formal investigation reports outlining findings and recommendations in accordance with organisational procedures.</t>
+          <t>Creates formal investigation reports that outline findings and recommendations following organisational procedures.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>incident reporting, root‑cause analysis, procedural compliance, report writing, safety management</t>
+          <t>["incident reporting", "root\u2011cause analysis", "procedural compliance", "report writing", "safety management"]</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -10258,7 +10266,7 @@
         <v>1</v>
       </c>
       <c r="T99" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -10266,7 +10274,7 @@
         </is>
       </c>
       <c r="V99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -10274,7 +10282,7 @@
         </is>
       </c>
       <c r="X99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -10313,12 +10321,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Develops and validates mitigation strategies, action steps and lessons learned with relevant personnel.</t>
+          <t>Creates and checks mitigation strategies, action steps and lessons learned with relevant personnel.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>risk management, lessons learned, action planning, stakeholder engagement, mitigation planning</t>
+          <t>["risk management", "lessons learned", "action planning", "stakeholder engagement", "mitigation planning"]</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -10374,7 +10382,7 @@
         </is>
       </c>
       <c r="V100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -10382,7 +10390,7 @@
         </is>
       </c>
       <c r="X100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -10401,7 +10409,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Risk Likelihood and Impact Assessment</t>
+          <t>Risk Likelihood Assessment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10421,12 +10429,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Assesses threats by evaluating likelihood and impact to prioritise risk mitigation actions.</t>
+          <t>Evaluates threats by judging their likelihood and impact to set risk mitigation priorities.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
+          <t>["risk assessment", "probability analysis", "threat modelling", "impact evaluation", "risk matrices"]</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -10467,10 +10475,10 @@
         </is>
       </c>
       <c r="S101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -10478,7 +10486,7 @@
         </is>
       </c>
       <c r="V101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -10486,7 +10494,7 @@
         </is>
       </c>
       <c r="X101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -10505,7 +10513,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Identify Security Equipment and Data Sources</t>
+          <t>Security Equipment Identification</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10525,12 +10533,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Identifies network and data‑source security equipment using system diagrams and technical documentation.</t>
+          <t>Identifies network and data source security equipment using system diagrams and technical documentation.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>cyber security, network security, asset inventories, IDS, firewalls</t>
+          <t>["cyber security", "network security", "asset inventories", "intrusion detection systems", "firewalls"]</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -10571,10 +10579,10 @@
         </is>
       </c>
       <c r="S102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -10582,7 +10590,7 @@
         </is>
       </c>
       <c r="V102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -10590,7 +10598,7 @@
         </is>
       </c>
       <c r="X102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -10634,7 +10642,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
+          <t>["log aggregation", "SIEM", "data ingestion", "security analytics", "ELK stack"]</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -10694,7 +10702,7 @@
         </is>
       </c>
       <c r="X103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -10713,7 +10721,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Threat Data Discussion and Review</t>
+          <t>Threat Data Review</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10738,7 +10746,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
+          <t>["stakeholder engagement", "threat intelligence", "risk reporting", "data briefings", "cyber security communication"]</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -10782,7 +10790,7 @@
         <v>1</v>
       </c>
       <c r="T104" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -10798,7 +10806,7 @@
         </is>
       </c>
       <c r="X104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -10837,12 +10845,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collects and structures alerts, logs and event data in accordance with organisational data policies.</t>
+          <t>Collects and structures alerts, logs and event data according to organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>threat intelligence, log analysis, SIEM, incident response, security monitoring</t>
+          <t>["threat intelligence", "log analysis", "SIEM", "incident response", "security monitoring"]</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -10894,7 +10902,7 @@
         </is>
       </c>
       <c r="V105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -10902,7 +10910,7 @@
         </is>
       </c>
       <c r="X105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -10921,7 +10929,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Anomaly Detection, Response, and Protection Strategy</t>
+          <t>Anomaly Detection and Remediation</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10941,12 +10949,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Monitors operational data to detect contextual anomalies and resolves deviations in a timely manner.</t>
+          <t>Monitors operational data to detect contextual anomalies and resolves deviations promptly.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
+          <t>["outlier analysis", "root\u2011cause analysis", "statistical process control", "monitoring and diagnostics"]</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -10979,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -10987,7 +10995,7 @@
         </is>
       </c>
       <c r="V106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -10995,7 +11003,7 @@
         </is>
       </c>
       <c r="X106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -11014,7 +11022,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Protection Strategy and Asset Management Implementation</t>
+          <t>Infrastructure Asset Management Implementation</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11039,7 +11047,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>asset tracking, risk mitigation, protection plans, maintenance scheduling, capital budgeting</t>
+          <t>["asset tracking", "risk mitigation", "protection plans", "maintenance scheduling", "capital budgeting"]</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -11088,7 +11096,7 @@
         </is>
       </c>
       <c r="X107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -11107,7 +11115,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Protection Research</t>
+          <t>Critical Infrastructure Research</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11127,12 +11135,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Conducts critical infrastructure research to support protection planning and documentation requirements.</t>
+          <t>Conducts research on critical infrastructure to support protection planning and documentation requirements.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>infrastructure protection, risk assessment, threat modelling, resilience analysis, policy compliance</t>
+          <t>["infrastructure protection", "risk assessment", "threat modelling", "resilience analysis", "policy compliance"]</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -11162,7 +11170,7 @@
         </is>
       </c>
       <c r="S108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
         <v>0.97</v>
@@ -11173,7 +11181,7 @@
         </is>
       </c>
       <c r="V108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -11181,7 +11189,7 @@
         </is>
       </c>
       <c r="X108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -11200,7 +11208,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Data Backup</t>
+          <t>Data Backup Strategy</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11220,12 +11228,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Executes scheduled data backups in line with organisational policies and procedures.</t>
+          <t>Runs scheduled data backups following organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>disaster recovery, backup software, data retention policies, storage replication, ICT compliance</t>
+          <t>["disaster recovery", "backup software", "data retention policies", "storage replication", "ICT compliance"]</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -11258,7 +11266,7 @@
         <v>1</v>
       </c>
       <c r="T109" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -11266,7 +11274,7 @@
         </is>
       </c>
       <c r="V109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11274,7 +11282,7 @@
         </is>
       </c>
       <c r="X109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -11293,7 +11301,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Secure Devices per Protection Strategy</t>
+          <t>Device Security Measures</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11313,12 +11321,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Implements device security controls in accordance with protection plans and technical specifications.</t>
+          <t>Implements device security controls following protection plans and technical specifications.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>endpoint protection, device hardening, security policies, encryption, mobile device management</t>
+          <t>["endpoint protection", "device hardening", "security policies", "encryption", "mobile device management"]</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -11359,7 +11367,7 @@
         </is>
       </c>
       <c r="V110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -11367,7 +11375,7 @@
         </is>
       </c>
       <c r="X110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -11386,7 +11394,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Feedback Seeking and Response Management</t>
+          <t>Protection Plan Feedback Management</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11406,12 +11414,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Submits protection plans for review and incorporates stakeholder feedback to improve outcomes.</t>
+          <t>Submit protection plans for review and incorporate stakeholder feedback to improve outcomes.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>stakeholder communication, feedback loops, response management, plan documentation, compliance reporting</t>
+          <t>["stakeholder communication", "feedback loops", "response management", "plan documentation", "compliance reporting"]</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -11444,7 +11452,7 @@
         <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -11452,7 +11460,7 @@
         </is>
       </c>
       <c r="V111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -11460,7 +11468,7 @@
         </is>
       </c>
       <c r="X111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -11479,7 +11487,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Network Segmentation Deployment</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11499,12 +11507,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
+          <t>Deploys network segmentation to isolate security zones according to approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
+          <t>["VLANs", "firewall policies", "micro\u2011segmentation", "zero\u2011trust architecture", "network security zones"]</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -11534,10 +11542,10 @@
         </is>
       </c>
       <c r="S112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -11545,7 +11553,7 @@
         </is>
       </c>
       <c r="V112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -11553,7 +11561,7 @@
         </is>
       </c>
       <c r="X112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -11572,7 +11580,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Protection Strategy Development</t>
+          <t>Protection Strategy Development</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11592,12 +11600,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Develops staged operational plans and regularly reviews priorities and performance during execution.</t>
+          <t>Creates staged operational plans and reviews priorities and performance throughout execution.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>operational planning, performance monitoring, resource allocation, timeline management, Gantt charts</t>
+          <t>["operational planning", "performance monitoring", "resource allocation", "timeline management", "Gantt charts"]</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -11630,7 +11638,7 @@
         <v>1</v>
       </c>
       <c r="T113" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -11638,7 +11646,7 @@
         </is>
       </c>
       <c r="V113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -11646,7 +11654,7 @@
         </is>
       </c>
       <c r="X113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -11685,12 +11693,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Evaluates current critical infrastructure protection plans to identify gaps and recommend improvements.</t>
+          <t>Evaluates current critical infrastructure protection plans, identifies gaps, and recommends improvements.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>critical infrastructure, risk assessment, cyber security resilience, ISO 27001, vulnerability analysis</t>
+          <t>["critical infrastructure", "risk assessment", "cyber security resilience", "ISO 27001", "vulnerability analysis"]</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -11731,7 +11739,7 @@
         </is>
       </c>
       <c r="V114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -11739,7 +11747,7 @@
         </is>
       </c>
       <c r="X114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -11778,12 +11786,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Develops and records critical infrastructure protection plans aligned with organisational policies and procedures.</t>
+          <t>Creates and documents protection plans for critical infrastructure that follow organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
+          <t>["critical infrastructure", "risk assessment", "security policy compliance", "business continuity planning", "incident response frameworks"]</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -11824,7 +11832,7 @@
         </is>
       </c>
       <c r="V115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -11832,7 +11840,7 @@
         </is>
       </c>
       <c r="X115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -11851,7 +11859,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Protection Deployment Testing</t>
+          <t>Protection Plan Deployment Test</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11871,12 +11879,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Conducts protection plan testing to validate safeguards in line with organisational requirements.</t>
+          <t>Tests protection plans to confirm safeguards meet organisational requirements.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>cyber security, risk assessment, compliance testing, security policies, vulnerability testing</t>
+          <t>["cyber security", "risk assessment", "compliance testing", "security policies", "vulnerability testing"]</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -11917,7 +11925,7 @@
         </is>
       </c>
       <c r="V116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -11925,7 +11933,7 @@
         </is>
       </c>
       <c r="X116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -11944,7 +11952,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Results Analysis Reporting</t>
+          <t>Results Analysis</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11969,7 +11977,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>data interpretation, performance metrics, compliance reporting, organisational standards, business intelligence</t>
+          <t>["data interpretation", "performance metrics", "compliance reporting", "organisational standards", "business intelligence"]</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -11999,7 +12007,7 @@
         </is>
       </c>
       <c r="S117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" t="n">
         <v>0.92</v>
@@ -12018,7 +12026,7 @@
         </is>
       </c>
       <c r="X117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -12062,7 +12070,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>vulnerability analysis, mitigation planning, risk matrices, security governance, ISO 27001 compliance</t>
+          <t>["vulnerability analysis", "mitigation planning", "risk matrices", "security governance", "ISO 27001 compliance"]</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -12111,7 +12119,7 @@
         </is>
       </c>
       <c r="X118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -12130,7 +12138,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Apply Software Patches for Critical Infrastructure Protection</t>
+          <t>Software Patch Deployment</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12150,12 +12158,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Installs and configures software updates in line with documented technical specifications.</t>
+          <t>Installs and configures software updates according to documented technical specifications.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
+          <t>["patch management", "vulnerability remediation", "update deployment", "configuration management", "WSUS"]</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -12188,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -12196,7 +12204,7 @@
         </is>
       </c>
       <c r="V119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
@@ -12204,7 +12212,7 @@
         </is>
       </c>
       <c r="X119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -12223,7 +12231,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Technical Documentation Preparation</t>
+          <t>Technical Documentation for Infrastructure Protection</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12243,12 +12251,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Produces workplace documentation using mandated structure, layout and organisational language standards.</t>
+          <t>Creates workplace documents that follow required structure, layout and organisational language standards.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>technical writing, process documentation, standard operating procedures, document formatting</t>
+          <t>["technical writing", "process documentation", "standard operating procedures", "document formatting"]</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -12278,10 +12286,10 @@
         </is>
       </c>
       <c r="S120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -12289,7 +12297,7 @@
         </is>
       </c>
       <c r="V120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
@@ -12297,7 +12305,7 @@
         </is>
       </c>
       <c r="X120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -12316,7 +12324,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Establish Data Types for Security Architecture</t>
+          <t>Data Classification Identification</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12341,7 +12349,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>information security, data inventories, classification schemes, confidentiality levels, security architecture</t>
+          <t>["information security", "data inventories", "classification schemes", "confidentiality levels", "security architecture"]</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -12386,10 +12394,10 @@
         </is>
       </c>
       <c r="S121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -12405,7 +12413,7 @@
         </is>
       </c>
       <c r="X121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -12424,7 +12432,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Manage Feedback Responses</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12444,12 +12452,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Submits required documentation promptly to obtain initial stakeholder feedback.</t>
+          <t>Submit required documentation promptly to obtain initial stakeholder feedback.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
+          <t>["documentation", "stakeholder communication", "feedback loops", "record\u2011keeping", "internal reporting"]</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -12493,7 +12501,7 @@
         <v>1</v>
       </c>
       <c r="T122" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -12501,7 +12509,7 @@
         </is>
       </c>
       <c r="V122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" t="inlineStr">
         <is>
@@ -12509,7 +12517,7 @@
         </is>
       </c>
       <c r="X122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -12528,7 +12536,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Security Architecture Design Methodology</t>
+          <t>Industry Design Methodology Research</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12553,7 +12561,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>security architecture, design methodologies, industry standards, security frameworks, risk assessment</t>
+          <t>["security architecture", "design methodologies", "industry standards", "security frameworks", "risk assessment"]</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -12593,7 +12601,7 @@
         <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -12609,7 +12617,7 @@
         </is>
       </c>
       <c r="X123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -12628,7 +12636,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Contextual Analysis for Security Architecture Design</t>
+          <t>Contextual Anomaly Detection</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12648,12 +12656,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
+          <t>Uses contextual awareness to spot security anomalies and deviations from normal operating patterns.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>anomaly detection, threat analysis, security monitoring, pattern recognition, situational awareness</t>
+          <t>["anomaly detection", "threat analysis", "security monitoring", "pattern recognition", "situational awareness"]</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -12701,7 +12709,7 @@
         <v>1</v>
       </c>
       <c r="T124" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -12709,7 +12717,7 @@
         </is>
       </c>
       <c r="V124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -12717,7 +12725,7 @@
         </is>
       </c>
       <c r="X124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -12736,7 +12744,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Architecture Documentation and Confirmation</t>
+          <t>Security Architecture Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12756,12 +12764,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Documents and validates security architecture findings with relevant personnel.</t>
+          <t>Document and validate security architecture findings with relevant personnel.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>security architecture, risk assessment, compliance frameworks, ISO 27001, threat modelling</t>
+          <t>["security architecture", "risk assessment", "compliance frameworks", "ISO 27001", "threat modelling"]</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -12802,10 +12810,10 @@
         </is>
       </c>
       <c r="S125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -12813,7 +12821,7 @@
         </is>
       </c>
       <c r="V125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" t="inlineStr">
         <is>
@@ -12821,7 +12829,7 @@
         </is>
       </c>
       <c r="X125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -12840,7 +12848,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Security Architecture Presentation Documentation</t>
+          <t>Security Architecture Presentation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12860,12 +12868,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Prepares and delivers documented security architecture presentations for stakeholder engagement.</t>
+          <t>Creates and delivers documented security architecture presentations to engage stakeholders.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>information security, enterprise architecture, risk assessment, security frameworks, technical presentations</t>
+          <t>["information security", "enterprise architecture", "risk assessment", "security frameworks", "technical presentations"]</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -12906,7 +12914,7 @@
         </is>
       </c>
       <c r="S126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
         <v>0.95</v>
@@ -12917,7 +12925,7 @@
         </is>
       </c>
       <c r="V126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" t="inlineStr">
         <is>
@@ -12925,7 +12933,7 @@
         </is>
       </c>
       <c r="X126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -12944,7 +12952,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Validate Security Design Using Standard Methodologies</t>
+          <t>Security Design Validation</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -12964,12 +12972,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Validates security designs using industry‑recognised methodologies.</t>
+          <t>Validates security designs using industry‑recognised methods.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>security architecture, threat modelling, NIST framework, ISO 27001, risk assessment</t>
+          <t>["security architecture", "threat modelling", "NIST framework", "ISO 27001", "risk assessment"]</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -13010,7 +13018,7 @@
         </is>
       </c>
       <c r="S127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T127" t="n">
         <v>0.92</v>
@@ -13021,7 +13029,7 @@
         </is>
       </c>
       <c r="V127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" t="inlineStr">
         <is>
@@ -13029,7 +13037,7 @@
         </is>
       </c>
       <c r="X127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -13048,7 +13056,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Determine Required Security Level</t>
+          <t>Security Level Determination</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13068,12 +13076,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
+          <t>Assesses assets to decide required security levels, perimeters, features and protection modes.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>risk assessment, access control, security architecture, perimeter security, security policy</t>
+          <t>["risk assessment", "access control", "security architecture", "perimeter security", "security policy"]</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -13118,10 +13126,10 @@
         </is>
       </c>
       <c r="S128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -13129,7 +13137,7 @@
         </is>
       </c>
       <c r="V128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
@@ -13137,7 +13145,7 @@
         </is>
       </c>
       <c r="X128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -13156,7 +13164,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Security Project Planning</t>
+          <t>Security Architecture Design</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13176,12 +13184,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Develops staged operational plans for security initiatives and reviews progress during delivery.</t>
+          <t>Creates staged operational plans for security initiatives and reviews progress during delivery.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>cyber security governance, risk assessment, phased implementation, performance monitoring, project scheduling tools</t>
+          <t>["cyber security governance", "risk assessment", "phased implementation", "performance monitoring", "project scheduling tools"]</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -13226,10 +13234,10 @@
         </is>
       </c>
       <c r="S129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -13237,7 +13245,7 @@
         </is>
       </c>
       <c r="V129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" t="inlineStr">
         <is>
@@ -13245,7 +13253,7 @@
         </is>
       </c>
       <c r="X129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -13289,7 +13297,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
+          <t>["risk assessment", "threat modelling", "security architecture", "compliance standards", "vulnerability analysis"]</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -13329,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -13345,7 +13353,7 @@
         </is>
       </c>
       <c r="X130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -13384,12 +13392,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Designs and documents security solutions aligned with organisational standards and requirements.</t>
+          <t>Designs and documents security solutions that meet organisational standards and requirements.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>cyber security architecture, risk assessment, security compliance, solution documentation, threat modelling</t>
+          <t>["cyber security architecture", "risk assessment", "security compliance", "solution documentation", "threat modelling"]</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -13437,7 +13445,7 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -13445,7 +13453,7 @@
         </is>
       </c>
       <c r="V131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" t="inlineStr">
         <is>
@@ -13453,7 +13461,7 @@
         </is>
       </c>
       <c r="X131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -13472,7 +13480,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Security Architecture Documentation Preparation</t>
+          <t>Complex Documentation Preparation</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13492,12 +13500,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Produces detailed technical documentation outlining findings and proposed solutions.</t>
+          <t>Creates detailed technical documents that outline findings and propose solutions.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>technical writing, documentation standards, reporting and analysis, knowledge management</t>
+          <t>["technical writing", "documentation standards", "reporting and analysis", "knowledge management"]</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -13545,7 +13553,7 @@
         <v>1</v>
       </c>
       <c r="T132" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -13553,7 +13561,7 @@
         </is>
       </c>
       <c r="V132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" t="inlineStr">
         <is>
@@ -13561,7 +13569,7 @@
         </is>
       </c>
       <c r="X132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -13580,7 +13588,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Documentation Interpretation</t>
+          <t>Technical Documentation Interpretation</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13600,12 +13608,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements prior to work commencement.</t>
+          <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements before work starts.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>technical documentation, specification standards, manufacturer manuals, job requirement analysis, engineering drawings</t>
+          <t>["technical documentation", "specification standards", "manufacturer manuals", "job requirement analysis", "engineering drawings"]</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -13649,7 +13657,7 @@
         <v>1</v>
       </c>
       <c r="T133" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -13657,7 +13665,7 @@
         </is>
       </c>
       <c r="V133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" t="inlineStr">
         <is>
@@ -13665,7 +13673,7 @@
         </is>
       </c>
       <c r="X133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -13684,7 +13692,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Autonomous Incident Response Planning</t>
+          <t>Autonomous Decision Making</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13704,12 +13712,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Makes independent strategic decisions to align actions with organisational objectives and improve performance.</t>
+          <t>Makes independent strategic decisions that align actions with organisational objectives and improve performance.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
+          <t>["autonomy", "strategic decision\u2011making", "self\u2011management", "leadership", "organisational performance"]</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -13755,7 +13763,7 @@
         </is>
       </c>
       <c r="S134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T134" t="n">
         <v>0.92</v>
@@ -13766,7 +13774,7 @@
         </is>
       </c>
       <c r="V134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W134" t="inlineStr">
         <is>
@@ -13774,7 +13782,7 @@
         </is>
       </c>
       <c r="X134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -13793,7 +13801,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Develop Forensic Evidence Collection Procedure</t>
+          <t>Forensic Evidence Collection Procedure Development</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -13818,7 +13826,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
+          <t>["chain of custody", "evidence preservation", "incident response", "digital forensics tools", "crime scene documentation"]</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -13863,7 +13871,7 @@
         <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -13879,7 +13887,7 @@
         </is>
       </c>
       <c r="X135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -13918,12 +13926,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Prepares detailed incident reports documenting response actions against task requirements.</t>
+          <t>Prepares detailed incident reports that document response actions and meet task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
+          <t>["security incident response", "incident reporting", "ITIL", "SIEM", "compliance documentation"]</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -13964,7 +13972,7 @@
         <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -13972,7 +13980,7 @@
         </is>
       </c>
       <c r="V136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" t="inlineStr">
         <is>
@@ -13980,7 +13988,7 @@
         </is>
       </c>
       <c r="X136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -13999,7 +14007,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Incident Response Plan Evaluation</t>
+          <t>Incident Response Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14019,12 +14027,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Evaluates incident response plans for effectiveness across hybrid operating environments.</t>
+          <t>Assesses incident response plans for effectiveness in hybrid operating environments.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>security operations, post‑incident analysis, efficiency metrics, response plan documentation, SOC tools</t>
+          <t>["security operations", "post\u2011incident analysis", "efficiency metrics", "response plan documentation", "SOC tools"]</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -14066,7 +14074,7 @@
         </is>
       </c>
       <c r="S137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
         <v>0.97</v>
@@ -14077,7 +14085,7 @@
         </is>
       </c>
       <c r="V137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" t="inlineStr">
         <is>
@@ -14085,7 +14093,7 @@
         </is>
       </c>
       <c r="X137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -14124,12 +14132,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Develops and records incident response plans aligned with organisational requirements.</t>
+          <t>Creates and documents incident response plans that meet organisational requirements.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>cyber security, incident handling, NIST framework, playbook development, risk management</t>
+          <t>["cyber security", "incident handling", "NIST framework", "playbook development", "risk management"]</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -14174,7 +14182,7 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -14182,7 +14190,7 @@
         </is>
       </c>
       <c r="V138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W138" t="inlineStr">
         <is>
@@ -14190,7 +14198,7 @@
         </is>
       </c>
       <c r="X138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -14209,7 +14217,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Incident Response Team Coordination</t>
+          <t>Incident Response Team Services</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -14229,12 +14237,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Documents incident response team roles and services to support coordinated response.</t>
+          <t>Document incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>incident response, service documentation, team coordination, organisational compliance, ticketing systems</t>
+          <t>["incident response", "service documentation", "team coordination", "organisational compliance", "ticketing systems"]</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -14275,7 +14283,7 @@
         <v>1</v>
       </c>
       <c r="T139" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -14283,7 +14291,7 @@
         </is>
       </c>
       <c r="V139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" t="inlineStr">
         <is>
@@ -14291,7 +14299,7 @@
         </is>
       </c>
       <c r="X139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -14310,7 +14318,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Incident Response Plan Development, Implementation, and Evaluation</t>
+          <t>Incident Response Red‑Team Planning</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14330,12 +14338,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Designs and conducts red‑team exercises and incident response simulations, including staffing and training plans.</t>
+          <t>Designs and runs red‑team exercises and incident response simulations, including staffing and training plans.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>adversary simulation, incident response planning, threat modelling, security training programmes, MITRE ATT&amp;CK framework</t>
+          <t>["adversary simulation", "incident response planning", "threat modelling", "security training programmes", "MITRE ATT&amp;CK framework"]</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -14380,7 +14388,7 @@
         <v>1</v>
       </c>
       <c r="T140" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
@@ -14388,7 +14396,7 @@
         </is>
       </c>
       <c r="V140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" t="inlineStr">
         <is>
@@ -14396,7 +14404,7 @@
         </is>
       </c>
       <c r="X140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -14435,12 +14443,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Evaluates the effectiveness of incident response communications across internal and external stakeholders.</t>
+          <t>Evaluates how well incident response communications work with internal and external stakeholders.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>incident response, stakeholder communication, internal coordination, external liaison, communication effectiveness</t>
+          <t>["incident response", "stakeholder communication", "internal coordination", "external liaison", "communication effectiveness"]</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -14485,7 +14493,7 @@
         <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -14493,7 +14501,7 @@
         </is>
       </c>
       <c r="V141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" t="inlineStr">
         <is>
@@ -14501,7 +14509,7 @@
         </is>
       </c>
       <c r="X141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -14520,7 +14528,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Interpret, Analyze, and Document System Data</t>
+          <t>Risk Analysis</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14540,12 +14548,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
+          <t>Interprets and records numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical data interpretation, risk assessment, system modelling, data documentation</t>
+          <t>["quantitative analysis", "technical data interpretation", "risk assessment", "system modelling", "data documentation"]</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -14591,10 +14599,10 @@
         </is>
       </c>
       <c r="S142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -14602,7 +14610,7 @@
         </is>
       </c>
       <c r="V142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" t="inlineStr">
         <is>
@@ -14610,7 +14618,7 @@
         </is>
       </c>
       <c r="X142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -14629,7 +14637,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Incident Response Planning and Execution</t>
+          <t>Incident Response Management</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14649,12 +14657,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Executes incident response actions in accordance with approved incident response plans.</t>
+          <t>Executes incident response actions following approved response plans.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
+          <t>["incident response", "security operations centre", "SIEM", "playbook execution", "forensic analysis"]</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -14703,7 +14711,7 @@
         <v>1</v>
       </c>
       <c r="T143" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -14711,7 +14719,7 @@
         </is>
       </c>
       <c r="V143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" t="inlineStr">
         <is>
@@ -14719,7 +14727,7 @@
         </is>
       </c>
       <c r="X143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -14758,12 +14766,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Develops and documents incident management policies aligned with organisational specifications.</t>
+          <t>Creates and records incident management policies that match organisational specifications.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
+          <t>["incident management", "risk assessment", "governance", "compliance", "ISO 27001"]</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -14812,7 +14820,7 @@
         <v>1</v>
       </c>
       <c r="T144" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -14820,7 +14828,7 @@
         </is>
       </c>
       <c r="V144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W144" t="inlineStr">
         <is>
@@ -14828,7 +14836,7 @@
         </is>
       </c>
       <c r="X144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -14847,7 +14855,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Develop, Implement, and Evaluate Incident Response Plan</t>
+          <t>Technical Data Interpretation</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -14872,7 +14880,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, engineering diagnostics</t>
+          <t>["quantitative analysis", "technical system data", "measurement instrumentation", "data documentation", "engineering diagnostics"]</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -14918,7 +14926,7 @@
         </is>
       </c>
       <c r="S145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
         <v>0.95</v>
@@ -14937,7 +14945,7 @@
         </is>
       </c>
       <c r="X145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -14956,7 +14964,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Business Continuity Evaluation</t>
+          <t>Business Continuity Impact Evaluation</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -14976,12 +14984,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Assesses system impacts on business continuity to identify risks and mitigation strategies.</t>
+          <t>Evaluates system impacts on business continuity, identifies risks and develops mitigation strategies.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>business continuity, risk assessment, impact analysis, disaster recovery, resilience planning</t>
+          <t>["business continuity", "risk assessment", "impact analysis", "disaster recovery", "resilience planning"]</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -15023,7 +15031,7 @@
         </is>
       </c>
       <c r="S146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" t="n">
         <v>0.95</v>
@@ -15034,7 +15042,7 @@
         </is>
       </c>
       <c r="V146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" t="inlineStr">
         <is>
@@ -15042,7 +15050,7 @@
         </is>
       </c>
       <c r="X146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -15061,7 +15069,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Disaster Recovery and Business Continuity Planning</t>
+          <t>Disaster Recovery Planning</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15081,12 +15089,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Designs and implements compliance strategies to align organisational processes with regulatory requirements.</t>
+          <t>Designs and implements compliance strategies that align organisational processes with regulatory requirements.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>regulatory compliance, policy enforcement, risk management, governance, audit</t>
+          <t>["regulatory compliance", "policy enforcement", "risk management", "governance", "audit"]</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -15139,7 +15147,7 @@
         </is>
       </c>
       <c r="V147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" t="inlineStr">
         <is>
@@ -15147,7 +15155,7 @@
         </is>
       </c>
       <c r="X147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -15166,7 +15174,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Contingency Planning and Disaster Recovery</t>
+          <t>Contingency Plan Development</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15186,12 +15194,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Develops contingency plans by identifying threats and defining response actions.</t>
+          <t>Creates contingency plans by identifying threats and defining response actions.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>risk assessment, business continuity, threat identification, mitigation strategies, scenario analysis</t>
+          <t>["risk assessment", "business continuity", "threat identification", "mitigation strategies", "scenario analysis"]</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -15237,10 +15245,10 @@
         </is>
       </c>
       <c r="S148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
@@ -15248,7 +15256,7 @@
         </is>
       </c>
       <c r="V148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" t="inlineStr">
         <is>
@@ -15256,7 +15264,7 @@
         </is>
       </c>
       <c r="X148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -15275,7 +15283,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cost Constraint Evaluation</t>
+          <t>Cost Constraint Analysis</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15295,12 +15303,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Evaluates prevention and recovery options for compliance and cost effectiveness.</t>
+          <t>Evaluates options to prevent and recover while meeting compliance and cost effectiveness.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, financial modelling</t>
+          <t>["cost\u2011benefit analysis", "budgeting", "risk assessment", "business case evaluation", "financial modelling"]</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -15342,7 +15350,7 @@
         </is>
       </c>
       <c r="S149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
         <v>0.95</v>
@@ -15353,7 +15361,7 @@
         </is>
       </c>
       <c r="V149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" t="inlineStr">
         <is>
@@ -15361,7 +15369,7 @@
         </is>
       </c>
       <c r="X149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -15400,12 +15408,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes.</t>
+          <t>Creates detailed disaster recovery plans that outline procedures, resources and recovery timeframes.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>business continuity, backup and restore, recovery time objectives, risk assessment, disaster recovery testing</t>
+          <t>["business continuity", "backup and restore", "recovery time objectives", "risk assessment", "disaster recovery testing"]</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -15450,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -15458,7 +15466,7 @@
         </is>
       </c>
       <c r="V150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W150" t="inlineStr">
         <is>
@@ -15466,7 +15474,7 @@
         </is>
       </c>
       <c r="X150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -15485,7 +15493,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Industry Standards Review and Risk Safeguard Assessment</t>
+          <t>Industry Standards Review</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15510,7 +15518,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>compliance, risk management, standard operating procedures, regulatory guidance, audit</t>
+          <t>["compliance", "risk management", "standard operating procedures", "regulatory guidance", "audit"]</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -15552,7 +15560,7 @@
         </is>
       </c>
       <c r="S151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
         <v>0.95</v>
@@ -15571,7 +15579,7 @@
         </is>
       </c>
       <c r="X151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -15590,7 +15598,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Disaster Recovery Data Analysis</t>
+          <t>Numerical Data Analysis</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -15615,7 +15623,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, data reporting</t>
+          <t>["quantitative analysis", "financial modelling", "technical data interpretation", "statistical methods", "data reporting"]</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -15657,7 +15665,7 @@
         </is>
       </c>
       <c r="S152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
         <v>0.92</v>
@@ -15676,7 +15684,7 @@
         </is>
       </c>
       <c r="X152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -15695,7 +15703,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Prevention and Recovery Strategy Formulation</t>
+          <t>Prevention Strategy Formulation</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -15720,7 +15728,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
+          <t>["risk assessment", "mitigation planning", "contingency strategies", "recovery planning", "scenario analysis"]</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -15762,7 +15770,7 @@
         </is>
       </c>
       <c r="S153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T153" t="n">
         <v>0.97</v>
@@ -15781,7 +15789,7 @@
         </is>
       </c>
       <c r="X153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -15800,7 +15808,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Disaster Recovery and Business Continuity Evaluation</t>
+          <t>Disaster Recovery Evaluation</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -15820,12 +15828,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Collects and analyses data, incorporates feedback and refines plans and processes.</t>
+          <t>Collects and analyses data, incorporates feedback, and refines plans and processes.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>data analysis, feedback loops, process improvement, root‑cause analysis, continuous improvement</t>
+          <t>["data analysis", "feedback loops", "process improvement", "root\u2011cause analysis", "continuous improvement"]</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -15874,7 +15882,7 @@
         <v>1</v>
       </c>
       <c r="T154" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -15882,7 +15890,7 @@
         </is>
       </c>
       <c r="V154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" t="inlineStr">
         <is>
@@ -15890,7 +15898,7 @@
         </is>
       </c>
       <c r="X154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -15909,7 +15917,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Disaster Recovery and Risk Analysis</t>
+          <t>Business Continuity Risk Analysis</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -15929,12 +15937,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
+          <t>Conducts thorough risk assessments and creates disaster recovery and contingency solutions.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
+          <t>["risk assessment", "disaster recovery", "contingency planning", "business continuity", "threat modelling"]</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -15987,7 +15995,7 @@
         </is>
       </c>
       <c r="V155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" t="inlineStr">
         <is>
@@ -15995,7 +16003,7 @@
         </is>
       </c>
       <c r="X155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -16014,7 +16022,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Stakeholder Communication and Feedback Management</t>
+          <t>Stakeholder Communication Process</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16034,12 +16042,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Engages stakeholders through timely document submission, feedback collection and response.</t>
+          <t>Engages stakeholders by submitting documents on time, collecting feedback and responding promptly.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback loops, document management, communication protocols, collaboration tools</t>
+          <t>["stakeholder engagement", "feedback loops", "document management", "communication protocols", "collaboration tools"]</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -16084,7 +16092,7 @@
         <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -16092,7 +16100,7 @@
         </is>
       </c>
       <c r="V156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W156" t="inlineStr">
         <is>
@@ -16100,7 +16108,7 @@
         </is>
       </c>
       <c r="X156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -16119,7 +16127,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Disaster Recovery Planning</t>
+          <t>Strategic Disaster Recovery Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -16144,7 +16152,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>priority alignment, outcome mapping, roadmap development, performance metrics, scenario analysis</t>
+          <t>["priority alignment", "outcome mapping", "roadmap development", "performance metrics", "scenario analysis"]</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -16205,7 +16213,7 @@
         </is>
       </c>
       <c r="X157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -16224,7 +16232,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Effective Team Collaboration</t>
+          <t>Disaster Recovery Planning</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -16244,12 +16252,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Collaborates with team members using communication tools and strategies to maintain effective working relationships.</t>
+          <t>Works with team members using communication tools and strategies to keep effective working relationships.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
+          <t>["communication tools", "relationship building", "stakeholder engagement", "collaboration platforms", "interpersonal communication"]</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -16294,7 +16302,7 @@
         <v>1</v>
       </c>
       <c r="T158" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -16302,7 +16310,7 @@
         </is>
       </c>
       <c r="V158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W158" t="inlineStr">
         <is>
@@ -16310,7 +16318,7 @@
         </is>
       </c>
       <c r="X158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -16329,7 +16337,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Evaluation and Strategy Documentation</t>
+          <t>Technical Evaluation Documentation</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -16349,12 +16357,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Prepares evaluation and strategy documents outlining findings and recommendations for stakeholders.</t>
+          <t>Prepares evaluation and strategy documents that outline findings and recommendations for stakeholders.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
+          <t>["specification drafting", "process documentation", "evaluation reporting", "strategic articulation", "document control"]</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -16407,7 +16415,7 @@
         </is>
       </c>
       <c r="V159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W159" t="inlineStr">
         <is>
@@ -16415,7 +16423,7 @@
         </is>
       </c>
       <c r="X159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -16434,7 +16442,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Threat Assessment and Evaluation</t>
+          <t>Threat Assessment</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -16454,12 +16462,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Assesses system vulnerabilities through structured threat identification and analysis to support mitigation planning.</t>
+          <t>Identifies system weaknesses by structuring threat identification and analysis to guide mitigation planning.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>risk analysis, vulnerability assessment, threat modelling, cyber security, intelligence gathering</t>
+          <t>["risk analysis", "vulnerability assessment", "threat modelling", "cyber security", "intelligence gathering"]</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -16501,7 +16509,7 @@
         </is>
       </c>
       <c r="S160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
         <v>0.95</v>
@@ -16512,7 +16520,7 @@
         </is>
       </c>
       <c r="V160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W160" t="inlineStr">
         <is>
@@ -16520,7 +16528,7 @@
         </is>
       </c>
       <c r="X160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Idea Elicitation</t>
+          <t>Idea Elicitation and Development</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gather others’ views and combine feedback to improve ideas in group discussions.</t>
+          <t>You gather others’ views and use feedback to improve ideas in group discussions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Best Practice Benchmarking</t>
+          <t>Best Practice Comparison</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Compares project concepts with industry best‑practice examples of similar products to identify improvement opportunities.</t>
+          <t>Compares project concepts with industry best‑practice examples of similar products to find improvement opportunities.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="S3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Idea Generation and Presentation</t>
+          <t>Solution Ideation and Development</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Concept Generation and Refinement</t>
+          <t>Concept Generation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Creative Thinking</t>
+          <t>Creative Solution Development</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="S6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compiled Feedback Documentation</t>
+          <t>Feedback Documentation Process</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Records and formats feedback to meet organisational standards, ensuring consistent documentation.</t>
+          <t>Record and format feedback using organisational standards to ensure consistent documentation.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Idea Viability Assessment</t>
+          <t>Concept Viability Analysis</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Systematically compare ideas with identified viability factors to assess them.</t>
+          <t>Compares ideas with identified viability factors to assess their potential.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1281,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Proposal Development and Planning</t>
+          <t>Proposal Preparation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1497,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Solution Research Information</t>
+          <t>Solution Information Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Solution Presentation</t>
+          <t>Solution Selection and Presentation</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1701,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stakeholder Feedback Solicitation</t>
+          <t>Stakeholder Idea Feedback</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Team Solution Facilitation</t>
+          <t>Collaborative Solution Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Leads group discussions, encourages participation, and coordinates tasks to achieve shared outcomes.</t>
+          <t>Guides group discussions, encourages participation, and coordinates tasks to achieve shared outcomes.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Clear Technical Writing</t>
+          <t>Clear Cybersecurity Terminology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
+          <t>Writes workplace documents using precise cybersecurity terminology to clearly convey technical information.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>["cyber security terminology", "technical documentation", "information security policies", "industry standards (ISO 27001, NIST)", "risk assessment reporting"]</t>
+          <t>["cybersecurity terminology", "technical documentation", "information security policies", "industry standards", "risk assessment reporting"]</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Conduct surveys and interviews to assess cyber security awareness in the work area and establish baseline levels.</t>
+          <t>We assess cyber security awareness in the work area using surveys and interviews to set baseline levels.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Improvement Communication</t>
+          <t>Review Outcomes Communication</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="S20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Insight Presentation Delivery</t>
+          <t>Insight Presentation</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Delivers concise insight presentations from reviews and training to designated personnel.</t>
+          <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2646,18 +2646,18 @@
         </is>
       </c>
       <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
+        </is>
+      </c>
+      <c r="V21" t="b">
         <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
-        </is>
-      </c>
-      <c r="V21" t="b">
-        <v>1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Legislation Interpretation</t>
+          <t>Data Protection Legislation Awareness</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="S22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0.92</v>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cybersecurity Policy Contribution</t>
+          <t>Policy Development and Communication</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cyber Security Collaboration</t>
+          <t>Cyber Security Awareness Collaboration</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3389,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Technology Platform Utilisation</t>
+          <t>Cyber Security Platform Utilisation</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
+          <t>Choose and run platforms that support cyber security awareness across the work area.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="S29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0.92</v>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="V29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Threat Trend Analysis</t>
+          <t>Cyber Threat Trend Analysis</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
         <v>0.95</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Training Coordination and Record Keeping</t>
+          <t>Training Coordination and Record Management</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3713,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Unnamed Skill</t>
+          <t>Skill Identification</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NaN Value</t>
+          <t>Skill Naming</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Anti‑Malware Deployment</t>
+          <t>Anti-Malware Installation</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Installs and configures up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
+          <t>Install and configure up‑to‑date anti‑malware on all workstations for continuous protection.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="V34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Security Configuration</t>
+          <t>Device Configuration and Update</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4120,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Device Inventory Register</t>
+          <t>Device Register Management</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Digital Device Security Planning</t>
+          <t>Physical Security Planning and Communication</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Creates physical security plans and shares them across the organisation to ensure coordinated protection.</t>
+          <t>Creates detailed physical security plans and shares them across the organisation to ensure coordinated protection.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4653,7 +4653,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Device Risk Level Categorisation</t>
+          <t>Device Risk Categorisation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physical Security Plan Communication</t>
+          <t>Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Provides organisation‑wide briefings on physical security plans to improve understanding and compliance.</t>
+          <t>Delivers organisation‑wide briefings on physical security plans to support understanding and compliance.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="S43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Security Strategy Selection Support</t>
+          <t>Security Strategy Support</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Provides advice to the organisation by evaluating options and recommending the best security strategies.</t>
+          <t>Advises the organisation by evaluating options and recommending the best security strategies.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="S45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Trend Monitoring</t>
+          <t>Digital Security Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="S46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Software Patch Application</t>
+          <t>Software Patch Deployment</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="S47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Strategic Action Plan</t>
+          <t>Action Plan Development</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Creates detailed action plans that match policies, set priorities, and schedule implementation tasks.</t>
+          <t>Creates detailed action plans that follow policies, set priorities, and schedule implementation tasks.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="S49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0.95</v>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Digital Technology Utilisation</t>
+          <t>Strategic ICT Utilisation and Evaluation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="S51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Evaluation Process Documentation</t>
+          <t>Evaluation Process Document</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5780,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Impact Evaluation</t>
+          <t>Strategic Impact Assessment</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="S54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
         <v>0.92</v>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Innovative Idea Evaluation</t>
+          <t>Innovative Process Improvement Investigation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Financial Impact Analysis</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="S56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
         <v>0.97</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Strategic Action Plan Detailing</t>
+          <t>Strategic Plan Review</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
+          <t>Assesses policy compliance by documenting standards, targets and implementation approaches in action plans.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="V57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Project Action Planning</t>
+          <t>Action Plan Development</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6360,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Implementation Difficulty Evaluation</t>
+          <t>Implementation Difficulty Assessment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Assesses the complexity of ICT system changes and plans risk mitigation strategies across hybrid environments.</t>
+          <t>Evaluates how complex ICT system changes are and plans ways to reduce risk in hybrid environments.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6452,7 +6452,7 @@
         <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="V59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Strategic Change Reporting</t>
+          <t>Strategic Change Gap Report</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6556,7 +6556,7 @@
         <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Current Strategic Plan Evaluation</t>
+          <t>Strategic Plan Evaluation</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6664,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Strategic Decision Analysis</t>
+          <t>Systematic Strategic Decision Making</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6756,7 +6756,7 @@
         <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technical Communication</t>
+          <t>Technical Communication Strategy</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="S63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
         <v>0.95</v>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Complex Text Legislative Analysis</t>
+          <t>Legislative Text Analysis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6941,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Privacy Policy Compliance Review</t>
+          <t>Privacy Policy Compliance Assessment</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ethics, IP, and Privacy Application</t>
+          <t>Ethical Policy Review</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7127,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Feedback Management</t>
+          <t>Grievance Feedback Management</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7313,7 +7313,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Information Synthesis for Policy Development</t>
+          <t>Information Synthesis and Integration</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Combines diverse sources into clear written reports using specialised terminology and supporting documentation.</t>
+          <t>Combines diverse sources into clear written reports, using specialised terms and supporting documents.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7406,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>IP Legislation Identification</t>
+          <t>Intellectual Property Policy Analysis</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7499,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Policy Distribution to Personnel</t>
+          <t>Policy and Procedure Distribution</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Privacy Policy and Ethics Documentation</t>
+          <t>IP, Ethics, and Privacy Policy Update</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Update privacy policies, procedures and codes of ethics to match current legislation and compliance requirements.</t>
+          <t>Updates privacy policies, procedures and codes of ethics to meet current legislation and compliance requirements.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Review and Grievance Procedure</t>
+          <t>Review and Grievance Process</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Creates, records and sends review and grievance procedures to the appointed staff.</t>
+          <t>Creates, records and sends review and grievance procedures to the designated staff.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Project Planning and Communication Management</t>
+          <t>Project Sequencing and Monitoring</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Create schedules for complex activities, monitor progress, and coordinate communication to keep delivery moving forward.</t>
+          <t>Sequences and schedules complex activities, monitors progress, and coordinates communication to keep delivery momentum.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Regulatory Monitoring</t>
+          <t>Legislative Change Analysis</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7961,10 +7961,10 @@
         </is>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Digital Ethics and Privacy Management</t>
+          <t>Digital Information Ethics</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8057,7 +8057,7 @@
         <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Stakeholder Policy Distribution</t>
+          <t>Policy Distribution</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Distribute updated policies to stakeholders following organisational protocols.</t>
+          <t>Distributes updated policies to stakeholders following organisational protocols.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Verbal Communication Participation</t>
+          <t>Verbal Interaction</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Blockchain Solution Development</t>
+          <t>Blockchain Platform Implementation</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8336,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Problem Solving</t>
+          <t>Anomaly Detection and Remediation</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Detects and fixes blockchain anomalies by analysing context to spot subtle deviations.</t>
+          <t>Detects blockchain anomalies and resolves them using contextual analysis to spot subtle deviations.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="S80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
         <v>0.97</v>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Consensus Mechanism Implementation</t>
+          <t>Consensus Portal Implementation</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Configures and deploys system components to implement consensus mechanisms.</t>
+          <t>Configures and deploys system components to enable consensus mechanisms.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="S82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
         <v>0.95</v>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Design Documentation Preparation</t>
+          <t>Design Documentation</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Creates detailed design documents that meet organisational requirements and support project delivery.</t>
+          <t>Creates detailed design documentation that meets organisational requirements and supports project delivery.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="S83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Documentation Submission</t>
+          <t>Documentation Submission and Feedback</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Submit documentation for review, seek feedback and incorporate approved amendments.</t>
+          <t>Submit documentation for review, seek feedback, and incorporate approved amendments.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="S84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
         <v>0.97</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Maintenance Schedule Documentation</t>
+          <t>Maintenance Schedule Planning</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8984,10 +8984,10 @@
         </is>
       </c>
       <c r="S86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Security Platform Selection</t>
+          <t>Blockchain Security Platform Selection</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Selects and configures security platforms for blockchain solutions based on risk assessments.</t>
+          <t>Choose and set up security platforms for blockchain solutions using risk assessments.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="S88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" t="n">
         <v>0.97</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="V88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Smart Contract Execution</t>
+          <t>Blockchain Solution Execution</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="S89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Blockchain Solution Debugging</t>
+          <t>Solution Debugging and Scaling</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Identifies and fixes blockchain solution problems, then improves performance for scalable deployment.</t>
+          <t>Diagnoses and resolves blockchain solution issues and optimises performance for scalable deployment.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9359,7 +9359,7 @@
         <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="V90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Organisational Performance Testing</t>
+          <t>Solution Performance Testing</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="S91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Stakeholder Oral Communication</t>
+          <t>Requirements Confirmation</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="S92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Threat Data Ingestion Platform</t>
+          <t>Threat Data Management</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>The system ingests data logs into analytics platforms to support monitoring and analysis.</t>
+          <t>Ingest data logs into analytics platforms as instructed to support monitoring and analysis.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Compliance Threat Data Identification</t>
+          <t>Threat Data Collection and Interpretation</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Identifies legislation and internal policies that govern the collection, analysis and use of threat data.</t>
+          <t>Identifies relevant legislation and internal policies that govern the collection, analysis and use of threat data.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9850,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>["data validation", "anomaly detection", "data quality", "data auditing", "profiling"]</t>
+          <t>["data validation", "anomaly detection", "data quality", "data auditing", "data profiling"]</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Threat Data Set Procedure</t>
+          <t>Threat Data Collection Procedure</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Collect alerts, logs and event reports and organise them into structured data sets following organisational policies.</t>
+          <t>Collect alerts, logs and event reports and organise them into structured datasets following organisational policies.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>False Positive Detection</t>
+          <t>False Positive/Negative Review</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Reviews test results to identify and correct false positives and false negatives.</t>
+          <t>Reviews test results to find and fix false positives and false negatives.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="S98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="n">
         <v>0.97</v>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="V98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>1</v>
       </c>
       <c r="T99" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Threat Mitigation Strategy Recommendation</t>
+          <t>Threat Data Mitigation Recommendation</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10374,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="T100" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Risk Likelihood Assessment</t>
+          <t>Risk Likelihood and Impact Assessment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Evaluates threats by judging their likelihood and impact to set risk mitigation priorities.</t>
+          <t>Evaluates threats by judging how likely they are and how much impact they could cause, then prioritises actions to reduce risk.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="S101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" t="n">
         <v>0.92</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Security Equipment Identification</t>
+          <t>Security Equipment Inventory</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="S102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>1</v>
       </c>
       <c r="T104" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Threat Data Gathering</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="S105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Infrastructure Asset Management Implementation</t>
+          <t>Protection and Asset Management</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11080,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Research</t>
+          <t>Critical Infrastructure Protection Strategy</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="S108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" t="n">
         <v>0.97</v>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Data Backup Strategy</t>
+          <t>Data Backup</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Device Security Measures</t>
+          <t>Device Security Implementation</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11356,10 +11356,10 @@
         </is>
       </c>
       <c r="S110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Protection Plan Feedback Management</t>
+          <t>Protection Plan Feedback</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11452,7 +11452,7 @@
         <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Network Segmentation Deployment</t>
+          <t>Critical Infrastructure Network Segmentation</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Deploys network segmentation to isolate security zones according to approved protection plans.</t>
+          <t>Implements network segmentation to isolate security zones according to approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -11542,10 +11542,10 @@
         </is>
       </c>
       <c r="S112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Protection Strategy Development</t>
+          <t>Operational Detail Development</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Creates staged operational plans and reviews priorities and performance throughout execution.</t>
+          <t>Creates staged operational plans and reviews priorities and performance while executing.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -11638,7 +11638,7 @@
         <v>1</v>
       </c>
       <c r="T113" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Protection Plan</t>
+          <t>Critical Infrastructure Protection Strategy</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Creates and documents protection plans for critical infrastructure that follow organisational policies and procedures.</t>
+          <t>Creates and documents protection plans that match organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11824,7 +11824,7 @@
         <v>1</v>
       </c>
       <c r="T115" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Protection Plan Deployment Test</t>
+          <t>Protection Plan Test</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12010,7 +12010,7 @@
         <v>1</v>
       </c>
       <c r="T117" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Software Patch Deployment</t>
+          <t>Software Patch Implementation</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Technical Documentation for Infrastructure Protection</t>
+          <t>Critical Infrastructure Documentation</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data Classification Identification</t>
+          <t>Data Type Catalog</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12394,7 +12394,7 @@
         </is>
       </c>
       <c r="S121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T121" t="n">
         <v>0.95</v>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Feedback Management</t>
+          <t>Initial Design Feedback</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12501,7 +12501,7 @@
         <v>1</v>
       </c>
       <c r="T122" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Industry Design Methodology Research</t>
+          <t>Industry Design Methodologies</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12601,7 +12601,7 @@
         <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Contextual Anomaly Detection</t>
+          <t>Anomaly Detection in Security</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12813,7 +12813,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Security Architecture Presentation</t>
+          <t>Security Architecture Report</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Creates and delivers documented security architecture presentations to engage stakeholders.</t>
+          <t>Prepares and delivers documented security architecture presentations for stakeholder engagement.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -12914,7 +12914,7 @@
         </is>
       </c>
       <c r="S126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" t="n">
         <v>0.95</v>
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="V126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W126" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Security Design Validation</t>
+          <t>Security Design Methodology Utilisation</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Validates security designs using industry‑recognised methods.</t>
+          <t>Validates security designs using recognised industry methods.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -13018,10 +13018,10 @@
         </is>
       </c>
       <c r="S127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Security Level Determination</t>
+          <t>Security Level Definition</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="S128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Security Architecture Design</t>
+          <t>Security Architecture Planning</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13237,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="T129" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Complex Documentation Preparation</t>
+          <t>Security Architecture Documentation</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13553,7 +13553,7 @@
         <v>1</v>
       </c>
       <c r="T132" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Documentation Interpretation</t>
+          <t>Technical Requirements Interpretation</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Autonomous Decision Making</t>
+          <t>Autonomous Decision‑Making for Incident Response</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13763,7 +13763,7 @@
         </is>
       </c>
       <c r="S134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" t="n">
         <v>0.92</v>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Forensic Evidence Collection Procedure Development</t>
+          <t>Forensic Evidence Handling</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Designs and implements forensic evidence collection processes to preserve data during incident response.</t>
+          <t>Designs and implements processes to collect forensic evidence and preserve data during incident response.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="V135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Incident Response Evaluation</t>
+          <t>Incident Response Plan Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Assesses incident response plans for effectiveness in hybrid operating environments.</t>
+          <t>Evaluates incident response plans for effectiveness across hybrid operating environments.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -14074,7 +14074,7 @@
         </is>
       </c>
       <c r="S137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" t="n">
         <v>0.97</v>
@@ -14085,7 +14085,7 @@
         </is>
       </c>
       <c r="V137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W137" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Incident Response Team Services</t>
+          <t>Incident Team Coordination</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Document incident response team roles and services to support coordinated response.</t>
+          <t>Document incident response team roles and services to support a coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -14280,10 +14280,10 @@
         </is>
       </c>
       <c r="S139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Incident Response Red‑Team Planning</t>
+          <t>Comprehensive Incident Response Exercise Design</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Risk Data Analysis</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14599,10 +14599,10 @@
         </is>
       </c>
       <c r="S142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T142" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Incident Response Management</t>
+          <t>Incident Response Application</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Executes incident response actions following approved response plans.</t>
+          <t>Runs incident response actions following approved response plans.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -14711,7 +14711,7 @@
         <v>1</v>
       </c>
       <c r="T143" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Creates and records incident management policies that match organisational specifications.</t>
+          <t>Creates and writes incident management policies that match organisational specifications.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -14820,7 +14820,7 @@
         <v>1</v>
       </c>
       <c r="T144" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Business Continuity Impact Evaluation</t>
+          <t>Business Continuity Assessment</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Evaluates system impacts on business continuity, identifies risks and develops mitigation strategies.</t>
+          <t>Evaluates system impacts on business continuity, identifies risks and suggests mitigation strategies.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Disaster Recovery Planning</t>
+          <t>Regulatory Compliance Strategy</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15139,7 +15139,7 @@
         <v>1</v>
       </c>
       <c r="T147" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cost Constraint Analysis</t>
+          <t>Prevention and Recovery Options Assessment</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Evaluates options to prevent and recover while meeting compliance and cost effectiveness.</t>
+          <t>Evaluates options to prevent and recover, ensuring compliance and cost effectiveness.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -15350,10 +15350,10 @@
         </is>
       </c>
       <c r="S149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T149" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Industry Standards Review</t>
+          <t>Disaster Recovery Review</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15560,7 +15560,7 @@
         </is>
       </c>
       <c r="S151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T151" t="n">
         <v>0.95</v>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Numerical Data Analysis</t>
+          <t>Numerical System Data Analysis</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -15665,7 +15665,7 @@
         </is>
       </c>
       <c r="S152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" t="n">
         <v>0.92</v>
@@ -15703,7 +15703,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Prevention Strategy Formulation</t>
+          <t>Prevention and Recovery Strategy</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -15770,10 +15770,10 @@
         </is>
       </c>
       <c r="S153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Disaster Recovery Evaluation</t>
+          <t>Business Continuity Evaluation and Recovery Strategy</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -15882,7 +15882,7 @@
         <v>1</v>
       </c>
       <c r="T154" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Business Continuity Risk Analysis</t>
+          <t>Risk Analysis and Recovery Planning</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Stakeholder Communication Process</t>
+          <t>Stakeholder Communication Management</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16092,7 +16092,7 @@
         <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Disaster Recovery Planning</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Develops and aligns hybrid work priorities and outcomes through structured strategic planning.</t>
+          <t>Creates hybrid work priorities and outcomes by using structured strategic planning.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -16194,7 +16194,7 @@
         </is>
       </c>
       <c r="S157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
         <v>0.92</v>
@@ -16205,7 +16205,7 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Disaster Recovery Planning</t>
+          <t>System Impact and Recovery Planning</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Technical Evaluation Documentation</t>
+          <t>Evaluation and Strategy Documentation</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -16407,7 +16407,7 @@
         <v>1</v>
       </c>
       <c r="T159" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>

--- a/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Idea Elicitation and Development</t>
+          <t>Viewpoint Elicitation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>You gather others’ views and use feedback to improve ideas in group discussions.</t>
+          <t>Collects others' views and integrates feedback to improve ideas during collaborative discussions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>["communication", "empathy", "feedback", "stakeholder engagement", "interpersonal skills"]</t>
+          <t>communication, empathy, feedback, stakeholder engagement, interpersonal skills</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -696,12 +696,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Compares project concepts with industry best‑practice examples of similar products to find improvement opportunities.</t>
+          <t>Compares project concepts with industry best‑practice examples of similar products to identify improvement opportunities.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>["benchmarking", "best practice", "performance metrics", "competitive analysis", "industry standards"]</t>
+          <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="X3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -788,7 +788,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Solution Ideation and Development</t>
+          <t>Idea Generation</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>["ideation", "creative problem solving", "mind mapping", "group facilitation", "innovation techniques"]</t>
+          <t>ideation, creative problem solving, mind mapping, group facilitation, innovation techniques</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="X4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -900,7 +900,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Concept Generation</t>
+          <t>Concept Generation and Evaluation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Uses systematic analytical methods to collect and assess concepts in complex, non‑routine scenarios.</t>
+          <t>Applies systematic analytical methods to collect and assess concepts in complex, non‑routine scenarios.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>["analytical methodology", "systematic concept evaluation", "ideation processes", "feasibility analysis", "design thinking"]</t>
+          <t>analytical methodology, systematic concept evaluation, ideation processes, feasibility analysis, design thinking</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="X5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Creative Solution Development</t>
+          <t>Solution Generation</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Uses creative thinking techniques to develop innovative solutions for workplace challenges.</t>
+          <t>Applies creative thinking techniques to develop innovative solutions for workplace challenges.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>["ideation", "innovation", "brainstorming", "design thinking", "problem solving"]</t>
+          <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="X6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Feedback Documentation Process</t>
+          <t>Feedback Documentation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Record and format feedback using organisational standards to ensure consistent documentation.</t>
+          <t>Record and format feedback according to organisational standards for consistent documentation.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>["record\u2011keeping", "compliance", "audit trail", "quality assurance", "organisational standards"]</t>
+          <t>record‑keeping, compliance, audit trail, quality assurance, organisational standards</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="S7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="X7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Concept Viability Analysis</t>
+          <t>Viability Evaluation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Compares ideas with identified viability factors to assess their potential.</t>
+          <t>Systematically compares ideas against identified viability factors to assess them.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>["feasibility analysis", "risk assessment", "criteria weighting", "business case evaluation", "market viability"]</t>
+          <t>feasibility analysis, risk assessment, criteria weighting, business case evaluation, market viability</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="X8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Works with relevant staff to identify and choose consultation issues for focused analysis.</t>
+          <t>Works with relevant personnel to identify and select consultation issues for focused analysis.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>["stakeholder engagement", "problem identification", "needs assessment", "consultation processes", "decision\u2011making"]</t>
+          <t>stakeholder engagement, problem identification, needs assessment, consultation processes, decision‑making</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="X9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Proposal Preparation</t>
+          <t>Proposal Development</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>["stakeholder communication", "business case development", "grant and RFP responses", "technical documentation", "persuasive writing"]</t>
+          <t>stakeholder communication, business case development, grant and RFP responses, technical documentation, persuasive writing</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1497,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="X10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Solution Information Research</t>
+          <t>Solution Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Collects and assesses data to find workable solutions for the identified problem.</t>
+          <t>Collects and evaluates data to identify viable solutions for the issue.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>["literature review", "data collection", "search strategies", "online databases", "evidence\u2011based analysis"]</t>
+          <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="X11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Solution Selection and Presentation</t>
+          <t>Solution Presentation</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Chooses suitable solution formats and delivers customised presentations to stakeholders.</t>
+          <t>Choose suitable solution formats and deliver tailored presentations to stakeholders.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>["stakeholder communication", "visual presentation tools", "solution pitching", "format selection", "business briefings"]</t>
+          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="X12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
+          <t>Iteratively refine and finalise solutions to meet specific task requirements.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>["requirements analysis", "design optimisation", "prototype testing", "continuous improvement", "validation feedback"]</t>
+          <t>requirements analysis, design optimisation, prototype testing, continuous improvement, validation feedback</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="V13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="X13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Solution Viability Assessment</t>
+          <t>Viability Assessment</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>["feasibility analysis", "constraint identification", "business issue evaluation", "risk assessment", "decision matrices"]</t>
+          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="X14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stakeholder Idea Feedback</t>
+          <t>Feedback Solicitation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>["stakeholder engagement", "feedback collection", "surveys", "interviews", "communication"]</t>
+          <t>stakeholder engagement, feedback collection, surveys, interviews, communication</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="S15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="X15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Collaborative Solution Facilitation</t>
+          <t>Group Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>["group dynamics", "collaboration tools", "meeting facilitation", "conflict resolution", "consensus building"]</t>
+          <t>group dynamics, collaboration tools, meeting facilitation, conflict resolution, consensus building</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -2125,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="X16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cyber Security Awareness Program</t>
+          <t>Security Awareness Program Development</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Designs, implements and updates organisation‑wide cyber security awareness programmes following best practice.</t>
+          <t>Designs, implements and updates organisation‑wide cyber security awareness programmes in line with best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>["cyber security", "security awareness training", "risk management", "phishing simulations", "compliance governance"]</t>
+          <t>cyber security, security awareness training, risk management, phishing simulations, compliance governance</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="X17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Clear Cybersecurity Terminology</t>
+          <t>Technical Writing</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Writes workplace documents using precise cybersecurity terminology to clearly convey technical information.</t>
+          <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>["cybersecurity terminology", "technical documentation", "information security policies", "industry standards", "risk assessment reporting"]</t>
+          <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="V18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="X18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cyber Security Awareness Assessment</t>
+          <t>Security Awareness Assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>We assess cyber security awareness in the work area using surveys and interviews to set baseline levels.</t>
+          <t>We assess cyber security awareness in the work area using surveys and interviews to establish a baseline level.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>["cyber security awareness", "risk awareness", "security posture", "threat intelligence", "security metrics"]</t>
+          <t>cyber security, risk awareness, security posture, threat intelligence, security metrics</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2445,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="X19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Review Outcomes Communication</t>
+          <t>Security Improvement Communication</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>["cyber security", "policy compliance", "risk communication", "security standards", "stakeholder reporting"]</t>
+          <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="X20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>["stakeholder communication", "knowledge transfer", "visual storytelling", "training briefings", "presentation tools"]</t>
+          <t>stakeholder communication, knowledge transfer, visual storytelling, training briefings, presentation tools</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="X21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Data Protection Legislation Awareness</t>
+          <t>Data Breach Legislation Interpretation</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Interprets Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
+          <t>Interprets the Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>["Notifiable Data Breach", "Australian Privacy Act", "data protection compliance", "privacy law interpretation", "regulatory risk assessment"]</t>
+          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="V22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="X22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Outcome Documentation</t>
+          <t>Outcome Reporting</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>["reporting", "review outcomes", "improvement recommendations", "stakeholder communication", "record\u2011keeping"]</t>
+          <t>reporting, review outcomes, improvement recommendations, stakeholder communication, record‑keeping</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="S23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0.97</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="X23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Policy Development and Communication</t>
+          <t>Policy Drafting</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>["cyber security governance", "policy development", "risk management", "compliance frameworks", "stakeholder communication"]</t>
+          <t>cyber security governance, policy development, risk management, compliance frameworks, stakeholder communication</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="X24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cyber Security Practice Review</t>
+          <t>Security Practice Review</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Systematically reviews cyber security practices to ensure they align with organisational policies and procedures.</t>
+          <t>Systematically review cyber security practices to ensure they align with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>["cyber security", "policy compliance", "risk assessment", "security governance", "audit controls"]</t>
+          <t>cyber security, policy compliance, risk assessment, security governance, audit controls</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -3077,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="X25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cyber Security Record Keeping</t>
+          <t>Record Keeping</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Keeps cyber security protection records current by organising and documenting relevant data.</t>
+          <t>Maintains up‑to‑date cyber security protection records by organising and documenting relevant data.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>["cyber security documentation", "information security records", "compliance logging", "data governance", "audit trail management"]</t>
+          <t>cyber security documentation, information security records, compliance logging, data governance, audit trail management</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -3185,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="V26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="X26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Engages relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
+          <t>Engage relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>["stakeholder engagement", "consultation workshops", "decision support", "needs analysis", "facilitation"]</t>
+          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="V27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="X27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cyber Security Awareness Collaboration</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>["interdisciplinary teamwork", "cyber security coordination", "cross\u2011functional communication", "stakeholder engagement", "collaboration tools"]</t>
+          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, collaboration tools</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -3389,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="X28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cyber Security Platform Utilisation</t>
+          <t>Security Platform Utilisation</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Choose and run platforms that support cyber security awareness across the work area.</t>
+          <t>Select and operate suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>["cyber security", "security platforms", "SIEM", "threat monitoring", "information security"]</t>
+          <t>cyber security, security platforms, SIEM, threat monitoring, information security</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="X29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cyber Threat Trend Analysis</t>
+          <t>Threat Trend Review</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>["cyber security", "threat intelligence", "trend monitoring", "vulnerability assessment", "security analytics"]</t>
+          <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3605,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="X30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Training Coordination and Record Management</t>
+          <t>Training Coordination</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coordinates training sessions and updates information by scheduling, delivering and recording activities.</t>
+          <t>Coordinates training sessions and information updates by scheduling, delivering and recording activities.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>["training schedules", "learning management systems", "record management", "information updates", "training logistics"]</t>
+          <t>training schedules, learning management systems, record management, information updates, training logistics</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="V31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="X31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3740,18 +3740,14 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Skill Identification</t>
+          <t>Nan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -3766,10 +3762,10 @@
         </is>
       </c>
       <c r="S32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="b">
@@ -3788,18 +3784,14 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Skill Naming</t>
+          <t>Nan</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -3814,10 +3806,10 @@
         </is>
       </c>
       <c r="S33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="b">
@@ -3869,7 +3861,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>["cyber security", "endpoint protection", "malware scanning", "signature updates", "security hygiene"]</t>
+          <t>cyber security, endpoint protection, malware scanning, signature updates, security hygiene</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -3914,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3930,7 +3922,7 @@
         </is>
       </c>
       <c r="X34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3949,7 +3941,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Breach Impact Assessment</t>
+          <t>Impact Analysis</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3974,7 +3966,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>["risk assessment", "incident tracking", "business impact analysis", "compliance reporting", "security metrics"]</t>
+          <t>risk assessment, incident tracking, business impact analysis, compliance reporting, security metrics</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -4019,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -4035,7 +4027,7 @@
         </is>
       </c>
       <c r="X35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4054,7 +4046,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration and Update</t>
+          <t>Device Configuration</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4074,12 +4066,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sets up new devices by updating firmware and configuring settings.</t>
+          <t>Set up new devices by updating firmware and configuring settings.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>["device provisioning", "firmware updates", "configuration management", "hardware initialisation", "system onboarding"]</t>
+          <t>device provisioning, firmware updates, configuration management, hardware initialisation, system onboarding</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -4136,7 +4128,7 @@
         </is>
       </c>
       <c r="X36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4155,7 +4147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Device Encryption Implementation</t>
+          <t>Device Encryption</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4180,7 +4172,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>["encryption", "device security", "endpoint encryption", "mobile device management", "cryptography"]</t>
+          <t>encryption, device security, endpoint encryption, mobile device management, cryptography</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -4218,10 +4210,10 @@
         </is>
       </c>
       <c r="S37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -4237,7 +4229,7 @@
         </is>
       </c>
       <c r="X37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4256,7 +4248,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Device Register Management</t>
+          <t>Register Maintenance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4276,12 +4268,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
+          <t>Create and update a register of networked devices to support inventory tracking and asset management.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>["IT asset tracking", "hardware registers", "network inventories", "CMDB", "asset management software"]</t>
+          <t>IT asset tracking, hardware registers, network inventories, CMDB, asset management software</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -4334,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -4342,7 +4334,7 @@
         </is>
       </c>
       <c r="V38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4350,7 +4342,7 @@
         </is>
       </c>
       <c r="X38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4369,7 +4361,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Security Gap Analysis</t>
+          <t>Gap Analysis</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4394,7 +4386,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>["benchmarking", "performance metrics", "best\u2011practice assessment", "process improvement", "effectiveness evaluation"]</t>
+          <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -4443,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -4459,7 +4451,7 @@
         </is>
       </c>
       <c r="X39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4478,7 +4470,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Strong Password Creation</t>
+          <t>Password Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4498,12 +4490,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Creates strong, unique passwords for personal and work accounts that meet approved complexity rules.</t>
+          <t>Creates strong, unique passwords for personal and work accounts that meet approved complexity criteria.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>["authentication", "password complexity", "entropy", "cyber security", "password managers"]</t>
+          <t>authentication, password complexity, entropy, cyber security, password managers</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -4560,7 +4552,7 @@
         </is>
       </c>
       <c r="X40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4579,7 +4571,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Physical Security Planning and Communication</t>
+          <t>Security Planning</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4599,12 +4591,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Creates detailed physical security plans and shares them across the organisation to ensure coordinated protection.</t>
+          <t>Creates physical security plans and shares them across the organisation to ensure coordinated protection.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>["risk assessment", "access control systems", "security policy development", "facility protection", "stakeholder communication"]</t>
+          <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -4650,10 +4642,10 @@
         </is>
       </c>
       <c r="S41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -4669,7 +4661,7 @@
         </is>
       </c>
       <c r="X41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4688,7 +4680,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Device Risk Categorisation</t>
+          <t>Risk Categorisation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4708,12 +4700,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Evaluates how sensitive device data are and assigns a risk category for security management.</t>
+          <t>Assesses device data sensitivity and assigns a risk category for security management.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>["risk assessment", "information sensitivity", "device classification", "cyber security", "risk matrices"]</t>
+          <t>risk assessment, information sensitivity, device classification, cyber security, risk matrices</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -4774,7 +4766,7 @@
         </is>
       </c>
       <c r="X42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4793,7 +4785,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Security Plan Briefing</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4818,7 +4810,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>["physical security", "risk assessment", "security policy", "stakeholder communication", "access control"]</t>
+          <t>physical security, risk assessment, security policy, stakeholder communication, access control</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -4864,7 +4856,7 @@
         </is>
       </c>
       <c r="S43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>0.97</v>
@@ -4883,7 +4875,7 @@
         </is>
       </c>
       <c r="X43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4902,7 +4894,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Security Protocol Selection</t>
+          <t>Protocol Selection</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4922,12 +4914,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Choose suitable security protocols for each device to reduce identified risk levels.</t>
+          <t>Selects appropriate security protocols for each device to mitigate identified risk levels.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>["risk assessment", "encryption standards", "device hardening", "cyber security governance", "protocol compliance"]</t>
+          <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -4976,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -4984,7 +4976,7 @@
         </is>
       </c>
       <c r="V44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4992,7 +4984,7 @@
         </is>
       </c>
       <c r="X44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5011,7 +5003,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Security Strategy Support</t>
+          <t>Strategy Evaluation</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5031,12 +5023,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Advises the organisation by evaluating options and recommending the best security strategies.</t>
+          <t>Advises the organisation by evaluating options and recommending optimal security strategies.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>["cyber security governance", "risk assessment", "security frameworks", "threat modelling", "ISO 27001"]</t>
+          <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -5082,10 +5074,10 @@
         </is>
       </c>
       <c r="S45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -5093,7 +5085,7 @@
         </is>
       </c>
       <c r="V45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5101,7 +5093,7 @@
         </is>
       </c>
       <c r="X45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5120,7 +5112,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Digital Security Monitoring</t>
+          <t>Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5140,12 +5132,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Monitors new digital security developments to inform risk assessments and protective measures.</t>
+          <t>Monitors emerging digital security developments to inform risk assessments and protective measures.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>["cyber security", "threat intelligence", "vulnerability tracking", "security intelligence feeds", "digital risk monitoring"]</t>
+          <t>cyber security, threat intelligence, vulnerability tracking, security intelligence feeds, digital risk monitoring</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -5190,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -5198,7 +5190,7 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5206,7 +5198,7 @@
         </is>
       </c>
       <c r="X46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5225,7 +5217,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Software Patch Deployment</t>
+          <t>Patch Installation</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5250,7 +5242,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>["patch management", "software updates", "endpoint management", "mobile device management", "security patches"]</t>
+          <t>patch management, software updates, endpoint management, mobile device management, security patches</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -5299,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -5315,7 +5307,7 @@
         </is>
       </c>
       <c r="X47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5334,7 +5326,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Two‑Factor Authentication Enablement</t>
+          <t>Two-Factor Authentication Enabling</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5359,7 +5351,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>["multi\u2011factor authentication", "MFA", "OTP", "access control", "cyber security"]</t>
+          <t>multi‑factor authentication, MFA, OTP, access control, cyber security</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -5405,7 +5397,7 @@
         </is>
       </c>
       <c r="S48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
         <v>0.97</v>
@@ -5424,7 +5416,7 @@
         </is>
       </c>
       <c r="X48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5463,12 +5455,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Creates detailed action plans that follow policies, set priorities, and schedule implementation tasks.</t>
+          <t>Creates detailed action plans that align with policies, prioritise tasks and schedule implementation.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>["project scheduling", "prioritisation", "policy compliance", "change management", "implementation planning"]</t>
+          <t>project scheduling, prioritisation, policy compliance, change management, implementation planning</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -5516,7 +5508,7 @@
         </is>
       </c>
       <c r="X49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5560,7 +5552,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>["change management", "prioritisation", "opportunity assessment", "implementation scheduling", "project planning"]</t>
+          <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -5593,10 +5585,10 @@
         </is>
       </c>
       <c r="S50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -5612,7 +5604,7 @@
         </is>
       </c>
       <c r="X50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -5631,7 +5623,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Strategic ICT Utilisation and Evaluation</t>
+          <t>Technology Evaluation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5656,7 +5648,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>["data management", "digital collaboration tools", "emerging technologies", "cloud computing", "data visualisation"]</t>
+          <t>data management, digital collaboration tools, emerging technologies, cloud computing, data visualisation</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -5688,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -5704,7 +5696,7 @@
         </is>
       </c>
       <c r="X51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -5723,7 +5715,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Evaluation Process Document</t>
+          <t>Document Preparation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5748,7 +5740,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>["technical writing", "document review", "quality assurance", "reporting standards", "document control"]</t>
+          <t>technical writing, document review, quality assurance, reporting standards, document control</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -5780,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -5796,7 +5788,7 @@
         </is>
       </c>
       <c r="X52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5815,7 +5807,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Analysis</t>
+          <t>Gap Analysis</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5835,12 +5827,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Compares strategic objectives with current ICT capability in hybrid environments, identifies gaps, and proposes improvements.</t>
+          <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>["gap analysis", "strategic alignment", "technology roadmaps", "ICT governance", "digital transformation"]</t>
+          <t>gap analysis, strategic alignment, technology roadmaps, ICT governance, digital transformation</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -5884,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -5892,7 +5884,7 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5900,7 +5892,7 @@
         </is>
       </c>
       <c r="X53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -5919,7 +5911,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Strategic Impact Assessment</t>
+          <t>Impact Evaluation</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5939,12 +5931,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Evaluates proposed ICT system changes in hybrid environments to ensure they align with organisational strategic objectives.</t>
+          <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>["impact assessment", "ICT systems", "strategic alignment", "change management", "performance metrics"]</t>
+          <t>impact assessment, ICT systems, strategic alignment, change management, performance metrics</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -5992,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -6000,7 +5992,7 @@
         </is>
       </c>
       <c r="V54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6008,7 +6000,7 @@
         </is>
       </c>
       <c r="X54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -6027,7 +6019,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Innovative Process Improvement Investigation</t>
+          <t>Idea Evaluation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6047,12 +6039,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Researches and tests new ideas, then applies findings to improve work practices and processes.</t>
+          <t>Researches and tests innovative ideas, then applies findings to refine work practices and processes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>["continuous improvement", "process optimisation", "ideation techniques", "creative problem solving", "innovation management"]</t>
+          <t>continuous improvement, process optimisation, ideation techniques, creative problem solving, innovation management</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -6084,7 +6076,7 @@
         <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -6100,7 +6092,7 @@
         </is>
       </c>
       <c r="X55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6119,7 +6111,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial Impact Analysis</t>
+          <t>Impact Analysis</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6144,7 +6136,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>["financial analysis", "quantitative modelling", "cost\u2011benefit assessment", "Excel", "statistical calculations"]</t>
+          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, statistical calculations</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -6192,7 +6184,7 @@
         </is>
       </c>
       <c r="X56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6211,7 +6203,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Strategic Plan Review</t>
+          <t>Compliance Evaluation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6236,7 +6228,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>["regulatory standards", "compliance frameworks", "risk assessment", "governance risk and compliance", "policy implementation planning"]</t>
+          <t>regulatory standards, compliance frameworks, risk assessment, governance risk and compliance, policy implementation planning</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -6268,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -6284,7 +6276,7 @@
         </is>
       </c>
       <c r="X57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -6303,7 +6295,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Action Plan Development</t>
+          <t>Schedule Planning</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6323,12 +6315,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Creates detailed action plans with prioritised schedules to implement change initiatives efficiently.</t>
+          <t>Creates detailed action plans and prioritised schedules to implement change initiatives efficiently.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>["action planning", "prioritised schedules", "timeline management", "resource allocation", "critical path"]</t>
+          <t>action planning, prioritised schedules, timeline management, resource allocation, critical path</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -6376,7 +6368,7 @@
         </is>
       </c>
       <c r="X58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -6395,7 +6387,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Implementation Difficulty Assessment</t>
+          <t>Change Complexity Assessment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6415,12 +6407,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Evaluates how complex ICT system changes are and plans ways to reduce risk in hybrid environments.</t>
+          <t>Assesses ICT system change complexity and plans risk mitigation strategies across hybrid environments.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>["ICT systems", "change management", "implementation complexity", "risk analysis", "impact assessment"]</t>
+          <t>ICT systems, change management, implementation complexity, risk analysis, impact assessment</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -6468,7 +6460,7 @@
         </is>
       </c>
       <c r="X59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6487,7 +6479,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Strategic Change Gap Report</t>
+          <t>Proposal Reporting</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6512,7 +6504,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>["executive communication", "gap analysis", "change management", "improvement recommendations", "business reporting"]</t>
+          <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -6572,7 +6564,7 @@
         </is>
       </c>
       <c r="X60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -6591,7 +6583,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Strategic Plan Evaluation</t>
+          <t>Plan Evaluation</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6616,7 +6608,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>["strategic alignment", "industry benchmarking", "SWOT analysis", "organisational objectives", "gap analysis"]</t>
+          <t>strategic alignment, industry benchmarking, SWOT analysis, organisational objectives, gap analysis</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -6680,7 +6672,7 @@
         </is>
       </c>
       <c r="X61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -6699,7 +6691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Systematic Strategic Decision Making</t>
+          <t>Decision Analysis</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6724,7 +6716,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>["decision analysis", "analytical reasoning", "structured methodologies", "risk assessment", "scenario modelling"]</t>
+          <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -6772,7 +6764,7 @@
         </is>
       </c>
       <c r="X62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6791,7 +6783,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technical Communication Strategy</t>
+          <t>Technical Communication</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6811,12 +6803,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Translates technical terms into plain English to help diverse staff understand. Uses clear language for all audiences.</t>
+          <t>Translates technical terms into plain English to help diverse staff understand.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>["plain language", "jargon translation", "stakeholder communication", "technical writing", "audience adaptation"]</t>
+          <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -6845,7 +6837,7 @@
         </is>
       </c>
       <c r="S63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
         <v>0.95</v>
@@ -6864,7 +6856,7 @@
         </is>
       </c>
       <c r="X63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -6883,7 +6875,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Legislative Text Analysis</t>
+          <t>Text Evaluation</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6908,7 +6900,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>["legislative compliance", "policy analysis", "regulatory standards", "qualitative analysis"]</t>
+          <t>legislative compliance, policy analysis, regulatory standards, qualitative analysis</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -6941,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -6957,7 +6949,7 @@
         </is>
       </c>
       <c r="X64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -6976,7 +6968,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Privacy Policy Compliance Assessment</t>
+          <t>Policy Compliance Review</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7001,7 +6993,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>["privacy policy", "regulatory standards", "risk assessment", "audit", "data protection"]</t>
+          <t>privacy policy, regulatory standards, risk assessment, audit, data protection</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -7050,7 +7042,7 @@
         </is>
       </c>
       <c r="X65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -7069,7 +7061,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ethical Policy Review</t>
+          <t>Ethics Code Application</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7094,7 +7086,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>["professional ethics", "codes of conduct", "compliance", "organisational governance", "ethical frameworks"]</t>
+          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical frameworks</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -7127,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -7143,7 +7135,7 @@
         </is>
       </c>
       <c r="X66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -7162,7 +7154,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Grievance Feedback Management</t>
+          <t>Feedback Collection and Response</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7182,12 +7174,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Collects and addresses feedback on review and grievance documentation from designated personnel.</t>
+          <t>Collect feedback on review and grievance documents from designated personnel and address it promptly.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>["grievance procedures", "review processes", "stakeholder communication", "document management", "complaint handling"]</t>
+          <t>grievance procedures, review processes, stakeholder communication, document management, complaint handling</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -7220,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -7228,7 +7220,7 @@
         </is>
       </c>
       <c r="V67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -7236,7 +7228,7 @@
         </is>
       </c>
       <c r="X67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -7255,7 +7247,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Information Security Testing</t>
+          <t>Security Testing</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7275,12 +7267,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Conducts industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
+          <t>Conduct industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>["penetration testing", "vulnerability assessment", "ISO 27001", "CIA triad", "security controls"]</t>
+          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, security controls</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -7321,7 +7313,7 @@
         </is>
       </c>
       <c r="V68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -7329,7 +7321,7 @@
         </is>
       </c>
       <c r="X68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7348,7 +7340,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Information Synthesis and Integration</t>
+          <t>Information Synthesis</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7368,12 +7360,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Combines diverse sources into clear written reports, using specialised terms and supporting documents.</t>
+          <t>Combines diverse sources into clear written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>["literature review", "source integration", "technical writing", "citation management", "knowledge synthesis"]</t>
+          <t>literature review, source integration, technical writing, citation management, knowledge synthesis</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -7406,7 +7398,7 @@
         <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -7422,7 +7414,7 @@
         </is>
       </c>
       <c r="X69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -7441,7 +7433,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Intellectual Property Policy Analysis</t>
+          <t>Intellectual Property Legislation Analysis</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7466,7 +7458,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>["intellectual property law", "copyright legislation", "policy compliance", "legal research", "regulatory analysis"]</t>
+          <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -7499,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -7515,7 +7507,7 @@
         </is>
       </c>
       <c r="X70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -7534,7 +7526,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Policy and Procedure Distribution</t>
+          <t>Policy Distribution</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7559,7 +7551,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>["document dissemination", "compliance communication", "stakeholder engagement", "internal governance", "ethics training"]</t>
+          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -7589,10 +7581,10 @@
         </is>
       </c>
       <c r="S71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -7608,7 +7600,7 @@
         </is>
       </c>
       <c r="X71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -7627,7 +7619,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>IP, Ethics, and Privacy Policy Update</t>
+          <t>Policy Updating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7647,12 +7639,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Updates privacy policies, procedures and codes of ethics to meet current legislation and compliance requirements.</t>
+          <t>Updates privacy policies, procedures and codes of ethics to reflect current legislation and compliance requirements.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>["privacy legislation", "compliance governance", "policy management", "codes of ethics", "regulatory documentation"]</t>
+          <t>privacy legislation, compliance governance, policy management, codes of ethics, regulatory documentation</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -7693,7 +7685,7 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
@@ -7701,7 +7693,7 @@
         </is>
       </c>
       <c r="X72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -7720,7 +7712,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Review and Grievance Process</t>
+          <t>Procedure Development</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7740,12 +7732,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Creates, records and sends review and grievance procedures to the designated staff.</t>
+          <t>Develops, records and submits review and grievance procedures to designated personnel.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>["policy drafting", "grievance management", "standard operating procedures", "process documentation", "compliance workflows"]</t>
+          <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -7775,10 +7767,10 @@
         </is>
       </c>
       <c r="S73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -7786,7 +7778,7 @@
         </is>
       </c>
       <c r="V73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -7794,7 +7786,7 @@
         </is>
       </c>
       <c r="X73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -7813,7 +7805,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Project Sequencing and Monitoring</t>
+          <t>Sequencing and Communication Management</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7833,12 +7825,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sequences and schedules complex activities, monitors progress, and coordinates communication to keep delivery momentum.</t>
+          <t>Sequences and schedules complex activities, monitors progress, and coordinates communication to maintain delivery momentum.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>["scheduling", "resource allocation", "stakeholder communication", "project monitoring", "Gantt charts"]</t>
+          <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -7887,7 +7879,7 @@
         </is>
       </c>
       <c r="X74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7906,7 +7898,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Legislative Change Analysis</t>
+          <t>Change Monitoring</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7931,7 +7923,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>["compliance", "legislation monitoring", "regulatory analysis", "policy tracking", "legal research"]</t>
+          <t>compliance, legislation monitoring, regulatory analysis, policy tracking, legal research</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -7980,7 +7972,7 @@
         </is>
       </c>
       <c r="X75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -7999,7 +7991,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Digital Information Ethics</t>
+          <t>Information Security Management</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8024,7 +8016,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>["cyber security", "data protection", "information governance", "privacy compliance", "access control"]</t>
+          <t>cyber security, data protection, information governance, privacy compliance, access control</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -8073,7 +8065,7 @@
         </is>
       </c>
       <c r="X76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -8117,7 +8109,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>["policy dissemination", "stakeholder engagement", "communication protocols", "change management", "organisational compliance"]</t>
+          <t>policy dissemination, stakeholder engagement, communication protocols, change management, organisational compliance</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -8166,7 +8158,7 @@
         </is>
       </c>
       <c r="X77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -8185,7 +8177,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Verbal Interaction</t>
+          <t>Viewpoint Elicitation</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8205,12 +8197,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Engages in verbal idea exchange, actively listening and questioning to draw out others’ views.</t>
+          <t>Engage in verbal idea exchange, actively listen and ask questions to draw out others' views.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>["active listening", "questioning techniques", "stakeholder engagement", "dialogue facilitation", "interpersonal communication"]</t>
+          <t>active listening, questioning techniques, stakeholder engagement, dialogue facilitation, interpersonal communication</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -8243,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -8251,7 +8243,7 @@
         </is>
       </c>
       <c r="V78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
@@ -8259,7 +8251,7 @@
         </is>
       </c>
       <c r="X78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -8278,7 +8270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Blockchain Platform Implementation</t>
+          <t>Platform Installation</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8303,7 +8295,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>["distributed ledger", "node deployment", "consensus configuration", "Ethereum", "Docker"]</t>
+          <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -8352,7 +8344,7 @@
         </is>
       </c>
       <c r="X79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -8371,7 +8363,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Anomaly Detection and Remediation</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8391,12 +8383,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Detects blockchain anomalies and resolves them using contextual analysis to spot subtle deviations.</t>
+          <t>Identifies and resolves blockchain anomalies through contextual analysis to detect subtle deviations.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>["anomaly detection", "blockchain analytics", "smart contract debugging", "cryptographic forensics", "pattern recognition"]</t>
+          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -8437,7 +8429,7 @@
         </is>
       </c>
       <c r="V80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -8445,7 +8437,7 @@
         </is>
       </c>
       <c r="X80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -8464,7 +8456,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Blockchain Requirements Analysis</t>
+          <t>Requirements Determination</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8484,12 +8476,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Defines blockchain objectives and requirements that match organisational needs in hybrid environments.</t>
+          <t>Defines blockchain objectives and requirements that align with organisational needs in hybrid environments.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>["distributed ledger", "use\u2011case definition", "stakeholder analysis", "smart contract design", "governance frameworks"]</t>
+          <t>distributed ledger, use‑case definition, stakeholder analysis, smart contract design, governance frameworks</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -8519,10 +8511,10 @@
         </is>
       </c>
       <c r="S81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -8538,7 +8530,7 @@
         </is>
       </c>
       <c r="X81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -8557,7 +8549,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Consensus Portal Implementation</t>
+          <t>Consensus Mechanism Implementation</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8577,12 +8569,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Configures and deploys system components to enable consensus mechanisms.</t>
+          <t>Configures and deploys system components to implement consensus mechanisms.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>["blockchain", "distributed ledger", "consensus algorithms", "peer\u2011to\u2011peer networking", "Byzantine fault tolerance"]</t>
+          <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -8612,10 +8604,10 @@
         </is>
       </c>
       <c r="S82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -8631,7 +8623,7 @@
         </is>
       </c>
       <c r="X82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -8650,7 +8642,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Design Documentation</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8675,7 +8667,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>["technical specifications", "design standards", "engineering documentation", "organisational requirements"]</t>
+          <t>technical specifications, design standards, engineering documentation, organisational requirements</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -8705,7 +8697,7 @@
         </is>
       </c>
       <c r="S83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
         <v>0.97</v>
@@ -8724,7 +8716,7 @@
         </is>
       </c>
       <c r="X83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -8743,7 +8735,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Documentation Submission and Feedback</t>
+          <t>Documentation Submission</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8768,7 +8760,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>["record\u2011keeping", "feedback loops", "compliance", "workflow approvals", "electronic filing"]</t>
+          <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -8798,7 +8790,7 @@
         </is>
       </c>
       <c r="S84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
         <v>0.97</v>
@@ -8817,7 +8809,7 @@
         </is>
       </c>
       <c r="X84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -8836,7 +8828,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Integration Workflow Design</t>
+          <t>Workflow Design</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8861,7 +8853,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>["systems integration", "workflow orchestration", "process automation", "ETL", "API middleware"]</t>
+          <t>systems integration, workflow orchestration, process automation, ETL, API middleware</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -8910,7 +8902,7 @@
         </is>
       </c>
       <c r="X85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -8929,7 +8921,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Maintenance Schedule Planning</t>
+          <t>Schedule Development</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8954,7 +8946,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>["preventive maintenance", "asset management", "CMMS", "work order scheduling", "reliability engineering"]</t>
+          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -8984,7 +8976,7 @@
         </is>
       </c>
       <c r="S86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
         <v>0.97</v>
@@ -9003,7 +8995,7 @@
         </is>
       </c>
       <c r="X86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -9022,7 +9014,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Test Execution</t>
+          <t>Maintenance Testing</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9047,7 +9039,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>["preventive maintenance", "test procedures", "equipment inspection", "reliability testing", "compliance standards"]</t>
+          <t>preventive maintenance, test procedures, equipment inspection, reliability testing, compliance standards</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -9080,7 +9072,7 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -9096,7 +9088,7 @@
         </is>
       </c>
       <c r="X87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -9115,7 +9107,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Blockchain Security Platform Selection</t>
+          <t>Security Platform Selection</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9135,12 +9127,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Choose and set up security platforms for blockchain solutions using risk assessments.</t>
+          <t>Selects and configures security platforms for blockchain solutions based on risk assessments.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>["blockchain", "security architecture", "platform evaluation", "cryptography", "risk assessment"]</t>
+          <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -9170,7 +9162,7 @@
         </is>
       </c>
       <c r="S88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
         <v>0.97</v>
@@ -9181,7 +9173,7 @@
         </is>
       </c>
       <c r="V88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -9189,7 +9181,7 @@
         </is>
       </c>
       <c r="X88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -9208,7 +9200,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Blockchain Solution Execution</t>
+          <t>Contract Execution</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9233,7 +9225,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>["blockchain", "Ethereum", "Solidity", "decentralised applications", "Web3"]</t>
+          <t>blockchain, Ethereum, Solidity, decentralised applications, Web3</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -9263,10 +9255,10 @@
         </is>
       </c>
       <c r="S89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -9282,7 +9274,7 @@
         </is>
       </c>
       <c r="X89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -9301,7 +9293,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Solution Debugging and Scaling</t>
+          <t>Solution Debugging</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9321,12 +9313,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Diagnoses and resolves blockchain solution issues and optimises performance for scalable deployment.</t>
+          <t>Diagnoses and resolves blockchain solution issues, then optimises performance for scalable deployment.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>["blockchain", "smart contracts", "Solidity", "distributed ledger", "performance scaling"]</t>
+          <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -9359,7 +9351,7 @@
         <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -9367,7 +9359,7 @@
         </is>
       </c>
       <c r="V90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9375,7 +9367,7 @@
         </is>
       </c>
       <c r="X90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -9394,7 +9386,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Solution Performance Testing</t>
+          <t>Performance Evaluation</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9414,12 +9406,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests solutions against organisational requirements to confirm they are suitable.</t>
+          <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>["benchmarking", "requirements compliance", "load testing", "service level agreements", "performance metrics"]</t>
+          <t>benchmarking, requirements compliance, load testing, service level agreements, performance metrics</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -9449,10 +9441,10 @@
         </is>
       </c>
       <c r="S91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -9460,7 +9452,7 @@
         </is>
       </c>
       <c r="V91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9468,7 +9460,7 @@
         </is>
       </c>
       <c r="X91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -9487,7 +9479,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Requirements Confirmation</t>
+          <t>Requirement Clarification</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9512,7 +9504,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>["stakeholder engagement", "requirements gathering", "industry terminology", "verbal communication", "active listening"]</t>
+          <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, active listening</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -9545,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -9561,7 +9553,7 @@
         </is>
       </c>
       <c r="X92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -9600,12 +9592,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Analyses hybrid environments to identify organisational use cases that match business needs.</t>
+          <t>Analyses hybrid environments to identify organisational use cases that align with business needs.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>["requirements analysis", "business analysis", "stakeholder mapping", "use\u2011case modelling", "functional requirements"]</t>
+          <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, functional requirements</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -9638,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -9654,7 +9646,7 @@
         </is>
       </c>
       <c r="X93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -9673,7 +9665,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Threat Data Management</t>
+          <t>Log Ingestion</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9698,7 +9690,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>["data ingestion", "log analytics", "ETL pipelines", "analytics platforms", "monitoring"]</t>
+          <t>data ingestion, log analytics, ETL pipelines, analytics platforms, monitoring</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -9742,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -9758,7 +9750,7 @@
         </is>
       </c>
       <c r="X94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -9777,7 +9769,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Threat Data Collection and Interpretation</t>
+          <t>Legislative and Policy Requirement Identification</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9802,7 +9794,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>["regulatory compliance", "legislation", "policy analysis", "threat intelligence", "risk assessment"]</t>
+          <t>regulatory compliance, legislation, policy analysis, threat intelligence, risk assessment</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -9866,7 +9858,7 @@
         </is>
       </c>
       <c r="X95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -9885,7 +9877,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Data Discrepancy Analysis</t>
+          <t>Discrepancy Identification</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9905,12 +9897,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Examines datasets to find, record and fix data discrepancies and inconsistencies.</t>
+          <t>Examines datasets to identify, document and resolve data discrepancies and inconsistencies.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>["data validation", "anomaly detection", "data quality", "data auditing", "data profiling"]</t>
+          <t>data validation, anomaly detection, data quality, data auditing, profiling</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -9951,10 +9943,10 @@
         </is>
       </c>
       <c r="S96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -9962,7 +9954,7 @@
         </is>
       </c>
       <c r="V96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -9970,7 +9962,7 @@
         </is>
       </c>
       <c r="X96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -9989,7 +9981,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Threat Data Collection Procedure</t>
+          <t>Data Set Creation</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10009,12 +10001,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Collect alerts, logs and event reports and organise them into structured datasets following organisational policies.</t>
+          <t>Compiles alerts, logs and event reports into structured datasets following organisational policies.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>["log analysis", "data ingestion", "security monitoring", "data governance", "ETL processes"]</t>
+          <t>log analysis, data ingestion, security monitoring, data governance, ETL processes</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -10058,7 +10050,7 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -10074,7 +10066,7 @@
         </is>
       </c>
       <c r="X97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -10093,7 +10085,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>False Positive/Negative Review</t>
+          <t>Data Detection</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10113,12 +10105,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Reviews test results to find and fix false positives and false negatives.</t>
+          <t>Reviews test results to identify and correct false positives and false negatives.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>["type I error", "anomaly detection", "validation testing", "precision\u2011recall analysis", "statistical significance"]</t>
+          <t>type I error, anomaly detection, validation testing, precision‑recall analysis, statistical significance</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -10174,7 +10166,7 @@
         </is>
       </c>
       <c r="V98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -10182,7 +10174,7 @@
         </is>
       </c>
       <c r="X98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -10201,7 +10193,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Threat Data Report</t>
+          <t>Data Report Documentation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10221,12 +10213,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Creates formal investigation reports that outline findings and recommendations following organisational procedures.</t>
+          <t>Produces formal investigation reports that outline findings and recommendations following organisational procedures.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>["incident reporting", "root\u2011cause analysis", "procedural compliance", "report writing", "safety management"]</t>
+          <t>incident reporting, root‑cause analysis, procedural compliance, report writing, safety management</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -10266,7 +10258,7 @@
         <v>1</v>
       </c>
       <c r="T99" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -10282,7 +10274,7 @@
         </is>
       </c>
       <c r="X99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -10301,7 +10293,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Threat Data Mitigation Recommendation</t>
+          <t>Strategy Recommendation</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10321,12 +10313,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Creates and checks mitigation strategies, action steps and lessons learned with relevant personnel.</t>
+          <t>Develops and validates mitigation strategies, action steps and lessons learned with relevant personnel.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>["risk management", "lessons learned", "action planning", "stakeholder engagement", "mitigation planning"]</t>
+          <t>risk management, lessons learned, action planning, stakeholder engagement, mitigation planning</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -10371,10 +10363,10 @@
         </is>
       </c>
       <c r="S100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -10382,7 +10374,7 @@
         </is>
       </c>
       <c r="V100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -10390,7 +10382,7 @@
         </is>
       </c>
       <c r="X100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -10409,7 +10401,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Risk Likelihood and Impact Assessment</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10429,12 +10421,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Evaluates threats by judging how likely they are and how much impact they could cause, then prioritises actions to reduce risk.</t>
+          <t>Evaluates threats by analysing likelihood and impact, then prioritises mitigation actions.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>["risk assessment", "probability analysis", "threat modelling", "impact evaluation", "risk matrices"]</t>
+          <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -10478,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="T101" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -10494,7 +10486,7 @@
         </is>
       </c>
       <c r="X101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -10513,7 +10505,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Security Equipment Inventory</t>
+          <t>Equipment Identification</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10533,12 +10525,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Identifies network and data source security equipment using system diagrams and technical documentation.</t>
+          <t>Identifies network and data‑source security equipment using system diagrams and technical documentation.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>["cyber security", "network security", "asset inventories", "intrusion detection systems", "firewalls"]</t>
+          <t>cyber security, network security, asset inventories, IDS, firewalls</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -10579,10 +10571,10 @@
         </is>
       </c>
       <c r="S102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -10590,7 +10582,7 @@
         </is>
       </c>
       <c r="V102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -10598,7 +10590,7 @@
         </is>
       </c>
       <c r="X102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -10617,7 +10609,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Security Log Ingestion</t>
+          <t>Log Ingestion</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10642,7 +10634,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>["log aggregation", "SIEM", "data ingestion", "security analytics", "ELK stack"]</t>
+          <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -10683,10 +10675,10 @@
         </is>
       </c>
       <c r="S103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -10702,7 +10694,7 @@
         </is>
       </c>
       <c r="X103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -10721,7 +10713,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Threat Data Review</t>
+          <t>Findings Communication</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10746,7 +10738,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>["stakeholder engagement", "threat intelligence", "risk reporting", "data briefings", "cyber security communication"]</t>
+          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -10790,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="T104" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -10806,7 +10798,7 @@
         </is>
       </c>
       <c r="X104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -10825,7 +10817,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Gathering</t>
+          <t>Data Gathering</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10845,12 +10837,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collects and structures alerts, logs and event data according to organisational data policies.</t>
+          <t>Collect and structure alerts, logs and event data according to organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>["threat intelligence", "log analysis", "SIEM", "incident response", "security monitoring"]</t>
+          <t>threat intelligence, log analysis, SIEM, incident response, security monitoring</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -10894,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="T105" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -10910,7 +10902,7 @@
         </is>
       </c>
       <c r="X105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -10929,7 +10921,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Anomaly Detection and Remediation</t>
+          <t>Anomaly Detection and Resolution</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10949,12 +10941,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Monitors operational data to detect contextual anomalies and resolves deviations promptly.</t>
+          <t>Monitors operational data, detects contextual anomalies, and resolves deviations promptly.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>["outlier analysis", "root\u2011cause analysis", "statistical process control", "monitoring and diagnostics"]</t>
+          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -11003,7 +10995,7 @@
         </is>
       </c>
       <c r="X106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -11022,7 +11014,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Protection and Asset Management</t>
+          <t>Process Implementation</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11047,7 +11039,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>["asset tracking", "risk mitigation", "protection plans", "maintenance scheduling", "capital budgeting"]</t>
+          <t>asset tracking, risk mitigation, protection plans, maintenance scheduling, capital budgeting</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -11080,7 +11072,7 @@
         <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -11096,7 +11088,7 @@
         </is>
       </c>
       <c r="X107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -11115,7 +11107,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Protection Strategy</t>
+          <t>Critical Infrastructure Research</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11135,12 +11127,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Conducts research on critical infrastructure to support protection planning and documentation requirements.</t>
+          <t>Conducts critical infrastructure research to support protection planning and documentation requirements.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>["infrastructure protection", "risk assessment", "threat modelling", "resilience analysis", "policy compliance"]</t>
+          <t>infrastructure protection, risk assessment, threat modelling, resilience analysis, policy compliance</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -11170,10 +11162,10 @@
         </is>
       </c>
       <c r="S108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -11181,7 +11173,7 @@
         </is>
       </c>
       <c r="V108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -11189,7 +11181,7 @@
         </is>
       </c>
       <c r="X108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -11208,7 +11200,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Data Backup</t>
+          <t>Backup Execution</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11228,12 +11220,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Runs scheduled data backups following organisational policies and procedures.</t>
+          <t>Runs scheduled data backups according to organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>["disaster recovery", "backup software", "data retention policies", "storage replication", "ICT compliance"]</t>
+          <t>disaster recovery, backup software, data retention policies, storage replication, ICT compliance</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -11263,10 +11255,10 @@
         </is>
       </c>
       <c r="S109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -11282,7 +11274,7 @@
         </is>
       </c>
       <c r="X109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -11301,7 +11293,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Device Security Implementation</t>
+          <t>Security Implementation</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11321,12 +11313,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Implements device security controls following protection plans and technical specifications.</t>
+          <t>Implements device security controls according to protection plans and technical specifications.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>["endpoint protection", "device hardening", "security policies", "encryption", "mobile device management"]</t>
+          <t>endpoint protection, device hardening, security policies, encryption, mobile device management</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -11359,7 +11351,7 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -11375,7 +11367,7 @@
         </is>
       </c>
       <c r="X110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -11394,7 +11386,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Protection Plan Feedback</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11419,7 +11411,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>["stakeholder communication", "feedback loops", "response management", "plan documentation", "compliance reporting"]</t>
+          <t>stakeholder communication, feedback loops, response management, plan documentation, compliance reporting</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -11452,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -11468,7 +11460,7 @@
         </is>
       </c>
       <c r="X111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -11487,7 +11479,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Network Segmentation</t>
+          <t>Segmentation Implementation</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11512,7 +11504,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>["VLANs", "firewall policies", "micro\u2011segmentation", "zero\u2011trust architecture", "network security zones"]</t>
+          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -11545,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="T112" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -11561,7 +11553,7 @@
         </is>
       </c>
       <c r="X112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -11580,7 +11572,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Operational Detail Development</t>
+          <t>Planning and Review</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11600,12 +11592,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Creates staged operational plans and reviews priorities and performance while executing.</t>
+          <t>Creates staged operational plans and reviews priorities and performance regularly during execution.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>["operational planning", "performance monitoring", "resource allocation", "timeline management", "Gantt charts"]</t>
+          <t>operational planning, performance monitoring, resource allocation, timeline management, Gantt charts</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -11638,7 +11630,7 @@
         <v>1</v>
       </c>
       <c r="T113" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -11654,7 +11646,7 @@
         </is>
       </c>
       <c r="X113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -11698,7 +11690,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>["critical infrastructure", "risk assessment", "cyber security resilience", "ISO 27001", "vulnerability analysis"]</t>
+          <t>critical infrastructure, risk assessment, cyber security resilience, ISO 27001, vulnerability analysis</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -11731,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="T114" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -11747,7 +11739,7 @@
         </is>
       </c>
       <c r="X114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -11766,7 +11758,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Protection Strategy</t>
+          <t>Protection Planning</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11786,12 +11778,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Creates and documents protection plans that match organisational policies and procedures.</t>
+          <t>Develops and records critical infrastructure protection plans that align with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>["critical infrastructure", "risk assessment", "security policy compliance", "business continuity planning", "incident response frameworks"]</t>
+          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -11840,7 +11832,7 @@
         </is>
       </c>
       <c r="X115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -11859,7 +11851,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Protection Plan Test</t>
+          <t>Plan Testing</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11879,12 +11871,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tests protection plans to confirm safeguards meet organisational requirements.</t>
+          <t>Conduct protection plan testing to validate safeguards against organisational requirements.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>["cyber security", "risk assessment", "compliance testing", "security policies", "vulnerability testing"]</t>
+          <t>cyber security, risk assessment, compliance testing, security policies, vulnerability testing</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -11933,7 +11925,7 @@
         </is>
       </c>
       <c r="X116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -11952,7 +11944,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Results Analysis</t>
+          <t>Results Analysis and Reporting</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11977,7 +11969,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>["data interpretation", "performance metrics", "compliance reporting", "organisational standards", "business intelligence"]</t>
+          <t>data interpretation, performance metrics, compliance reporting, organisational standards, business intelligence</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -12026,7 +12018,7 @@
         </is>
       </c>
       <c r="X117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -12045,7 +12037,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Risk Assessment</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12070,7 +12062,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>["vulnerability analysis", "mitigation planning", "risk matrices", "security governance", "ISO 27001 compliance"]</t>
+          <t>vulnerability analysis, mitigation planning, risk matrices, security governance, ISO 27001 compliance</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -12119,7 +12111,7 @@
         </is>
       </c>
       <c r="X118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -12138,7 +12130,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Software Patch Implementation</t>
+          <t>Patch Installation</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12163,7 +12155,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>["patch management", "vulnerability remediation", "update deployment", "configuration management", "WSUS"]</t>
+          <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -12196,7 +12188,7 @@
         <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -12212,7 +12204,7 @@
         </is>
       </c>
       <c r="X119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -12231,7 +12223,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Documentation</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12251,12 +12243,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Creates workplace documents that follow required structure, layout and organisational language standards.</t>
+          <t>Creates workplace documentation that follows required structure, layout and organisational language standards.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>["technical writing", "process documentation", "standard operating procedures", "document formatting"]</t>
+          <t>technical writing, process documentation, standard operating procedures, document formatting</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -12286,10 +12278,10 @@
         </is>
       </c>
       <c r="S120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -12305,7 +12297,7 @@
         </is>
       </c>
       <c r="X120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -12324,7 +12316,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data Type Catalog</t>
+          <t>Classification Identification</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12349,7 +12341,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>["information security", "data inventories", "classification schemes", "confidentiality levels", "security architecture"]</t>
+          <t>information security, data inventories, classification schemes, confidentiality levels, security architecture</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -12394,10 +12386,10 @@
         </is>
       </c>
       <c r="S121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -12413,7 +12405,7 @@
         </is>
       </c>
       <c r="X121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -12432,7 +12424,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Initial Design Feedback</t>
+          <t>Feedback Submission</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12457,7 +12449,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>["documentation", "stakeholder communication", "feedback loops", "record\u2011keeping", "internal reporting"]</t>
+          <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -12517,7 +12509,7 @@
         </is>
       </c>
       <c r="X122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -12536,7 +12528,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Industry Design Methodologies</t>
+          <t>Architecture Methodology Research</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12561,7 +12553,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>["security architecture", "design methodologies", "industry standards", "security frameworks", "risk assessment"]</t>
+          <t>security architecture, design methodologies, industry standards, security frameworks, risk assessment</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -12601,7 +12593,7 @@
         <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -12617,7 +12609,7 @@
         </is>
       </c>
       <c r="X123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -12636,7 +12628,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Anomaly Detection in Security</t>
+          <t>Anomaly Identification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12661,7 +12653,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>["anomaly detection", "threat analysis", "security monitoring", "pattern recognition", "situational awareness"]</t>
+          <t>anomaly detection, threat analysis, security monitoring, pattern recognition, situational awareness</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -12725,7 +12717,7 @@
         </is>
       </c>
       <c r="X124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -12744,7 +12736,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Architecture Documentation</t>
+          <t>Architecture Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12764,12 +12756,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Document and validate security architecture findings with relevant personnel.</t>
+          <t>Documents and validates security architecture findings with relevant personnel.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>["security architecture", "risk assessment", "compliance frameworks", "ISO 27001", "threat modelling"]</t>
+          <t>security architecture, risk assessment, compliance frameworks, ISO 27001, threat modelling</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -12813,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -12821,7 +12813,7 @@
         </is>
       </c>
       <c r="V125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W125" t="inlineStr">
         <is>
@@ -12829,7 +12821,7 @@
         </is>
       </c>
       <c r="X125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -12848,7 +12840,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Security Architecture Report</t>
+          <t>Architecture Presentation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12873,7 +12865,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>["information security", "enterprise architecture", "risk assessment", "security frameworks", "technical presentations"]</t>
+          <t>information security, enterprise architecture, risk assessment, security frameworks, technical presentations</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -12914,10 +12906,10 @@
         </is>
       </c>
       <c r="S126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -12933,7 +12925,7 @@
         </is>
       </c>
       <c r="X126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -12952,7 +12944,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Security Design Methodology Utilisation</t>
+          <t>Design Validation</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -12972,12 +12964,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Validates security designs using recognised industry methods.</t>
+          <t>Validates security designs using industry‑recognised methodologies.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>["security architecture", "threat modelling", "NIST framework", "ISO 27001", "risk assessment"]</t>
+          <t>security architecture, threat modelling, NIST framework, ISO 27001, risk assessment</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -13018,7 +13010,7 @@
         </is>
       </c>
       <c r="S127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T127" t="n">
         <v>0.97</v>
@@ -13029,7 +13021,7 @@
         </is>
       </c>
       <c r="V127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W127" t="inlineStr">
         <is>
@@ -13037,7 +13029,7 @@
         </is>
       </c>
       <c r="X127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -13056,7 +13048,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Security Level Definition</t>
+          <t>Level Assessment</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13076,12 +13068,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Assesses assets to decide required security levels, perimeters, features and protection modes.</t>
+          <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>["risk assessment", "access control", "security architecture", "perimeter security", "security policy"]</t>
+          <t>risk assessment, access control, security architecture, perimeter security, security policy</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -13137,7 +13129,7 @@
         </is>
       </c>
       <c r="V128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
@@ -13145,7 +13137,7 @@
         </is>
       </c>
       <c r="X128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -13164,7 +13156,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Security Architecture Planning</t>
+          <t>Initiative Planning</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13189,7 +13181,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>["cyber security governance", "risk assessment", "phased implementation", "performance monitoring", "project scheduling tools"]</t>
+          <t>cyber security governance, risk assessment, phased implementation, performance monitoring, project scheduling tools</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -13253,7 +13245,7 @@
         </is>
       </c>
       <c r="X129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -13272,7 +13264,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Security Requirements Analysis</t>
+          <t>Requirements Analysis</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -13292,12 +13284,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Analyses organisational operations and infrastructure to identify specific security requirements.</t>
+          <t>Analyse organisational operations and infrastructure to identify specific security requirements.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>["risk assessment", "threat modelling", "security architecture", "compliance standards", "vulnerability analysis"]</t>
+          <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -13345,7 +13337,7 @@
         </is>
       </c>
       <c r="V130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" t="inlineStr">
         <is>
@@ -13353,7 +13345,7 @@
         </is>
       </c>
       <c r="X130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -13372,7 +13364,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Security Solution Design</t>
+          <t>Architecture Design</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -13397,7 +13389,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>["cyber security architecture", "risk assessment", "security compliance", "solution documentation", "threat modelling"]</t>
+          <t>cyber security architecture, risk assessment, security compliance, solution documentation, threat modelling</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -13442,10 +13434,10 @@
         </is>
       </c>
       <c r="S131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -13461,7 +13453,7 @@
         </is>
       </c>
       <c r="X131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -13480,7 +13472,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Security Architecture Documentation</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13500,12 +13492,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Creates detailed technical documents that outline findings and propose solutions.</t>
+          <t>Creates detailed technical documentation that outlines findings and proposes solutions.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>["technical writing", "documentation standards", "reporting and analysis", "knowledge management"]</t>
+          <t>technical writing, documentation standards, reporting and analysis, knowledge management</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -13550,10 +13542,10 @@
         </is>
       </c>
       <c r="S132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -13569,7 +13561,7 @@
         </is>
       </c>
       <c r="X132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -13588,7 +13580,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Requirements Interpretation</t>
+          <t>Documentation Review</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13613,7 +13605,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>["technical documentation", "specification standards", "manufacturer manuals", "job requirement analysis", "engineering drawings"]</t>
+          <t>technical documentation, specification standards, manufacturer manuals, job requirement analysis, engineering drawings</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -13657,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="T133" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -13673,7 +13665,7 @@
         </is>
       </c>
       <c r="X133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -13692,7 +13684,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Autonomous Decision‑Making for Incident Response</t>
+          <t>Strategic Decision Making</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13717,7 +13709,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>["autonomy", "strategic decision\u2011making", "self\u2011management", "leadership", "organisational performance"]</t>
+          <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -13766,7 +13758,7 @@
         <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -13782,7 +13774,7 @@
         </is>
       </c>
       <c r="X134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -13801,7 +13793,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Forensic Evidence Handling</t>
+          <t>Evidence Collection Procedure Development</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -13821,12 +13813,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Designs and implements processes to collect forensic evidence and preserve data during incident response.</t>
+          <t>Designs and implements forensic evidence collection processes to preserve data during incident response.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>["chain of custody", "evidence preservation", "incident response", "digital forensics tools", "crime scene documentation"]</t>
+          <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -13871,7 +13863,7 @@
         <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -13879,7 +13871,7 @@
         </is>
       </c>
       <c r="V135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W135" t="inlineStr">
         <is>
@@ -13887,7 +13879,7 @@
         </is>
       </c>
       <c r="X135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -13906,7 +13898,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Incident Response Documentation</t>
+          <t>Report Preparation</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -13926,12 +13918,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Prepares detailed incident reports that document response actions and meet task requirements.</t>
+          <t>Prepares detailed incident reports that document response actions against task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>["security incident response", "incident reporting", "ITIL", "SIEM", "compliance documentation"]</t>
+          <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -13972,7 +13964,7 @@
         <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -13988,7 +13980,7 @@
         </is>
       </c>
       <c r="X136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -14032,7 +14024,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>["security operations", "post\u2011incident analysis", "efficiency metrics", "response plan documentation", "SOC tools"]</t>
+          <t>security operations, post‑incident analysis, efficiency metrics, response plan documentation, SOC tools</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -14093,7 +14085,7 @@
         </is>
       </c>
       <c r="X137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -14112,7 +14104,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Incident Response Planning</t>
+          <t>Incident Response Plan Development</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -14132,12 +14124,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Creates and documents incident response plans that meet organisational requirements.</t>
+          <t>Develop and record incident response plans that meet organisational requirements.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>["cyber security", "incident handling", "NIST framework", "playbook development", "risk management"]</t>
+          <t>cyber security, incident handling, NIST framework, playbook development, risk management</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -14179,10 +14171,10 @@
         </is>
       </c>
       <c r="S138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T138" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -14198,7 +14190,7 @@
         </is>
       </c>
       <c r="X138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -14217,7 +14209,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Incident Team Coordination</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -14237,12 +14229,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Document incident response team roles and services to support a coordinated response.</t>
+          <t>Document incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>["incident response", "service documentation", "team coordination", "organisational compliance", "ticketing systems"]</t>
+          <t>incident response, service documentation, team coordination, organisational compliance, ticketing systems</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -14280,7 +14272,7 @@
         </is>
       </c>
       <c r="S139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139" t="n">
         <v>0.97</v>
@@ -14299,7 +14291,7 @@
         </is>
       </c>
       <c r="X139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -14318,7 +14310,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Comprehensive Incident Response Exercise Design</t>
+          <t>Exercise Design</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14343,7 +14335,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>["adversary simulation", "incident response planning", "threat modelling", "security training programmes", "MITRE ATT&amp;CK framework"]</t>
+          <t>adversary simulation, incident response planning, threat modelling, security training programmes, MITRE ATT&amp;CK framework</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -14388,7 +14380,7 @@
         <v>1</v>
       </c>
       <c r="T140" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
@@ -14404,7 +14396,7 @@
         </is>
       </c>
       <c r="X140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -14448,7 +14440,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>["incident response", "stakeholder communication", "internal coordination", "external liaison", "communication effectiveness"]</t>
+          <t>incident response, stakeholder communication, internal coordination, external liaison, communication effectiveness</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -14493,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -14509,7 +14501,7 @@
         </is>
       </c>
       <c r="X141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -14528,7 +14520,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Data Analysis</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14548,12 +14540,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Interprets and records numerical and technical system data to support risk assessment.</t>
+          <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>["quantitative analysis", "technical data interpretation", "risk assessment", "system modelling", "data documentation"]</t>
+          <t>quantitative analysis, technical data interpretation, risk assessment, system modelling, data documentation</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -14610,7 +14602,7 @@
         </is>
       </c>
       <c r="V142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W142" t="inlineStr">
         <is>
@@ -14618,7 +14610,7 @@
         </is>
       </c>
       <c r="X142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -14637,7 +14629,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Incident Response Application</t>
+          <t>Response Execution</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14657,12 +14649,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Runs incident response actions following approved response plans.</t>
+          <t>Executes incident response actions following approved response plans.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>["incident response", "security operations centre", "SIEM", "playbook execution", "forensic analysis"]</t>
+          <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -14711,7 +14703,7 @@
         <v>1</v>
       </c>
       <c r="T143" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -14727,7 +14719,7 @@
         </is>
       </c>
       <c r="X143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -14746,7 +14738,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Incident Response Plan Development</t>
+          <t>Policy Development</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -14766,12 +14758,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Creates and writes incident management policies that match organisational specifications.</t>
+          <t>Creates and records incident management policies that meet organisational specifications.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>["incident management", "risk assessment", "governance", "compliance", "ISO 27001"]</t>
+          <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -14820,7 +14812,7 @@
         <v>1</v>
       </c>
       <c r="T144" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -14836,7 +14828,7 @@
         </is>
       </c>
       <c r="X144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -14855,7 +14847,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Technical Data Interpretation</t>
+          <t>Data Analysis and Documentation</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -14880,7 +14872,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>["quantitative analysis", "technical system data", "measurement instrumentation", "data documentation", "engineering diagnostics"]</t>
+          <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, engineering diagnostics</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -14926,10 +14918,10 @@
         </is>
       </c>
       <c r="S145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T145" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -14945,7 +14937,7 @@
         </is>
       </c>
       <c r="X145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -14964,7 +14956,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Business Continuity Assessment</t>
+          <t>Impact Evaluation</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -14984,12 +14976,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Evaluates system impacts on business continuity, identifies risks and suggests mitigation strategies.</t>
+          <t>Assesses system impacts on business continuity, identifies risks and mitigation strategies.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>["business continuity", "risk assessment", "impact analysis", "disaster recovery", "resilience planning"]</t>
+          <t>business continuity, risk assessment, impact analysis, disaster recovery, resilience planning</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -15034,7 +15026,7 @@
         <v>1</v>
       </c>
       <c r="T146" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
@@ -15050,7 +15042,7 @@
         </is>
       </c>
       <c r="X146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -15069,7 +15061,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Regulatory Compliance Strategy</t>
+          <t>Strategy Development</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15094,7 +15086,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>["regulatory compliance", "policy enforcement", "risk management", "governance", "audit"]</t>
+          <t>regulatory compliance, policy enforcement, risk management, governance, audit</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -15139,7 +15131,7 @@
         <v>1</v>
       </c>
       <c r="T147" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -15155,7 +15147,7 @@
         </is>
       </c>
       <c r="X147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -15174,7 +15166,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Contingency Plan Development</t>
+          <t>Contingency Planning</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15194,12 +15186,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Creates contingency plans by identifying threats and defining response actions.</t>
+          <t>Develops contingency plans by identifying threats and defining response actions.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>["risk assessment", "business continuity", "threat identification", "mitigation strategies", "scenario analysis"]</t>
+          <t>risk assessment, business continuity, threat identification, mitigation strategies, scenario analysis</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -15245,7 +15237,7 @@
         </is>
       </c>
       <c r="S148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" t="n">
         <v>0.97</v>
@@ -15256,7 +15248,7 @@
         </is>
       </c>
       <c r="V148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W148" t="inlineStr">
         <is>
@@ -15264,7 +15256,7 @@
         </is>
       </c>
       <c r="X148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -15283,7 +15275,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Prevention and Recovery Options Assessment</t>
+          <t>Constraint Evaluation</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15303,12 +15295,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Evaluates options to prevent and recover, ensuring compliance and cost effectiveness.</t>
+          <t>Evaluates prevention and recovery options for compliance and cost effectiveness.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>["cost\u2011benefit analysis", "budgeting", "risk assessment", "business case evaluation", "financial modelling"]</t>
+          <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, financial modelling</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -15361,7 +15353,7 @@
         </is>
       </c>
       <c r="V149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W149" t="inlineStr">
         <is>
@@ -15369,7 +15361,7 @@
         </is>
       </c>
       <c r="X149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -15388,7 +15380,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Disaster Recovery Planning</t>
+          <t>Recovery Plan Development</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -15408,12 +15400,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Creates detailed disaster recovery plans that outline procedures, resources and recovery timeframes.</t>
+          <t>Develops comprehensive disaster recovery plans that detail procedures, resources and recovery timeframes.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>["business continuity", "backup and restore", "recovery time objectives", "risk assessment", "disaster recovery testing"]</t>
+          <t>business continuity, backup and restore, recovery time objectives, risk assessment, disaster recovery testing</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -15455,7 +15447,7 @@
         </is>
       </c>
       <c r="S150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150" t="n">
         <v>0.97</v>
@@ -15474,7 +15466,7 @@
         </is>
       </c>
       <c r="X150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -15493,7 +15485,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Disaster Recovery Review</t>
+          <t>Standards Review</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15518,7 +15510,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>["compliance", "risk management", "standard operating procedures", "regulatory guidance", "audit"]</t>
+          <t>compliance, risk management, standard operating procedures, regulatory guidance, audit</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -15560,10 +15552,10 @@
         </is>
       </c>
       <c r="S151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -15579,7 +15571,7 @@
         </is>
       </c>
       <c r="X151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -15598,7 +15590,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Numerical System Data Analysis</t>
+          <t>Data Evaluation</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -15623,7 +15615,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>["quantitative analysis", "financial modelling", "technical data interpretation", "statistical methods", "data reporting"]</t>
+          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, data reporting</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -15668,7 +15660,7 @@
         <v>1</v>
       </c>
       <c r="T152" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -15684,7 +15676,7 @@
         </is>
       </c>
       <c r="X152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -15703,7 +15695,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Prevention and Recovery Strategy</t>
+          <t>Prevention and Recovery Strategy Formulation</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -15723,12 +15715,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Designs and implements prevention and recovery strategies to strengthen system resilience.</t>
+          <t>Designs and implements strategies that prevent incidents and aid recovery, strengthening system resilience.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>["risk assessment", "mitigation planning", "contingency strategies", "recovery planning", "scenario analysis"]</t>
+          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -15773,7 +15765,7 @@
         <v>1</v>
       </c>
       <c r="T153" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -15781,7 +15773,7 @@
         </is>
       </c>
       <c r="V153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" t="inlineStr">
         <is>
@@ -15789,7 +15781,7 @@
         </is>
       </c>
       <c r="X153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -15808,7 +15800,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Business Continuity Evaluation and Recovery Strategy</t>
+          <t>Recovery Planning Evaluation</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -15833,7 +15825,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>["data analysis", "feedback loops", "process improvement", "root\u2011cause analysis", "continuous improvement"]</t>
+          <t>data analysis, feedback loops, process improvement, root‑cause analysis, continuous improvement</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -15882,7 +15874,7 @@
         <v>1</v>
       </c>
       <c r="T154" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -15898,7 +15890,7 @@
         </is>
       </c>
       <c r="X154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -15917,7 +15909,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Risk Analysis and Recovery Planning</t>
+          <t>Risk Assessment and Disaster Recovery Planning</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -15937,12 +15929,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conducts thorough risk assessments and creates disaster recovery and contingency solutions.</t>
+          <t>Conduct comprehensive risk assessments and develop disaster recovery and contingency solutions.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>["risk assessment", "disaster recovery", "contingency planning", "business continuity", "threat modelling"]</t>
+          <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -15987,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="T155" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -16003,7 +15995,7 @@
         </is>
       </c>
       <c r="X155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -16022,7 +16014,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Stakeholder Communication Management</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16047,7 +16039,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>["stakeholder engagement", "feedback loops", "document management", "communication protocols", "collaboration tools"]</t>
+          <t>stakeholder engagement, feedback loops, document management, communication protocols, collaboration tools</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -16108,7 +16100,7 @@
         </is>
       </c>
       <c r="X156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -16127,7 +16119,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>Disaster Recovery Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -16147,12 +16139,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Creates hybrid work priorities and outcomes by using structured strategic planning.</t>
+          <t>Develops and aligns hybrid work priorities and outcomes through structured strategic planning.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>["priority alignment", "outcome mapping", "roadmap development", "performance metrics", "scenario analysis"]</t>
+          <t>priority alignment, outcome mapping, roadmap development, performance metrics, scenario analysis</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -16194,10 +16186,10 @@
         </is>
       </c>
       <c r="S157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T157" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -16205,7 +16197,7 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" t="inlineStr">
         <is>
@@ -16213,7 +16205,7 @@
         </is>
       </c>
       <c r="X157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -16232,7 +16224,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>System Impact and Recovery Planning</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -16252,12 +16244,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Works with team members using communication tools and strategies to keep effective working relationships.</t>
+          <t>Works with team members using communication tools and strategies to maintain effective relationships.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>["communication tools", "relationship building", "stakeholder engagement", "collaboration platforms", "interpersonal communication"]</t>
+          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -16299,7 +16291,7 @@
         </is>
       </c>
       <c r="S158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
         <v>0.95</v>
@@ -16318,7 +16310,7 @@
         </is>
       </c>
       <c r="X158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -16337,7 +16329,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Evaluation and Strategy Documentation</t>
+          <t>Recovery Documentation Preparation</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -16362,7 +16354,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>["specification drafting", "process documentation", "evaluation reporting", "strategic articulation", "document control"]</t>
+          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -16407,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="T159" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -16423,7 +16415,7 @@
         </is>
       </c>
       <c r="X159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -16462,12 +16454,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Identifies system weaknesses by structuring threat identification and analysis to guide mitigation planning.</t>
+          <t>Identifies system vulnerabilities by structuring threat identification and analysis to support mitigation planning.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>["risk analysis", "vulnerability assessment", "threat modelling", "cyber security", "intelligence gathering"]</t>
+          <t>risk analysis, vulnerability assessment, threat modelling, cyber security, intelligence gathering</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -16509,10 +16501,10 @@
         </is>
       </c>
       <c r="S160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -16528,7 +16520,7 @@
         </is>
       </c>
       <c r="X160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Best Practice Comparison</t>
+          <t>Best Practice Benchmarking</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="S3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0.97</v>
@@ -808,7 +808,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leads focused brainstorming sessions to create diverse solutions for identified issues.</t>
+          <t>Lead focused brainstorming sessions to create diverse solutions for identified issues.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Solution Generation</t>
+          <t>Creative Thinking</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Applies creative thinking techniques to develop innovative solutions for workplace challenges.</t>
+          <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="S6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0.97</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Viability Evaluation</t>
+          <t>Idea Evaluation Viability</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Systematically compares ideas against identified viability factors to assess them.</t>
+          <t>Systematically compare ideas with identified viability factors to assess them.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="S8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0.97</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Proposal Development</t>
+          <t>Proposal Writing</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="S10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Solution Research</t>
+          <t>Research Information Gathering</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Collects and evaluates data to identify viable solutions for the issue.</t>
+          <t>Collects and assesses data to find viable solutions for the identified issue.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="S11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0.97</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Choose suitable solution formats and deliver tailored presentations to stakeholders.</t>
+          <t>Select appropriate solution formats and deliver tailored presentations to stakeholders.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1701,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Iteratively refine and finalise solutions to meet specific task requirements.</t>
+          <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Feedback Solicitation</t>
+          <t>Stakeholder Feedback Solicitation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Proactively seeks stakeholder input on ideas to refine concepts and align expectations.</t>
+          <t>Actively request stakeholder input on ideas to improve concepts and align expectations.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="V15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Group Facilitation</t>
+          <t>Team Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="S16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0.95</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Technical Writing</t>
+          <t>Clear Technical Writing</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
+          <t>Writes workplace documents using precise cyber security terminology to convey technical information clearly.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="S18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0.97</v>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Security Awareness Assessment</t>
+          <t>Current Awareness Assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>We assess cyber security awareness in the work area using surveys and interviews to establish a baseline level.</t>
+          <t>Assesses cyber security awareness in the work area using surveys and interviews to establish baseline levels.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="S19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Data Breach Legislation Interpretation</t>
+          <t>Legislation Interpretation</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Interprets the Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
+          <t>Interprets Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="S22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0.97</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="V22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Outcome Reporting</t>
+          <t>Outcome Documentation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="S23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0.97</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Policy Drafting</t>
+          <t>Policy Contribution Drafting</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="S24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Security Practice Review</t>
+          <t>Practice Review Execution</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Systematically review cyber security practices to ensure they align with organisational policies and procedures.</t>
+          <t>Systematically reviews cyber security practices to ensure they align with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="S25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0.99</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Record Keeping</t>
+          <t>Record Maintenance</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maintains up‑to‑date cyber security protection records by organising and documenting relevant data.</t>
+          <t>Keeps cyber security protection records current by organising and documenting relevant data.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="S26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0.97</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="V26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="S28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0.97</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Security Platform Utilisation</t>
+          <t>Technology Platform Utilisation</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Select and operate suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
+          <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="S29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0.97</v>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="V29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Threat Trend Review</t>
+          <t>Threat Trend Analysis</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="S30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0.97</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Anti-Malware Installation</t>
+          <t>Anti-Malware Deployment</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Install and configure up‑to‑date anti‑malware on all workstations for continuous protection.</t>
+          <t>Install and configure up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="S34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Impact Analysis</t>
+          <t>Breach Impact Review</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="S35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0.97</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration</t>
+          <t>Device Configuration Setup</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Set up new devices by updating firmware and configuring settings.</t>
+          <t>Updates firmware and configures settings to set up new devices initially.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="S36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Device Encryption</t>
+          <t>Device Encryption Implementation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="S37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0.98</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Register Maintenance</t>
+          <t>Device Inventory Management</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Create and update a register of networked devices to support inventory tracking and asset management.</t>
+          <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="S38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0.97</v>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="V38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Gap Analysis</t>
+          <t>Gap Analysis Evaluation</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="S39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0.97</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Creation</t>
+          <t>Password Strength Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="S40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Creates physical security plans and shares them across the organisation to ensure coordinated protection.</t>
+          <t>Develops comprehensive physical security plans and shares them across the organisation to ensure coordinated protection.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Risk Categorisation</t>
+          <t>Risk Categorisation Analysis</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Assesses device data sensitivity and assigns a risk category for security management.</t>
+          <t>Evaluates device data sensitivity and assigns a suitable risk category for security management.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="S42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0.97</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Briefing</t>
+          <t>Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="S43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Selects appropriate security protocols for each device to mitigate identified risk levels.</t>
+          <t>Selects the right security protocol for each device to reduce identified risk levels.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="V44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Strategy Evaluation</t>
+          <t>Security Strategy Support</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="S45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0.97</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="S46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0.97</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Patch Installation</t>
+          <t>Software Patch Application</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="S47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Two-Factor Authentication Enabling</t>
+          <t>Two-Factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
+          <t>Enable multi‑factor authentication on supported systems to strengthen account security.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5397,18 +5397,18 @@
         </is>
       </c>
       <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
+        </is>
+      </c>
+      <c r="V48" t="b">
         <v>1</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
-        </is>
-      </c>
-      <c r="V48" t="b">
-        <v>0</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="S50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
         <v>0.97</v>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Technology Evaluation</t>
+          <t>Digital Technology Utilisation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="S51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
         <v>0.97</v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Document Preparation</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="S52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
         <v>0.97</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Gap Analysis</t>
+          <t>ICT Gap Analysis</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="S54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
         <v>0.97</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Idea Evaluation</t>
+          <t>Innovative Solution Investigation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="S55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>0.97</v>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Impact Analysis</t>
+          <t>Numerical Data Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="S56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
         <v>0.97</v>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Compliance Evaluation</t>
+          <t>Policy Compliance Assessment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Assesses policy compliance by documenting standards, targets and implementation approaches in action plans.</t>
+          <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="S57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
         <v>0.97</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="V57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Schedule Planning</t>
+          <t>Project Scheduling</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="S58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>0.97</v>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Change Complexity Assessment</t>
+          <t>Risk Assessment Planning</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Assesses ICT system change complexity and plans risk mitigation strategies across hybrid environments.</t>
+          <t>Assesses ICT system change complexity and plans mitigation strategies across hybrid environments.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="S59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
         <v>0.97</v>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Proposal Reporting</t>
+          <t>Stakeholder Reporting</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="S60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
         <v>0.97</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Plan Evaluation</t>
+          <t>Strategic Plan Analysis</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="S61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
         <v>0.97</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Decision Analysis</t>
+          <t>Systematic Decision Making</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="S62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
         <v>0.97</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Text Evaluation</t>
+          <t>Complex Text Analysis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="S64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
         <v>0.97</v>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Policy Compliance Review</t>
+          <t>Compliance Management</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="S65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
         <v>0.97</v>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ethics Code Application</t>
+          <t>Ethical Decision Making</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="S66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
         <v>0.95</v>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Information Synthesis</t>
+          <t>Information Synthesis Writing</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Combines diverse sources into clear written reports using specialised terminology and supporting documentation.</t>
+          <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="S69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
         <v>0.97</v>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="V69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Policy Updating</t>
+          <t>Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7674,7 +7674,7 @@
         </is>
       </c>
       <c r="S72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
         <v>0.97</v>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sequencing and Communication Management</t>
+          <t>Project Planning</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="S74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
         <v>0.97</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Change Monitoring</t>
+          <t>Regulatory Monitoring</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="S75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
         <v>0.97</v>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Information Security Management</t>
+          <t>Secure Digital Handling</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="S76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
         <v>0.97</v>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Policy Distribution</t>
+          <t>Stakeholder Communication</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="S77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
         <v>0.97</v>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Engage in verbal idea exchange, actively listen and ask questions to draw out others' views.</t>
+          <t>Talks with others, listens actively and asks questions to draw out their views.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Platform Installation</t>
+          <t>Blockchain Platform Setup</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="S79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
         <v>0.97</v>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Anomaly Detection</t>
+          <t>Blockchain Problem Solving</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="S80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
         <v>0.97</v>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Requirements Determination</t>
+          <t>Blockchain Requirements Analysis</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="S81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
         <v>0.97</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Configures and deploys system components to implement consensus mechanisms.</t>
+          <t>Configure and deploy system components to implement consensus mechanisms.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Documentation Submission</t>
+          <t>Documentation Submission and Feedback Management</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="S84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
         <v>0.97</v>
@@ -8886,7 +8886,7 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Schedule Development</t>
+          <t>Maintenance Schedule Planning</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Creates and records maintenance schedules that match equipment needs and timelines.</t>
+          <t>Develops and records maintenance schedules that match equipment requirements and timelines.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="S86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
         <v>0.97</v>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing</t>
+          <t>Maintenance Testing Execution</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="S87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
         <v>0.97</v>
@@ -9258,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="S90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
         <v>0.97</v>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Performance Evaluation</t>
+          <t>Solution Performance Testing</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
+          <t>Tests solutions against organisational requirements to confirm suitability.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="S91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
         <v>0.97</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="V91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Requirement Clarification</t>
+          <t>Stakeholder Oral Communication</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="S92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
         <v>0.97</v>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Use‑Case Identification</t>
+          <t>Use Case Identification</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9627,7 +9627,7 @@
         </is>
       </c>
       <c r="S93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
         <v>0.97</v>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Log Ingestion</t>
+          <t>Analytic Platform Operation</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="S94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Legislative and Policy Requirement Identification</t>
+          <t>Compliance Requirement Identification</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="S95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T95" t="n">
         <v>0.97</v>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Discrepancy Identification</t>
+          <t>Data Discrepancy Analysis</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="S96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
         <v>0.97</v>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Data Set Creation</t>
+          <t>Dataset Creation Procedures</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="S97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
         <v>0.97</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Data Detection</t>
+          <t>False Positive Detection</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10155,7 +10155,7 @@
         </is>
       </c>
       <c r="S98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
         <v>0.97</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Data Report Documentation</t>
+          <t>Incident Report Documentation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Produces formal investigation reports that outline findings and recommendations following organisational procedures.</t>
+          <t>Creates formal investigation reports that outline findings and recommendations following organisational procedures.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="S99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
         <v>0.97</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Likelihood Assessment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Evaluates threats by analysing likelihood and impact, then prioritises mitigation actions.</t>
+          <t>Evaluates threats by measuring likelihood and impact, then prioritises mitigation actions.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="S101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
         <v>0.97</v>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Log Ingestion</t>
+          <t>Security Log Ingestion</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="S103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
         <v>0.99</v>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Findings Communication</t>
+          <t>Stakeholder Findings Communication</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="S104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
         <v>0.97</v>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Data Gathering</t>
+          <t>Threat Data Collection</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collect and structure alerts, logs and event data according to organisational data policies.</t>
+          <t>Collects and structures alerts, logs and event data according to organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="S105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
         <v>0.97</v>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Process Implementation</t>
+          <t>Asset Management Implementation</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="S107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
         <v>0.97</v>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Research</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Feedback Management</t>
+          <t>Feedback Response Management</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="S111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
         <v>0.97</v>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Segmentation Implementation</t>
+          <t>Network Segmentation Deployment</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation to isolate security zones according to approved protection plans.</t>
+          <t>Deploys network segmentation to isolate security zones according to approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -11534,7 +11534,7 @@
         </is>
       </c>
       <c r="S112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
         <v>0.97</v>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Planning and Review</t>
+          <t>Project Planning Coordination</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11627,7 +11627,7 @@
         </is>
       </c>
       <c r="S113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
         <v>0.97</v>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Protection Plan Analysis</t>
+          <t>Critical Infrastructure Protection Plan Evaluation</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -11723,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="T114" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Protection Planning</t>
+          <t>Protection Strategy Development</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Develops and records critical infrastructure protection plans that align with organisational policies and procedures.</t>
+          <t>Develops and records protection plans for critical infrastructure that align with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="S115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
         <v>0.97</v>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Plan Testing</t>
+          <t>Protection Testing Execution</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="S116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
         <v>0.97</v>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Patch Installation</t>
+          <t>Patch Application</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="S119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Feedback Submission</t>
+          <t>Feedback Response Management</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="S122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Architecture Methodology Research</t>
+          <t>Industry Methodology Research</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="S123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
         <v>0.97</v>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Anomaly Identification</t>
+          <t>Problem Solving In Security</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Uses contextual awareness to spot security anomalies and deviations from normal operating patterns.</t>
+          <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="S124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
         <v>0.97</v>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="V124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Level Assessment</t>
+          <t>Security Level Determination</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
+          <t>Assesses assets to decide required security levels, perimeters, features and protection modes.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="S128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
         <v>0.97</v>
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="V128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Initiative Planning</t>
+          <t>Security Project Planning</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13226,7 +13226,7 @@
         </is>
       </c>
       <c r="S129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T129" t="n">
         <v>0.97</v>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Analyse organisational operations and infrastructure to identify specific security requirements.</t>
+          <t>Analyses organisational operations and infrastructure to identify specific security requirements.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="V130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W130" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Architecture Design</t>
+          <t>Security Solution Design</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="S131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
         <v>0.97</v>
@@ -13545,7 +13545,7 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Documentation Review</t>
+          <t>Technical Specification Reading</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="S133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T133" t="n">
         <v>0.97</v>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Strategic Decision Making</t>
+          <t>Autonomous Decision Making</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="S134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T134" t="n">
         <v>0.97</v>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Report Preparation</t>
+          <t>Incident Documentation Preparation</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Prepares detailed incident reports that document response actions against task requirements.</t>
+          <t>Prepares detailed incident reports that document response actions and meet task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="S136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
         <v>0.97</v>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Develop and record incident response plans that meet organisational requirements.</t>
+          <t>Develops and records incident response plans that meet organisational requirements.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Incident Team Coordination</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Document incident response team roles and services to support coordinated response.</t>
+          <t>Document incident response team roles and services to support a coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="S139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
         <v>0.97</v>
@@ -14310,7 +14310,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Exercise Design</t>
+          <t>Red Teaming Design</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="S140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
         <v>0.97</v>
@@ -14485,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Data Interpretation</t>
+          <t>Risk Analysis</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14591,7 +14591,7 @@
         </is>
       </c>
       <c r="S142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
         <v>0.97</v>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Response Execution</t>
+          <t>Security Incident Handling</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14700,10 +14700,10 @@
         </is>
       </c>
       <c r="S143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Policy Development</t>
+          <t>Security Policy Development</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Creates and records incident management policies that meet organisational specifications.</t>
+          <t>Develops and documents incident management policies that meet organisational specifications.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="S144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
         <v>0.97</v>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Impact Evaluation</t>
+          <t>Business Continuity Evaluation</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="S146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
         <v>0.97</v>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Strategy Development</t>
+          <t>Compliance Management</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="S147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
         <v>0.97</v>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Contingency Planning</t>
+          <t>Contingency Plan Development</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Develops contingency plans by identifying threats and defining response actions.</t>
+          <t>Identifies threats and defines response actions to develop contingency plans.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -15237,7 +15237,7 @@
         </is>
       </c>
       <c r="S148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
         <v>0.97</v>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="V148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Constraint Evaluation</t>
+          <t>Cost Constraint Analysis</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15342,7 +15342,7 @@
         </is>
       </c>
       <c r="S149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
         <v>0.97</v>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Recovery Plan Development</t>
+          <t>Disaster Recovery Planning</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Develops comprehensive disaster recovery plans that detail procedures, resources and recovery timeframes.</t>
+          <t>Creates detailed disaster recovery plans that outline procedures, resources and recovery timeframes.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -15447,7 +15447,7 @@
         </is>
       </c>
       <c r="S150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
         <v>0.97</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Standards Review</t>
+          <t>Industry Standards Review</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Data Evaluation</t>
+          <t>Numerical Data Analysis</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="S152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
         <v>0.97</v>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Recovery Planning Evaluation</t>
+          <t>Problem Solving</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="S154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
         <v>0.97</v>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Feedback Management</t>
+          <t>Stakeholder Communication</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Engages stakeholders by submitting documents on time, collecting feedback and responding promptly.</t>
+          <t>Engages stakeholders by submitting documents on time, collecting feedback, and responding promptly.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -16081,7 +16081,7 @@
         </is>
       </c>
       <c r="S156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
         <v>0.97</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Disaster Recovery Planning</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Develops and aligns hybrid work priorities and outcomes through structured strategic planning.</t>
+          <t>Creates hybrid work priorities and outcomes through structured strategic planning.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -16186,7 +16186,7 @@
         </is>
       </c>
       <c r="S157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
         <v>0.97</v>
@@ -16197,7 +16197,7 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Recovery Documentation Preparation</t>
+          <t>Technical Documentation Writing</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="S159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T159" t="n">
         <v>0.97</v>
@@ -16501,7 +16501,7 @@
         </is>
       </c>
       <c r="S160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
         <v>0.97</v>

--- a/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_refined_v2.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Best Practice Benchmarking</t>
+          <t>Best Practice Comparison</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="S3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Creative Thinking</t>
+          <t>Innovative Solution Generation</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
+          <t>Applies creative thinking techniques to develop new solutions for workplace challenges.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="S6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0.97</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Idea Evaluation Viability</t>
+          <t>Viability Evaluation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Systematically compare ideas with identified viability factors to assess them.</t>
+          <t>Systematically compares ideas against identified viability factors to assess them.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="S8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0.97</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Proposal Writing</t>
+          <t>Proposal Development</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="S10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0.97</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Research Information Gathering</t>
+          <t>Solution Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Collects and assesses data to find viable solutions for the identified issue.</t>
+          <t>Collects and evaluates data to identify viable solutions to the issue.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0.97</v>
@@ -1701,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
+          <t>Iteratively refine and finalise solutions to meet specific task requirements.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="V13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stakeholder Feedback Solicitation</t>
+          <t>Feedback Solicitation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Actively request stakeholder input on ideas to improve concepts and align expectations.</t>
+          <t>Proactively seeks stakeholder input on ideas to refine concepts and align expectations.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0.97</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Team Facilitation</t>
+          <t>Group Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Clear Technical Writing</t>
+          <t>Document Writing</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Writes workplace documents using precise cyber security terminology to convey technical information clearly.</t>
+          <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="V18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Current Awareness Assessment</t>
+          <t>Security Awareness Assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Assesses cyber security awareness in the work area using surveys and interviews to establish baseline levels.</t>
+          <t>We assess cyber security awareness in the work area using surveys and interviews to establish a baseline level.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="S19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0.97</v>
@@ -2649,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="S22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0.97</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Outcome Documentation</t>
+          <t>Outcome Reporting</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="S23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Policy Contribution Drafting</t>
+          <t>Policy Drafting</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="S24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>0.99</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Practice Review Execution</t>
+          <t>Security Practice Review</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="S25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Record Maintenance</t>
+          <t>Record Keeping</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Keeps cyber security protection records current by organising and documenting relevant data.</t>
+          <t>Maintains up‑to‑date cyber security protection records by organising and documenting relevant data.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
         <v>0.97</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="V26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Team Collaboration</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="S28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>0.97</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Technology Platform Utilisation</t>
+          <t>Security Platform Utilisation</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
+          <t>Select and operate suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="S29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0.97</v>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="V29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Threat Trend Analysis</t>
+          <t>Threat Trend Review</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
         <v>0.97</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Anti-Malware Deployment</t>
+          <t>Installation and Configuration</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Install and configure up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
+          <t>Installs and configures up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="S34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="V34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Breach Impact Review</t>
+          <t>Impact Analysis</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="S35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
         <v>0.97</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration Setup</t>
+          <t>Device Configuration</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Updates firmware and configures settings to set up new devices initially.</t>
+          <t>Sets up new devices by updating firmware and configuring settings.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="S36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Device Encryption Implementation</t>
+          <t>Device Encryption</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="S37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Device Inventory Management</t>
+          <t>Register Maintenance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="S38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Gap Analysis Evaluation</t>
+          <t>Effectiveness Evaluation</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="S39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
         <v>0.97</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Strength Creation</t>
+          <t>Password Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="S40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
         <v>0.99</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Risk Categorisation Analysis</t>
+          <t>Risk Categorisation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Evaluates device data sensitivity and assigns a suitable risk category for security management.</t>
+          <t>Evaluates device data sensitivity and assigns a risk category for security management.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="S42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
         <v>0.97</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Security Plan Briefing</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="S43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Security Strategy Support</t>
+          <t>Strategy Evaluation</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="S45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
         <v>0.97</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="S46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
         <v>0.97</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Software Patch Application</t>
+          <t>Patch Installation</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="S47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
         <v>0.97</v>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Two-Factor Authentication Enablement</t>
+          <t>Two-Factor Authentication Enabling</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Enable multi‑factor authentication on supported systems to strengthen account security.</t>
+          <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="S48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
         <v>0.99</v>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="V48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Digital Technology Utilisation</t>
+          <t>Technology Evaluation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="S51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>0.97</v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Document Preparation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Prepares evaluation documents, organises findings and submits them to a supervisor for review.</t>
+          <t>Prepare evaluation documents, organise findings, and submit them to a supervisor for review.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="S52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
         <v>0.97</v>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="V52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="S54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
         <v>0.97</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Innovative Solution Investigation</t>
+          <t>Idea Evaluation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="S55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
         <v>0.97</v>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Impact Assessment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Analyses numerical data and calculates financial impacts of proposed changes in hybrid environments.</t>
+          <t>Analyses data and calculates financial impacts of proposed changes in hybrid environments.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="S56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
         <v>0.97</v>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Policy Compliance Assessment</t>
+          <t>Compliance Evaluation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
+          <t>Assesses policy compliance by documenting standards, targets and implementation approaches in action plans.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="S57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
         <v>0.97</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="V57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Project Scheduling</t>
+          <t>Schedule Planning</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="S58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
         <v>0.97</v>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Risk Assessment Planning</t>
+          <t>Change Complexity Assessment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Assesses ICT system change complexity and plans mitigation strategies across hybrid environments.</t>
+          <t>Assesses ICT system change complexity and plans risk mitigation strategies across hybrid environments.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="S59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
         <v>0.97</v>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Stakeholder Reporting</t>
+          <t>Proposal Reporting</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="S60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
         <v>0.97</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Strategic Plan Analysis</t>
+          <t>Strategic Plan Evaluation</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="S61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>0.97</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Systematic Decision Making</t>
+          <t>Decision Analysis</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="S62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
         <v>0.97</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Complex Text Analysis</t>
+          <t>Compliance Analysis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="S64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
         <v>0.97</v>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Compliance Management</t>
+          <t>Policy Compliance Review</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="S65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
         <v>0.97</v>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ethical Decision Making</t>
+          <t>Code Application</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="S66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
         <v>0.95</v>
@@ -7212,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Information Synthesis Writing</t>
+          <t>Report Synthesis</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
+          <t>Combines diverse sources into clear written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="S69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="V69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Policy Documentation</t>
+          <t>Policy Updating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7674,7 +7674,7 @@
         </is>
       </c>
       <c r="S72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
         <v>0.97</v>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Project Planning</t>
+          <t>Sequencing and Communication Management</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="S74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
         <v>0.97</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Regulatory Monitoring</t>
+          <t>Change Monitoring</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
         <v>0.97</v>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Secure Digital Handling</t>
+          <t>Information Security Management</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="S76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
         <v>0.97</v>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Stakeholder Communication</t>
+          <t>Policy Distribution</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="S77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Talks with others, listens actively and asks questions to draw out their views.</t>
+          <t>Engage in verbal idea exchange, actively listen and ask questions to draw out others' views.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Blockchain Platform Setup</t>
+          <t>Platform Installation</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="S79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
         <v>0.97</v>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Problem Solving</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="S80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
         <v>0.97</v>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Blockchain Requirements Analysis</t>
+          <t>Requirements Determination</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="S81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
         <v>0.97</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Configure and deploy system components to implement consensus mechanisms.</t>
+          <t>Configures and deploys system components to implement consensus mechanisms.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8700,7 +8700,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Documentation Submission and Feedback Management</t>
+          <t>Documentation Submission</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="S84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Maintenance Schedule Planning</t>
+          <t>Schedule Development</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Develops and records maintenance schedules that match equipment requirements and timelines.</t>
+          <t>Creates and records maintenance schedules that match equipment needs and timelines.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="S86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing Execution</t>
+          <t>Maintenance Testing</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9069,10 +9069,10 @@
         </is>
       </c>
       <c r="S87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="S90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" t="n">
         <v>0.97</v>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Solution Performance Testing</t>
+          <t>Performance Evaluation</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests solutions against organisational requirements to confirm suitability.</t>
+          <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="S91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" t="n">
         <v>0.97</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="V91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Stakeholder Oral Communication</t>
+          <t>Requirement Clarification</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="S92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
         <v>0.97</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="S93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Analytic Platform Operation</t>
+          <t>Log Ingestion</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ingest data logs into analytics platforms as instructed to support monitoring and analysis.</t>
+          <t>Ingest data logs into analytics platforms to support monitoring and analysis.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="S94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" t="n">
         <v>0.99</v>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Compliance Requirement Identification</t>
+          <t>Requirement Identification</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="S95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
         <v>0.97</v>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Data Discrepancy Analysis</t>
+          <t>Discrepancy Identification</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="S96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" t="n">
         <v>0.97</v>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Dataset Creation Procedures</t>
+          <t>Data Set Creation</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="S97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" t="n">
         <v>0.97</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>False Positive Detection</t>
+          <t>Data Detection</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10155,7 +10155,7 @@
         </is>
       </c>
       <c r="S98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="n">
         <v>0.97</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Incident Report Documentation</t>
+          <t>Data Report Documentation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Creates formal investigation reports that outline findings and recommendations following organisational procedures.</t>
+          <t>Produces formal investigation reports that outline findings and recommendations following organisational procedures.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="S99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" t="n">
         <v>0.97</v>
@@ -10366,7 +10366,7 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Risk Likelihood Assessment</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Evaluates threats by measuring likelihood and impact, then prioritises mitigation actions.</t>
+          <t>Evaluates threats by analysing likelihood and impact, then prioritises mitigation actions.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="S101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" t="n">
         <v>0.97</v>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Security Log Ingestion</t>
+          <t>Log Ingestion</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="S103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" t="n">
         <v>0.99</v>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Stakeholder Findings Communication</t>
+          <t>Findings Communication</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="S104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" t="n">
         <v>0.97</v>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Data Gathering</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collects and structures alerts, logs and event data according to organisational data policies.</t>
+          <t>Collect and structure alerts, logs and event data according to organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="S105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" t="n">
         <v>0.97</v>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Asset Management Implementation</t>
+          <t>Process Implementation</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="S107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
         <v>0.97</v>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Feedback Response Management</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="S111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" t="n">
         <v>0.97</v>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Network Segmentation Deployment</t>
+          <t>Segmentation Implementation</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Deploys network segmentation to isolate security zones according to approved protection plans.</t>
+          <t>Implements network segmentation to isolate security zones according to approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -11534,7 +11534,7 @@
         </is>
       </c>
       <c r="S112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" t="n">
         <v>0.97</v>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Project Planning Coordination</t>
+          <t>Planning and Review</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11627,7 +11627,7 @@
         </is>
       </c>
       <c r="S113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" t="n">
         <v>0.97</v>
@@ -11723,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="T114" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Protection Strategy Development</t>
+          <t>Protection Planning</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Develops and records protection plans for critical infrastructure that align with organisational policies and procedures.</t>
+          <t>Develops and records critical infrastructure protection plans that align with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="S115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" t="n">
         <v>0.97</v>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Protection Testing Execution</t>
+          <t>Plan Testing</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Conduct protection plan testing to validate safeguards against organisational requirements.</t>
+          <t>Validates protection plans by testing safeguards against organisational requirements.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="S116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
         <v>0.97</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Results Analysis and Reporting</t>
+          <t>Implementation Results Analysis and Reporting</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12002,7 +12002,7 @@
         <v>1</v>
       </c>
       <c r="T117" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Feedback Response Management</t>
+          <t>Feedback Submission</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="S122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Industry Methodology Research</t>
+          <t>Architecture Methodology Research</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="S123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Problem Solving In Security</t>
+          <t>Anomaly Identification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
+          <t>Uses contextual awareness to spot security anomalies and deviations from normal operating patterns.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="S124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124" t="n">
         <v>0.97</v>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="V124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Validates security designs using industry‑recognised methodologies.</t>
+          <t>Validates security designs using industry‑recognised methods.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -13013,7 +13013,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="V127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Security Level Determination</t>
+          <t>Level Assessment</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Assesses assets to decide required security levels, perimeters, features and protection modes.</t>
+          <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="S128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
         <v>0.97</v>
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="V128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Security Project Planning</t>
+          <t>Initiative Planning</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13226,7 +13226,7 @@
         </is>
       </c>
       <c r="S129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" t="n">
         <v>0.97</v>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Security Solution Design</t>
+          <t>Architecture Design</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="S131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
         <v>0.97</v>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Creates detailed technical documentation that outlines findings and proposes solutions.</t>
+          <t>Creates detailed technical documentation that outlines findings and proposed solutions.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -13545,7 +13545,7 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Specification Reading</t>
+          <t>Documentation Review</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="S133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133" t="n">
         <v>0.97</v>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Autonomous Decision Making</t>
+          <t>Strategic Decision Making</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="S134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" t="n">
         <v>0.97</v>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Incident Documentation Preparation</t>
+          <t>Report Preparation</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Prepares detailed incident reports that document response actions and meet task requirements.</t>
+          <t>Prepares detailed incident reports that document response actions against task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -13961,10 +13961,10 @@
         </is>
       </c>
       <c r="S136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>1</v>
       </c>
       <c r="T137" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>1</v>
       </c>
       <c r="T138" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Incident Team Coordination</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Document incident response team roles and services to support a coordinated response.</t>
+          <t>Document incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="S139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139" t="n">
         <v>0.97</v>
@@ -14310,7 +14310,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Red Teaming Design</t>
+          <t>Incident Response Exercise Design</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="S140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T140" t="n">
         <v>0.97</v>
@@ -14520,7 +14520,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Risk Assessment Data Interpretation</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
+          <t>Interprets and records numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -14591,7 +14591,7 @@
         </is>
       </c>
       <c r="S142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T142" t="n">
         <v>0.97</v>
@@ -14602,7 +14602,7 @@
         </is>
       </c>
       <c r="V142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Security Incident Handling</t>
+          <t>Response Execution</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="S143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" t="n">
         <v>0.97</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Security Policy Development</t>
+          <t>Policy Development</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="S144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T144" t="n">
         <v>0.97</v>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Business Continuity Evaluation</t>
+          <t>Impact Evaluation</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="S146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" t="n">
         <v>0.97</v>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Compliance Management</t>
+          <t>Regulatory Strategy Development</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15128,10 +15128,10 @@
         </is>
       </c>
       <c r="S147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T147" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Contingency Plan Development</t>
+          <t>Contingency Planning</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Identifies threats and defines response actions to develop contingency plans.</t>
+          <t>Develops contingency plans by identifying threats and defining response actions.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -15237,10 +15237,10 @@
         </is>
       </c>
       <c r="S148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="V148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W148" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cost Constraint Analysis</t>
+          <t>Prevention and Recovery Evaluation</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15342,10 +15342,10 @@
         </is>
       </c>
       <c r="S149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T149" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Disaster Recovery Planning</t>
+          <t>Recovery Plan Development</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Creates detailed disaster recovery plans that outline procedures, resources and recovery timeframes.</t>
+          <t>Develops comprehensive disaster recovery plans that detail procedures, resources and recovery timeframes.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="S150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Industry Standards Review</t>
+          <t>Standards Evaluation</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15552,7 +15552,7 @@
         </is>
       </c>
       <c r="S151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T151" t="n">
         <v>0.97</v>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Numerical Data Analysis</t>
+          <t>Data Evaluation</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="S152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" t="n">
         <v>0.97</v>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
+          <t>Continuity Evaluation</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="S154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154" t="n">
         <v>0.97</v>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Stakeholder Communication</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16081,7 +16081,7 @@
         </is>
       </c>
       <c r="S156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" t="n">
         <v>0.97</v>
@@ -16186,7 +16186,7 @@
         </is>
       </c>
       <c r="S157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T157" t="n">
         <v>0.97</v>
@@ -16294,7 +16294,7 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Technical Documentation Writing</t>
+          <t>Recovery Documentation Preparation</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="S159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T159" t="n">
         <v>0.97</v>
@@ -16501,7 +16501,7 @@
         </is>
       </c>
       <c r="S160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" t="n">
         <v>0.97</v>
